--- a/snippet-extractor-metadata/word.xlsx
+++ b/snippet-extractor-metadata/word.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF34F44-527C-4446-A3C9-73489A74B909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14863876-029E-4319-A045-C665BA386D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2351" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="613">
   <si>
     <t>Class</t>
   </si>
@@ -1835,6 +1835,30 @@
   </si>
   <si>
     <t>ExportFormat</t>
+  </si>
+  <si>
+    <t>selection</t>
+  </si>
+  <si>
+    <t>word-selection-insert-formula</t>
+  </si>
+  <si>
+    <t>insertFormulaCustom</t>
+  </si>
+  <si>
+    <t>insertFormulaAuto</t>
+  </si>
+  <si>
+    <t>Selection</t>
+  </si>
+  <si>
+    <t>insertFormula</t>
+  </si>
+  <si>
+    <t>insertFormulaWithOptions</t>
+  </si>
+  <si>
+    <t>SelectionInsertFormulaOptions</t>
   </si>
 </sst>
 </file>
@@ -1883,7 +1907,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1894,8 +1918,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1951,8 +1973,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F470" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="A1:F470" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F474" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:F474" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{1DA12987-AB2C-4056-A643-B1229DC856C5}" name="Package" dataDxfId="4"/>
     <tableColumn id="1" xr3:uid="{0CD83AD1-F92A-407D-8460-4E881461FD01}" name="Class" dataDxfId="3"/>
@@ -2262,7 +2284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F470"/>
+  <dimension ref="A1:F474"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25.08984375" bestFit="1" customWidth="1"/>
@@ -5579,16 +5601,16 @@
       <c r="B182" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C182" s="4" t="s">
+      <c r="C182" s="1" t="s">
         <v>603</v>
       </c>
       <c r="D182" s="1">
         <v>1</v>
       </c>
-      <c r="E182" s="5" t="s">
+      <c r="E182" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="F182" s="2" t="s">
         <v>601</v>
       </c>
     </row>
@@ -6091,21 +6113,21 @@
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A210" s="1" t="s">
+      <c r="A210" t="s">
         <v>162</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C210" s="2" t="s">
-        <v>165</v>
+      <c r="C210" s="5" t="s">
+        <v>605</v>
       </c>
       <c r="D210" s="2"/>
-      <c r="E210" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>169</v>
+      <c r="E210" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.35">
@@ -6116,14 +6138,14 @@
         <v>65</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>530</v>
+        <v>165</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" s="2" t="s">
-        <v>497</v>
+        <v>164</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>529</v>
+        <v>169</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.35">
@@ -6131,17 +6153,17 @@
         <v>162</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C212" s="2"/>
-      <c r="D212" s="2" t="s">
-        <v>345</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D212" s="2"/>
       <c r="E212" s="2" t="s">
-        <v>389</v>
+        <v>497</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>86</v>
+        <v>529</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.35">
@@ -6149,34 +6171,34 @@
         <v>162</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D213" t="s">
-        <v>144</v>
+        <v>390</v>
+      </c>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>235</v>
+        <v>389</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>236</v>
+        <v>86</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B214" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="C214" s="7"/>
+      <c r="B214" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="D214" t="s">
-        <v>345</v>
-      </c>
-      <c r="E214" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="F214" s="5" t="s">
-        <v>601</v>
+        <v>144</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.35">
@@ -6184,16 +6206,16 @@
         <v>162</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>436</v>
+        <v>602</v>
       </c>
       <c r="D215" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>74</v>
+        <v>600</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>64</v>
+        <v>601</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.35">
@@ -6201,17 +6223,16 @@
         <v>162</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C216" s="2"/>
-      <c r="D216" s="2" t="s">
-        <v>128</v>
+        <v>436</v>
+      </c>
+      <c r="D216" t="s">
+        <v>144</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.35">
@@ -6219,17 +6240,17 @@
         <v>162</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>461</v>
+        <v>170</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>494</v>
+        <v>73</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.35">
@@ -6239,17 +6260,15 @@
       <c r="B218" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C218" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D218" s="2">
-        <v>1</v>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>494</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.35">
@@ -6260,7 +6279,7 @@
         <v>461</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D219" s="2">
         <v>1</v>
@@ -6269,7 +6288,7 @@
         <v>494</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.35">
@@ -6280,14 +6299,16 @@
         <v>461</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D220" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="D220" s="2">
+        <v>1</v>
+      </c>
       <c r="E220" s="2" t="s">
         <v>494</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.35">
@@ -6295,17 +6316,17 @@
         <v>162</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C221" s="2"/>
-      <c r="D221" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D221" s="2"/>
       <c r="E221" s="2" t="s">
-        <v>393</v>
+        <v>494</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>430</v>
+        <v>473</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.35">
@@ -6313,17 +6334,17 @@
         <v>162</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>123</v>
+        <v>430</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.35">
@@ -6341,60 +6362,60 @@
         <v>403</v>
       </c>
       <c r="F223" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A224" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>405</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
-        <v>162</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C224" s="1"/>
-      <c r="D224" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>162</v>
       </c>
-      <c r="B225" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="C225" s="4"/>
+      <c r="B225" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C225" s="1"/>
       <c r="D225" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E225" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="F225" s="6" t="s">
-        <v>601</v>
+      <c r="E225" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A226" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B226" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="C226" s="4"/>
+      <c r="A226" t="s">
+        <v>162</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C226" s="1"/>
       <c r="D226" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E226" s="5" t="s">
+      <c r="E226" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="F226" s="6" t="s">
+      <c r="F226" s="3" t="s">
         <v>601</v>
       </c>
     </row>
@@ -6403,17 +6424,17 @@
         <v>162</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C227" s="2"/>
-      <c r="D227" s="2" t="s">
-        <v>144</v>
+        <v>599</v>
+      </c>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>136</v>
+        <v>600</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.35">
@@ -6423,17 +6444,15 @@
       <c r="B228" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C228" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D228" s="1">
-        <v>1</v>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F228" s="3" t="s">
-        <v>290</v>
+      <c r="F228" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.35">
@@ -6444,7 +6463,7 @@
         <v>132</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D229" s="1">
         <v>1</v>
@@ -6453,7 +6472,7 @@
         <v>163</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
@@ -6464,7 +6483,7 @@
         <v>132</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>287</v>
+        <v>48</v>
       </c>
       <c r="D230" s="1">
         <v>1</v>
@@ -6477,38 +6496,40 @@
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
+      <c r="A231" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C231" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D231" s="2"/>
+      <c r="C231" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D231" s="1">
+        <v>1</v>
+      </c>
       <c r="E231" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F231" s="2" t="s">
-        <v>136</v>
+      <c r="F231" s="3" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A232" s="1" t="s">
+      <c r="A232" t="s">
         <v>162</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D232" s="1"/>
+      <c r="C232" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D232" s="2"/>
       <c r="E232" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F232" s="3" t="s">
+      <c r="F232" s="2" t="s">
         <v>136</v>
       </c>
     </row>
@@ -6519,33 +6540,33 @@
       <c r="B233" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C233" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D233" s="2"/>
+      <c r="C233" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D233" s="1"/>
       <c r="E233" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F233" s="2" t="s">
-        <v>289</v>
+      <c r="F233" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
+      <c r="A234" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.35">
@@ -6556,25 +6577,25 @@
         <v>132</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A236" s="1" t="s">
+      <c r="A236" t="s">
         <v>162</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" s="2" t="s">
@@ -6585,21 +6606,21 @@
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A237" t="s">
+      <c r="A237" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C237" s="2"/>
-      <c r="D237" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D237" s="2"/>
       <c r="E237" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.35">
@@ -6609,17 +6630,15 @@
       <c r="B238" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C238" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D238" s="2">
-        <v>1</v>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.35">
@@ -6630,32 +6649,34 @@
         <v>139</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D239" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="D239" s="2">
+        <v>1</v>
+      </c>
       <c r="E239" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A240" s="1" t="s">
+      <c r="A240" t="s">
         <v>162</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C240" s="2"/>
-      <c r="D240" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D240" s="2"/>
       <c r="E240" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
@@ -6663,7 +6684,7 @@
         <v>162</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>285</v>
+        <v>410</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2" t="s">
@@ -6673,7 +6694,7 @@
         <v>163</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>284</v>
+        <v>136</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
@@ -6681,17 +6702,17 @@
         <v>162</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>557</v>
+        <v>285</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>555</v>
+        <v>163</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>560</v>
+        <v>284</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
@@ -6699,53 +6720,53 @@
         <v>162</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>423</v>
+        <v>557</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>424</v>
+        <v>555</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>86</v>
+        <v>560</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A244" t="s">
+      <c r="A244" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>149</v>
+        <v>423</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="2" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A245" s="1" t="s">
+      <c r="A245" t="s">
         <v>162</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
@@ -6753,55 +6774,55 @@
         <v>162</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>525</v>
+        <v>173</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E246" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A247" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E247" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F246" s="2" t="s">
+      <c r="F247" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A247" t="s">
-        <v>162</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D247" s="2">
-        <v>1</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A248" s="1" t="s">
+      <c r="A248" t="s">
         <v>162</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C248" s="2"/>
-      <c r="D248" s="2" t="s">
-        <v>144</v>
+      <c r="C248" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D248" s="2">
+        <v>1</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
@@ -6811,15 +6832,15 @@
       <c r="B249" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C249" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E249" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.35">
@@ -6827,12 +6848,12 @@
         <v>162</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C250" s="2"/>
-      <c r="D250" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D250" s="2"/>
       <c r="E250" s="2" t="s">
         <v>70</v>
       </c>
@@ -6845,53 +6866,53 @@
         <v>162</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>347</v>
+        <v>177</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" s="2" t="s">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>348</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A252" t="s">
+      <c r="A252" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>154</v>
+        <v>347</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" s="2" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>140</v>
+        <v>235</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>155</v>
+        <v>348</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A253" s="1" t="s">
+      <c r="A253" t="s">
         <v>162</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>510</v>
+        <v>154</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="2" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>537</v>
+        <v>140</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>511</v>
+        <v>155</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
@@ -6899,17 +6920,17 @@
         <v>162</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>215</v>
+        <v>510</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>57</v>
+        <v>537</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>58</v>
+        <v>511</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
@@ -6919,11 +6940,9 @@
       <c r="B255" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C255" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D255" s="2">
-        <v>1</v>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>57</v>
@@ -6940,16 +6959,16 @@
         <v>215</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="D256" s="2">
         <v>1</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>220</v>
+        <v>58</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.35">
@@ -6960,7 +6979,7 @@
         <v>215</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D257" s="2">
         <v>1</v>
@@ -6980,14 +6999,16 @@
         <v>215</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D258" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="D258" s="2">
+        <v>1</v>
+      </c>
       <c r="E258" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.35">
@@ -6998,7 +7019,7 @@
         <v>215</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" s="2" t="s">
@@ -7013,17 +7034,17 @@
         <v>162</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C260" s="2"/>
-      <c r="D260" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D260" s="2"/>
       <c r="E260" s="2" t="s">
-        <v>481</v>
+        <v>219</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>64</v>
+        <v>300</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.35">
@@ -7031,17 +7052,17 @@
         <v>162</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>222</v>
+        <v>480</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>219</v>
+        <v>481</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>220</v>
+        <v>64</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.35">
@@ -7049,17 +7070,17 @@
         <v>162</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>425</v>
+        <v>222</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.35">
@@ -7067,17 +7088,17 @@
         <v>162</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>216</v>
+        <v>425</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>58</v>
+        <v>300</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.35">
@@ -7087,10 +7108,10 @@
       <c r="B264" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C264" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D264" s="2"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E264" s="2" t="s">
         <v>57</v>
       </c>
@@ -7103,17 +7124,17 @@
         <v>162</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C265" s="2"/>
-      <c r="D265" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D265" s="2"/>
       <c r="E265" s="2" t="s">
-        <v>481</v>
+        <v>57</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.35">
@@ -7121,7 +7142,7 @@
         <v>162</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2" t="s">
@@ -7139,17 +7160,17 @@
         <v>162</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>225</v>
+        <v>484</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>219</v>
+        <v>481</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>300</v>
+        <v>64</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.35">
@@ -7157,7 +7178,7 @@
         <v>162</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2" t="s">
@@ -7167,7 +7188,7 @@
         <v>219</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.35">
@@ -7175,17 +7196,17 @@
         <v>162</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>485</v>
+        <v>224</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>481</v>
+        <v>219</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>64</v>
+        <v>220</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.35">
@@ -7193,35 +7214,35 @@
         <v>162</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>226</v>
+        <v>485</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>227</v>
+        <v>481</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>228</v>
+        <v>64</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A271" t="s">
+      <c r="A271" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>91</v>
+        <v>226</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.35">
@@ -7231,17 +7252,15 @@
       <c r="B272" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C272" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D272" s="2">
-        <v>1</v>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.35">
@@ -7252,7 +7271,7 @@
         <v>91</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D273" s="2">
         <v>1</v>
@@ -7261,7 +7280,7 @@
         <v>146</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.35">
@@ -7272,14 +7291,16 @@
         <v>91</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D274" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="D274" s="2">
+        <v>1</v>
+      </c>
       <c r="E274" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.35">
@@ -7290,14 +7311,14 @@
         <v>91</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
@@ -7308,14 +7329,14 @@
         <v>91</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.35">
@@ -7323,17 +7344,17 @@
         <v>162</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C277" s="2"/>
-      <c r="D277" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D277" s="2"/>
       <c r="E277" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
@@ -7343,11 +7364,9 @@
       <c r="B278" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C278" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D278" s="2">
-        <v>1</v>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>146</v>
@@ -7360,34 +7379,37 @@
       <c r="A279" t="s">
         <v>162</v>
       </c>
-      <c r="B279" t="s">
-        <v>156</v>
-      </c>
-      <c r="D279" t="s">
-        <v>128</v>
+      <c r="B279" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D279" s="2">
+        <v>1</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A280" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>411</v>
+      <c r="A280" t="s">
+        <v>162</v>
+      </c>
+      <c r="B280" t="s">
+        <v>156</v>
       </c>
       <c r="D280" t="s">
         <v>128</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>374</v>
+        <v>146</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>375</v>
+        <v>95</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.35">
@@ -7395,16 +7417,16 @@
         <v>162</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>499</v>
+        <v>411</v>
       </c>
       <c r="D281" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>497</v>
+        <v>374</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>498</v>
+        <v>375</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
@@ -7414,11 +7436,8 @@
       <c r="B282" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C282" t="s">
-        <v>115</v>
-      </c>
-      <c r="D282">
-        <v>1</v>
+      <c r="D282" t="s">
+        <v>144</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>497</v>
@@ -7435,13 +7454,16 @@
         <v>499</v>
       </c>
       <c r="C283" t="s">
-        <v>500</v>
+        <v>115</v>
+      </c>
+      <c r="D283">
+        <v>1</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.35">
@@ -7449,16 +7471,16 @@
         <v>162</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="D284" t="s">
-        <v>144</v>
+        <v>499</v>
+      </c>
+      <c r="C284" t="s">
+        <v>500</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.35">
@@ -7466,7 +7488,7 @@
         <v>162</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="D285" t="s">
         <v>144</v>
@@ -7475,7 +7497,7 @@
         <v>497</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
@@ -7485,8 +7507,8 @@
       <c r="B286" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C286" t="s">
-        <v>508</v>
+      <c r="D286" t="s">
+        <v>144</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>497</v>
@@ -7503,13 +7525,13 @@
         <v>504</v>
       </c>
       <c r="C287" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.35">
@@ -7517,34 +7539,33 @@
         <v>162</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="D288" t="s">
-        <v>144</v>
+        <v>504</v>
+      </c>
+      <c r="C288" t="s">
+        <v>509</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F288" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A289" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D289" t="s">
+        <v>144</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>527</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A289" t="s">
-        <v>162</v>
-      </c>
-      <c r="B289" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C289" s="2"/>
-      <c r="D289" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E289" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.35">
@@ -7554,77 +7575,75 @@
       <c r="B290" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C290" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D290" s="2">
-        <v>1</v>
+      <c r="C290" s="2"/>
+      <c r="D290" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A291" s="1" t="s">
+      <c r="A291" t="s">
         <v>162</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>360</v>
+        <v>115</v>
       </c>
       <c r="D291" s="2">
         <v>1</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>360</v>
+        <v>12</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A292" t="s">
+      <c r="A292" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>29</v>
+        <v>360</v>
       </c>
       <c r="D292" s="2">
         <v>1</v>
       </c>
-      <c r="E292" s="2" t="s">
-        <v>75</v>
+      <c r="E292" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>28</v>
+        <v>360</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A293" s="1" t="s">
+      <c r="A293" t="s">
         <v>162</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D293" s="2">
         <v>1</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
@@ -7635,36 +7654,36 @@
         <v>10</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>556</v>
+        <v>36</v>
       </c>
       <c r="D294" s="2">
         <v>1</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>570</v>
+        <v>43</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A295" t="s">
+      <c r="A295" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>13</v>
+        <v>556</v>
       </c>
       <c r="D295" s="2">
         <v>1</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
@@ -7675,16 +7694,16 @@
         <v>10</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>512</v>
+        <v>13</v>
       </c>
       <c r="D296" s="2">
         <v>1</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>537</v>
+        <v>81</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>523</v>
+        <v>22</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.35">
@@ -7695,16 +7714,16 @@
         <v>10</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>48</v>
+        <v>512</v>
       </c>
       <c r="D297" s="2">
         <v>1</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>71</v>
+        <v>537</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>47</v>
+        <v>523</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
@@ -7724,7 +7743,7 @@
         <v>71</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.35">
@@ -7734,17 +7753,17 @@
       <c r="B299" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C299" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D299" s="1">
+      <c r="C299" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D299" s="2">
         <v>1</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.35">
@@ -7754,17 +7773,17 @@
       <c r="B300" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C300" s="2" t="s">
+      <c r="C300" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D300" s="2">
+      <c r="D300" s="1">
         <v>1</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.35">
@@ -7775,16 +7794,16 @@
         <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="D301" s="2">
         <v>1</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
@@ -7795,16 +7814,16 @@
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D302" s="2">
         <v>1</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.35">
@@ -7815,14 +7834,16 @@
         <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D303" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D303" s="2">
+        <v>1</v>
+      </c>
       <c r="E303" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.35">
@@ -7833,14 +7854,14 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.35">
@@ -7851,86 +7872,86 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A306" s="1" t="s">
+      <c r="A306" t="s">
         <v>162</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A307" s="3" t="s">
+      <c r="A307" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A308" t="s">
+      <c r="A308" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>17</v>
+        <v>381</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>17</v>
+        <v>382</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A309" s="1" t="s">
+      <c r="A309" t="s">
         <v>162</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>280</v>
+        <v>17</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" s="2" t="s">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>279</v>
+        <v>17</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
@@ -7941,32 +7962,32 @@
         <v>10</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" s="2" t="s">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A311" t="s">
+      <c r="A311" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>8</v>
+        <v>238</v>
       </c>
       <c r="D311" s="2"/>
-      <c r="E311" s="1" t="s">
-        <v>79</v>
+      <c r="E311" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>11</v>
+        <v>240</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.35">
@@ -7977,14 +7998,14 @@
         <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" s="1" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.35">
@@ -8002,25 +8023,25 @@
         <v>350</v>
       </c>
       <c r="F313" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>162</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D314" s="2"/>
+      <c r="E314" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F314" s="2" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A314" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C314" s="2"/>
-      <c r="D314" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E314" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.35">
@@ -8038,7 +8059,7 @@
         <v>318</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>319</v>
+        <v>267</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
@@ -8046,17 +8067,17 @@
         <v>162</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" s="2" t="s">
         <v>345</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>267</v>
+        <v>319</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
@@ -8074,65 +8095,63 @@
         <v>322</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A318" t="s">
+      <c r="A318" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>190</v>
+        <v>329</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>70</v>
+        <v>345</v>
+      </c>
+      <c r="E318" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>175</v>
+        <v>324</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A319" s="1" t="s">
+      <c r="A319" t="s">
         <v>162</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C319" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D319" s="2">
-        <v>1</v>
-      </c>
-      <c r="E319" s="1" t="s">
-        <v>350</v>
+      <c r="C319" s="2"/>
+      <c r="D319" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>353</v>
+        <v>175</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A320" t="s">
+      <c r="A320" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="D320" s="2">
         <v>1</v>
       </c>
-      <c r="E320" s="2" t="s">
-        <v>70</v>
+      <c r="E320" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>175</v>
+        <v>353</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
@@ -8143,14 +8162,16 @@
         <v>190</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D321" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="D321" s="2">
+        <v>1</v>
+      </c>
       <c r="E321" s="2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.35">
@@ -8158,17 +8179,17 @@
         <v>162</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C322" s="2"/>
-      <c r="D322" s="2" t="s">
-        <v>345</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D322" s="2"/>
       <c r="E322" s="2" t="s">
-        <v>323</v>
+        <v>57</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>267</v>
+        <v>58</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
@@ -8186,25 +8207,25 @@
         <v>323</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>325</v>
+        <v>267</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A324" s="1" t="s">
+      <c r="A324" t="s">
         <v>162</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
@@ -8214,10 +8235,10 @@
       <c r="B325" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C325" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D325" s="2"/>
+      <c r="C325" s="2"/>
+      <c r="D325" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E325" s="2" t="s">
         <v>269</v>
       </c>
@@ -8233,7 +8254,7 @@
         <v>281</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" s="2" t="s">
@@ -8248,17 +8269,17 @@
         <v>162</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C327" s="2"/>
-      <c r="D327" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D327" s="2"/>
       <c r="E327" s="2" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>445</v>
+        <v>294</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.35">
@@ -8268,17 +8289,15 @@
       <c r="B328" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C328" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D328" s="2">
-        <v>1</v>
+      <c r="C328" s="2"/>
+      <c r="D328" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>228</v>
+        <v>445</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -8289,36 +8308,36 @@
         <v>5</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>492</v>
+        <v>229</v>
       </c>
       <c r="D329" s="2">
         <v>1</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>12</v>
+        <v>228</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A330" t="s">
+      <c r="A330" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C330" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D330" s="1">
+      <c r="C330" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D330" s="2">
         <v>1</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
@@ -8329,16 +8348,16 @@
         <v>5</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>395</v>
+        <v>107</v>
       </c>
       <c r="D331" s="1">
         <v>1</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>393</v>
+        <v>145</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>427</v>
+        <v>108</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
@@ -8349,16 +8368,16 @@
         <v>5</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>115</v>
+        <v>395</v>
       </c>
       <c r="D332" s="1">
         <v>1</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>494</v>
+        <v>393</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.35">
@@ -8369,16 +8388,16 @@
         <v>5</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D333" s="1">
         <v>1</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>147</v>
+        <v>494</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>121</v>
+        <v>462</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.35">
@@ -8389,16 +8408,16 @@
         <v>5</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="D334" s="1">
         <v>1</v>
       </c>
-      <c r="E334" s="1" t="s">
-        <v>79</v>
+      <c r="E334" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
@@ -8409,16 +8428,16 @@
         <v>5</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="D335" s="1">
         <v>1</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
@@ -8429,56 +8448,56 @@
         <v>5</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="D336" s="1">
         <v>1</v>
       </c>
-      <c r="E336" s="2" t="s">
-        <v>82</v>
+      <c r="E336" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A337" s="1" t="s">
+      <c r="A337" t="s">
         <v>162</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>283</v>
+        <v>36</v>
       </c>
       <c r="D337" s="1">
         <v>1</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>284</v>
+        <v>35</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A338" t="s">
+      <c r="A338" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>88</v>
+        <v>283</v>
       </c>
       <c r="D338" s="1">
         <v>1</v>
       </c>
-      <c r="E338" s="1" t="s">
-        <v>146</v>
+      <c r="E338" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>88</v>
+        <v>284</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
@@ -8489,16 +8508,16 @@
         <v>5</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>313</v>
+        <v>88</v>
       </c>
       <c r="D339" s="1">
         <v>1</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>537</v>
+        <v>146</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>521</v>
+        <v>88</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
@@ -8518,7 +8537,7 @@
         <v>537</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.35">
@@ -8529,16 +8548,16 @@
         <v>5</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>556</v>
+        <v>313</v>
       </c>
       <c r="D341" s="1">
         <v>1</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.35">
@@ -8549,16 +8568,16 @@
         <v>5</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>512</v>
+        <v>556</v>
       </c>
       <c r="D342" s="1">
         <v>1</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>511</v>
+        <v>561</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.35">
@@ -8569,31 +8588,34 @@
         <v>5</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D343" s="1"/>
+        <v>512</v>
+      </c>
+      <c r="D343" s="1">
+        <v>1</v>
+      </c>
       <c r="E343" s="1" t="s">
-        <v>146</v>
+        <v>537</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>96</v>
+        <v>511</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A344" s="1" t="s">
+      <c r="A344" t="s">
         <v>162</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C344" t="s">
-        <v>428</v>
-      </c>
-      <c r="E344" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F344" t="s">
-        <v>422</v>
+      <c r="C344" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D344" s="1"/>
+      <c r="E344" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F344" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.35">
@@ -8603,15 +8625,14 @@
       <c r="B345" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C345" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D345" s="2"/>
+      <c r="C345" t="s">
+        <v>428</v>
+      </c>
       <c r="E345" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F345" s="2" t="s">
-        <v>239</v>
+        <v>393</v>
+      </c>
+      <c r="F345" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.35">
@@ -8619,53 +8640,53 @@
         <v>162</v>
       </c>
       <c r="B346" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D346" s="2"/>
+      <c r="E346" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F346" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A347" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C346" s="2"/>
-      <c r="D346" s="2" t="s">
+      <c r="C347" s="2"/>
+      <c r="D347" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E346" s="2" t="s">
+      <c r="E347" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F346" s="2" t="s">
+      <c r="F347" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A347" t="s">
-        <v>162</v>
-      </c>
-      <c r="B347" s="1" t="s">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>162</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C347" s="1"/>
-      <c r="D347" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E347" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F347" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A348" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B348" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="C348" s="1"/>
       <c r="D348" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>570</v>
+        <v>79</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>576</v>
+        <v>12</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.35">
@@ -8673,7 +8694,7 @@
         <v>162</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C349" s="1"/>
       <c r="D349" s="1" t="s">
@@ -8683,7 +8704,7 @@
         <v>570</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
@@ -8691,7 +8712,7 @@
         <v>162</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C350" s="1"/>
       <c r="D350" s="1" t="s">
@@ -8701,7 +8722,7 @@
         <v>570</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
@@ -8709,17 +8730,17 @@
         <v>162</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>418</v>
+        <v>579</v>
       </c>
       <c r="C351" s="1"/>
       <c r="D351" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>413</v>
+        <v>570</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>414</v>
+        <v>576</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
@@ -8727,37 +8748,35 @@
         <v>162</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>534</v>
+        <v>418</v>
       </c>
       <c r="C352" s="1"/>
       <c r="D352" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E352" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F352" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A353" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E353" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F352" s="2" t="s">
+      <c r="F353" s="2" t="s">
         <v>533</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A353" t="s">
-        <v>162</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C353" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D353" s="2">
-        <v>2</v>
-      </c>
-      <c r="E353" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F353" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.35">
@@ -8767,17 +8786,17 @@
       <c r="B354" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C354" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D354" s="1">
-        <v>1</v>
+      <c r="C354" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D354" s="2">
+        <v>2</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.35">
@@ -8787,15 +8806,17 @@
       <c r="B355" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C355" s="1"/>
-      <c r="D355" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>140</v>
+      <c r="C355" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D355" s="1">
+        <v>1</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
@@ -8803,17 +8824,17 @@
         <v>162</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C356" s="2"/>
-      <c r="D356" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C356" s="1"/>
+      <c r="D356" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E356" s="2" t="s">
+      <c r="E356" s="1" t="s">
         <v>140</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.35">
@@ -8821,89 +8842,91 @@
         <v>162</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="C357" s="2"/>
       <c r="D357" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A358" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B358" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C358" s="2"/>
+      <c r="A358" t="s">
+        <v>162</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="C358" s="5"/>
       <c r="D358" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E358" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F358" s="2" t="s">
-        <v>168</v>
+      <c r="E358" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="F358" s="5" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A359" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B359" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D359" s="2"/>
-      <c r="E359" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F359" s="2" t="s">
-        <v>168</v>
+      <c r="A359" t="s">
+        <v>162</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D359" s="2">
+        <v>1</v>
+      </c>
+      <c r="E359" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="F359" s="5" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A360" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B360" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C360" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D360" s="2"/>
-      <c r="E360" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F360" s="2" t="s">
-        <v>168</v>
+      <c r="A360" t="s">
+        <v>162</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="C360" s="5"/>
+      <c r="D360" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E360" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="F360" s="5" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A361" s="1" t="s">
+      <c r="A361" t="s">
         <v>162</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C361" s="2"/>
       <c r="D361" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>164</v>
+        <v>71</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>166</v>
+        <v>49</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.35">
@@ -8911,13 +8934,11 @@
         <v>162</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C362" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D362" s="2">
-        <v>1</v>
+        <v>296</v>
+      </c>
+      <c r="C362" s="2"/>
+      <c r="D362" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>164</v>
@@ -8931,17 +8952,17 @@
         <v>162</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>167</v>
+        <v>296</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>67</v>
+        <v>297</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" s="2" t="s">
         <v>164</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
@@ -8949,17 +8970,17 @@
         <v>162</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C364" s="2"/>
-      <c r="D364" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D364" s="2"/>
       <c r="E364" s="2" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>489</v>
+        <v>168</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
@@ -8967,17 +8988,17 @@
         <v>162</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>490</v>
+        <v>167</v>
       </c>
       <c r="C365" s="2"/>
       <c r="D365" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>489</v>
+        <v>166</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.35">
@@ -8985,17 +9006,19 @@
         <v>162</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C366" s="2"/>
-      <c r="D366" s="2" t="s">
-        <v>144</v>
+        <v>167</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D366" s="2">
+        <v>1</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>537</v>
+        <v>164</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>519</v>
+        <v>168</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.35">
@@ -9003,19 +9026,17 @@
         <v>162</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>516</v>
+        <v>167</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D367" s="2">
-        <v>1</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D367" s="2"/>
       <c r="E367" s="2" t="s">
-        <v>537</v>
+        <v>164</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>522</v>
+        <v>169</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
@@ -9023,19 +9044,17 @@
         <v>162</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C368" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="D368" s="2">
-        <v>1</v>
+        <v>491</v>
+      </c>
+      <c r="C368" s="2"/>
+      <c r="D368" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>570</v>
+        <v>269</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>584</v>
+        <v>489</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
@@ -9043,19 +9062,17 @@
         <v>162</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C369" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D369" s="2">
-        <v>1</v>
+        <v>490</v>
+      </c>
+      <c r="C369" s="2"/>
+      <c r="D369" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>570</v>
+        <v>269</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>584</v>
+        <v>489</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.35">
@@ -9065,17 +9082,15 @@
       <c r="B370" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C370" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="D370" s="2">
-        <v>1</v>
+      <c r="C370" s="2"/>
+      <c r="D370" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>581</v>
+        <v>519</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
@@ -9086,16 +9101,16 @@
         <v>516</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>588</v>
+        <v>97</v>
       </c>
       <c r="D371" s="2">
         <v>1</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>581</v>
+        <v>522</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.35">
@@ -9106,7 +9121,7 @@
         <v>516</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>48</v>
+        <v>583</v>
       </c>
       <c r="D372" s="2">
         <v>1</v>
@@ -9115,7 +9130,7 @@
         <v>570</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
@@ -9126,14 +9141,16 @@
         <v>516</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D373" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="D373" s="2">
+        <v>1</v>
+      </c>
       <c r="E373" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>520</v>
+        <v>584</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.35">
@@ -9144,14 +9161,16 @@
         <v>516</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D374" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="D374" s="2">
+        <v>1</v>
+      </c>
       <c r="E374" s="2" t="s">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
@@ -9162,14 +9181,16 @@
         <v>516</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D375" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="D375" s="2">
+        <v>1</v>
+      </c>
       <c r="E375" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.35">
@@ -9180,14 +9201,16 @@
         <v>516</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="D376" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D376" s="2">
+        <v>1</v>
+      </c>
       <c r="E376" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.35">
@@ -9198,14 +9221,14 @@
         <v>516</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>593</v>
+        <v>104</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>578</v>
+        <v>520</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -9216,14 +9239,14 @@
         <v>516</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" s="2" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.35">
@@ -9234,14 +9257,14 @@
         <v>516</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>591</v>
+        <v>563</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.35">
@@ -9252,14 +9275,14 @@
         <v>516</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>590</v>
+        <v>558</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.35">
@@ -9270,7 +9293,7 @@
         <v>516</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" s="2" t="s">
@@ -9288,14 +9311,14 @@
         <v>516</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.35">
@@ -9306,14 +9329,14 @@
         <v>516</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>538</v>
+        <v>591</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>539</v>
+        <v>578</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.35">
@@ -9324,14 +9347,14 @@
         <v>516</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>541</v>
+        <v>590</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>542</v>
+        <v>576</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
@@ -9342,14 +9365,14 @@
         <v>516</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>94</v>
+        <v>592</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>514</v>
+        <v>578</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.35">
@@ -9357,17 +9380,17 @@
         <v>162</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C386" s="2"/>
-      <c r="D386" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D386" s="2"/>
       <c r="E386" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>549</v>
+        <v>571</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.35">
@@ -9375,17 +9398,17 @@
         <v>162</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C387" s="2"/>
-      <c r="D387" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D387" s="2"/>
       <c r="E387" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.35">
@@ -9393,19 +9416,17 @@
         <v>162</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="D388" s="2">
-        <v>1</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="D388" s="2"/>
       <c r="E388" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
@@ -9413,19 +9434,17 @@
         <v>162</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D389" s="2">
-        <v>1</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D389" s="2"/>
       <c r="E389" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.35">
@@ -9433,19 +9452,17 @@
         <v>162</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C390" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D390" s="2">
-        <v>1</v>
+        <v>548</v>
+      </c>
+      <c r="C390" s="2"/>
+      <c r="D390" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>520</v>
+        <v>549</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.35">
@@ -9455,17 +9472,15 @@
       <c r="B391" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C391" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D391" s="2">
-        <v>1</v>
+      <c r="C391" s="2"/>
+      <c r="D391" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>536</v>
+        <v>514</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.35">
@@ -9476,16 +9491,16 @@
         <v>513</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="D392" s="2">
         <v>1</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.35">
@@ -9493,17 +9508,19 @@
         <v>162</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C393" s="2"/>
-      <c r="D393" s="2" t="s">
-        <v>144</v>
+        <v>513</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D393" s="2">
+        <v>1</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>564</v>
+        <v>519</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.35">
@@ -9511,19 +9528,19 @@
         <v>162</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>565</v>
+        <v>513</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>301</v>
+        <v>100</v>
       </c>
       <c r="D394" s="2">
         <v>1</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>567</v>
+        <v>520</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.35">
@@ -9531,19 +9548,19 @@
         <v>162</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>565</v>
+        <v>513</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>568</v>
+        <v>135</v>
       </c>
       <c r="D395" s="2">
         <v>1</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>567</v>
+        <v>536</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.35">
@@ -9551,17 +9568,19 @@
         <v>162</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="C396" s="2"/>
-      <c r="D396" s="2" t="s">
-        <v>128</v>
+        <v>513</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D396" s="2">
+        <v>1</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.35">
@@ -9569,17 +9588,17 @@
         <v>162</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C397" s="2"/>
       <c r="D397" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.35">
@@ -9587,19 +9606,19 @@
         <v>162</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>573</v>
+        <v>301</v>
       </c>
       <c r="D398" s="2">
         <v>1</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.35">
@@ -9607,17 +9626,19 @@
         <v>162</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D399" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="D399" s="2">
+        <v>1</v>
+      </c>
       <c r="E399" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.35">
@@ -9625,17 +9646,17 @@
         <v>162</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.35">
@@ -9643,17 +9664,17 @@
         <v>162</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C401" s="2"/>
       <c r="D401" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.35">
@@ -9661,17 +9682,19 @@
         <v>162</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C402" s="2"/>
-      <c r="D402" s="2" t="s">
-        <v>128</v>
+        <v>572</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D402" s="2">
+        <v>1</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.35">
@@ -9679,17 +9702,17 @@
         <v>162</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="C403" s="2"/>
-      <c r="D403" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D403" s="2"/>
       <c r="E403" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>549</v>
+        <v>584</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
@@ -9697,17 +9720,17 @@
         <v>162</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
@@ -9715,17 +9738,17 @@
         <v>162</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="D405" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="C405" s="2"/>
+      <c r="D405" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E405" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F405" s="2" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.35">
@@ -9733,17 +9756,17 @@
         <v>162</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C406" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D406" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C406" s="2"/>
+      <c r="D406" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E406" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.35">
@@ -9751,7 +9774,7 @@
         <v>162</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C407" s="2"/>
       <c r="D407" s="2" t="s">
@@ -9761,7 +9784,7 @@
         <v>537</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.35">
@@ -9769,17 +9792,17 @@
         <v>162</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
@@ -9787,17 +9810,17 @@
         <v>162</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="C409" s="2"/>
-      <c r="D409" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D409" s="2"/>
       <c r="E409" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.35">
@@ -9805,17 +9828,17 @@
         <v>162</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C410" s="2"/>
-      <c r="D410" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D410" s="2"/>
       <c r="E410" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>279</v>
+        <v>547</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.35">
@@ -9823,19 +9846,17 @@
         <v>162</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C411" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D411" s="2">
-        <v>1</v>
+        <v>545</v>
+      </c>
+      <c r="C411" s="2"/>
+      <c r="D411" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>282</v>
+        <v>547</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.35">
@@ -9843,17 +9864,17 @@
         <v>162</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C412" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D412" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="C412" s="2"/>
+      <c r="D412" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E412" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>378</v>
+        <v>547</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.35">
@@ -9861,17 +9882,17 @@
         <v>162</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C413" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D413" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="C413" s="2"/>
+      <c r="D413" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E413" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>295</v>
+        <v>514</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
@@ -9881,15 +9902,15 @@
       <c r="B414" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C414" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D414" s="2"/>
+      <c r="C414" s="2"/>
+      <c r="D414" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E414" s="2" t="s">
-        <v>481</v>
+        <v>269</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>64</v>
+        <v>279</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
@@ -9900,14 +9921,16 @@
         <v>275</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D415" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="D415" s="2">
+        <v>1</v>
+      </c>
       <c r="E415" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.35">
@@ -9918,14 +9941,14 @@
         <v>275</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>278</v>
+        <v>487</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>294</v>
+        <v>378</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.35">
@@ -9936,14 +9959,14 @@
         <v>275</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>488</v>
+        <v>277</v>
       </c>
       <c r="D417" s="2"/>
       <c r="E417" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>489</v>
+        <v>295</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.35">
@@ -9951,17 +9974,17 @@
         <v>162</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C418" s="2"/>
-      <c r="D418" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D418" s="2"/>
       <c r="E418" s="2" t="s">
-        <v>269</v>
+        <v>481</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>270</v>
+        <v>64</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.35">
@@ -9969,19 +9992,17 @@
         <v>162</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D419" s="2">
-        <v>1</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="D419" s="2"/>
       <c r="E419" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.35">
@@ -9989,19 +10010,17 @@
         <v>162</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D420" s="2">
-        <v>1</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="D420" s="2"/>
       <c r="E420" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
@@ -10009,17 +10028,17 @@
         <v>162</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C421" s="2"/>
-      <c r="D421" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D421" s="2"/>
       <c r="E421" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F421" s="2" t="s">
-        <v>279</v>
+        <v>489</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.35">
@@ -10027,39 +10046,37 @@
         <v>162</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C422" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D422" s="2">
-        <v>1</v>
+        <v>271</v>
+      </c>
+      <c r="C422" s="2"/>
+      <c r="D422" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>198</v>
+        <v>270</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A423" t="s">
+      <c r="A423" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C423" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D423" s="1">
+        <v>271</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D423" s="2">
         <v>1</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>52</v>
+        <v>269</v>
       </c>
       <c r="F423" s="2" t="s">
-        <v>54</v>
+        <v>273</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.35">
@@ -10067,19 +10084,19 @@
         <v>162</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C424" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D424" s="1">
+        <v>271</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D424" s="2">
         <v>1</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.35">
@@ -10087,17 +10104,17 @@
         <v>162</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D425" s="1"/>
+        <v>274</v>
+      </c>
+      <c r="C425" s="2"/>
+      <c r="D425" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E425" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F425" s="2" t="s">
-        <v>194</v>
+        <v>279</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.35">
@@ -10107,33 +10124,37 @@
       <c r="B426" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C426" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D426" s="1"/>
+      <c r="C426" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D426" s="2">
+        <v>1</v>
+      </c>
       <c r="E426" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A427" s="1" t="s">
+      <c r="A427" t="s">
         <v>162</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D427" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="D427" s="1">
+        <v>1</v>
+      </c>
       <c r="E427" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F427" s="2" t="s">
-        <v>206</v>
+        <v>54</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.35">
@@ -10144,14 +10165,16 @@
         <v>56</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D428" s="1"/>
+        <v>204</v>
+      </c>
+      <c r="D428" s="1">
+        <v>1</v>
+      </c>
       <c r="E428" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F428" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.35">
@@ -10161,15 +10184,15 @@
       <c r="B429" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C429" s="2"/>
-      <c r="D429" s="2" t="s">
-        <v>144</v>
-      </c>
+      <c r="C429" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D429" s="1"/>
       <c r="E429" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F429" s="2" t="s">
-        <v>53</v>
+        <v>194</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
@@ -10177,16 +10200,17 @@
         <v>162</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D430" t="s">
-        <v>144</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C430" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D430" s="1"/>
       <c r="E430" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.35">
@@ -10194,16 +10218,17 @@
         <v>162</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C431" t="s">
-        <v>200</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C431" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D431" s="1"/>
       <c r="E431" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.35">
@@ -10211,16 +10236,17 @@
         <v>162</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C432" t="s">
-        <v>94</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D432" s="1"/>
       <c r="E432" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
@@ -10228,24 +10254,25 @@
         <v>162</v>
       </c>
       <c r="B433" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C433" s="2"/>
+      <c r="D433" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E433" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F433" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A434" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B434" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C433" t="s">
-        <v>201</v>
-      </c>
-      <c r="E433" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F433" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A434" t="s">
-        <v>162</v>
-      </c>
-      <c r="B434" t="s">
-        <v>148</v>
       </c>
       <c r="D434" t="s">
         <v>144</v>
@@ -10254,7 +10281,7 @@
         <v>193</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.35">
@@ -10262,19 +10289,16 @@
         <v>162</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="C435" t="s">
-        <v>199</v>
-      </c>
-      <c r="D435">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.35">
@@ -10282,36 +10306,33 @@
         <v>162</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="C436" t="s">
-        <v>204</v>
-      </c>
-      <c r="D436">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A437" t="s">
-        <v>162</v>
-      </c>
-      <c r="B437" t="s">
-        <v>148</v>
+      <c r="A437" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="C437" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F437" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
@@ -10321,8 +10342,8 @@
       <c r="B438" t="s">
         <v>148</v>
       </c>
-      <c r="C438" t="s">
-        <v>196</v>
+      <c r="D438" t="s">
+        <v>144</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>193</v>
@@ -10336,16 +10357,19 @@
         <v>162</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="D439" t="s">
-        <v>144</v>
+        <v>148</v>
+      </c>
+      <c r="C439" t="s">
+        <v>199</v>
+      </c>
+      <c r="D439">
+        <v>2</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
@@ -10353,47 +10377,47 @@
         <v>162</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D440" t="s">
-        <v>144</v>
+        <v>148</v>
+      </c>
+      <c r="C440" t="s">
+        <v>204</v>
+      </c>
+      <c r="D440">
+        <v>2</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A441" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B441" s="1" t="s">
-        <v>192</v>
+      <c r="A441" t="s">
+        <v>162</v>
+      </c>
+      <c r="B441" t="s">
+        <v>148</v>
       </c>
       <c r="C441" t="s">
-        <v>100</v>
-      </c>
-      <c r="D441">
-        <v>1</v>
+        <v>195</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F441" s="2" t="s">
-        <v>54</v>
+        <v>212</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A442" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B442" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D442" t="s">
-        <v>144</v>
+      <c r="A442" t="s">
+        <v>162</v>
+      </c>
+      <c r="B442" t="s">
+        <v>148</v>
+      </c>
+      <c r="C442" t="s">
+        <v>196</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>193</v>
@@ -10407,19 +10431,16 @@
         <v>162</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C443" t="s">
-        <v>199</v>
-      </c>
-      <c r="D443">
-        <v>1</v>
+        <v>450</v>
+      </c>
+      <c r="D443" t="s">
+        <v>144</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.35">
@@ -10427,19 +10448,16 @@
         <v>162</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C444" t="s">
-        <v>204</v>
-      </c>
-      <c r="D444">
-        <v>1</v>
+        <v>192</v>
+      </c>
+      <c r="D444" t="s">
+        <v>144</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.35">
@@ -10447,16 +10465,19 @@
         <v>162</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C445" t="s">
-        <v>449</v>
+        <v>100</v>
+      </c>
+      <c r="D445">
+        <v>1</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>212</v>
+        <v>54</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.35">
@@ -10464,16 +10485,16 @@
         <v>162</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D446" t="s">
         <v>144</v>
       </c>
-      <c r="E446" t="s">
+      <c r="E446" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F446" t="s">
-        <v>206</v>
+      <c r="F446" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.35">
@@ -10481,18 +10502,18 @@
         <v>162</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C447" t="s">
-        <v>100</v>
+        <v>199</v>
       </c>
       <c r="D447">
         <v>1</v>
       </c>
-      <c r="E447" t="s">
+      <c r="E447" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F447" t="s">
+      <c r="F447" s="2" t="s">
         <v>208</v>
       </c>
     </row>
@@ -10501,16 +10522,19 @@
         <v>162</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D448" t="s">
-        <v>144</v>
-      </c>
-      <c r="E448" t="s">
-        <v>374</v>
-      </c>
-      <c r="F448" t="s">
-        <v>376</v>
+        <v>209</v>
+      </c>
+      <c r="C448" t="s">
+        <v>204</v>
+      </c>
+      <c r="D448">
+        <v>1</v>
+      </c>
+      <c r="E448" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F448" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
@@ -10518,16 +10542,16 @@
         <v>162</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="D449" t="s">
-        <v>144</v>
-      </c>
-      <c r="E449" t="s">
-        <v>537</v>
-      </c>
-      <c r="F449" t="s">
-        <v>539</v>
+        <v>209</v>
+      </c>
+      <c r="C449" t="s">
+        <v>449</v>
+      </c>
+      <c r="E449" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F449" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.35">
@@ -10535,16 +10559,16 @@
         <v>162</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="C450" t="s">
-        <v>552</v>
+        <v>207</v>
+      </c>
+      <c r="D450" t="s">
+        <v>144</v>
       </c>
       <c r="E450" t="s">
-        <v>537</v>
+        <v>193</v>
       </c>
       <c r="F450" t="s">
-        <v>549</v>
+        <v>206</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
@@ -10552,16 +10576,19 @@
         <v>162</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>540</v>
+        <v>207</v>
       </c>
       <c r="C451" t="s">
-        <v>553</v>
+        <v>100</v>
+      </c>
+      <c r="D451">
+        <v>1</v>
       </c>
       <c r="E451" t="s">
-        <v>537</v>
+        <v>193</v>
       </c>
       <c r="F451" t="s">
-        <v>549</v>
+        <v>208</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.35">
@@ -10569,16 +10596,16 @@
         <v>162</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="C452" t="s">
-        <v>196</v>
+        <v>373</v>
+      </c>
+      <c r="D452" t="s">
+        <v>144</v>
       </c>
       <c r="E452" t="s">
-        <v>537</v>
+        <v>374</v>
       </c>
       <c r="F452" t="s">
-        <v>549</v>
+        <v>376</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
@@ -10586,16 +10613,16 @@
         <v>162</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>335</v>
+        <v>540</v>
       </c>
       <c r="D453" t="s">
         <v>144</v>
       </c>
       <c r="E453" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F453" t="s">
-        <v>344</v>
+        <v>539</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.35">
@@ -10603,19 +10630,16 @@
         <v>162</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>335</v>
+        <v>540</v>
       </c>
       <c r="C454" t="s">
-        <v>336</v>
-      </c>
-      <c r="D454">
-        <v>1</v>
+        <v>552</v>
       </c>
       <c r="E454" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F454" t="s">
-        <v>337</v>
+        <v>549</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.35">
@@ -10623,19 +10647,16 @@
         <v>162</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>335</v>
+        <v>540</v>
       </c>
       <c r="C455" t="s">
-        <v>102</v>
-      </c>
-      <c r="D455">
-        <v>1</v>
+        <v>553</v>
       </c>
       <c r="E455" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F455" t="s">
-        <v>344</v>
+        <v>549</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.35">
@@ -10643,19 +10664,16 @@
         <v>162</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>335</v>
+        <v>540</v>
       </c>
       <c r="C456" t="s">
-        <v>115</v>
-      </c>
-      <c r="D456">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="E456" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F456" t="s">
-        <v>334</v>
+        <v>549</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
@@ -10665,17 +10683,14 @@
       <c r="B457" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C457" t="s">
-        <v>338</v>
-      </c>
-      <c r="D457">
-        <v>1</v>
+      <c r="D457" t="s">
+        <v>144</v>
       </c>
       <c r="E457" t="s">
         <v>331</v>
       </c>
       <c r="F457" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.35">
@@ -10683,16 +10698,19 @@
         <v>162</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D458" t="s">
-        <v>144</v>
+        <v>335</v>
+      </c>
+      <c r="C458" t="s">
+        <v>336</v>
+      </c>
+      <c r="D458">
+        <v>1</v>
       </c>
       <c r="E458" t="s">
         <v>331</v>
       </c>
       <c r="F458" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.35">
@@ -10700,10 +10718,10 @@
         <v>162</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C459" t="s">
-        <v>340</v>
+        <v>102</v>
       </c>
       <c r="D459">
         <v>1</v>
@@ -10712,7 +10730,7 @@
         <v>331</v>
       </c>
       <c r="F459" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.35">
@@ -10720,10 +10738,10 @@
         <v>162</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C460" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D460">
         <v>1</v>
@@ -10740,10 +10758,10 @@
         <v>162</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C461" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D461">
         <v>1</v>
@@ -10752,7 +10770,7 @@
         <v>331</v>
       </c>
       <c r="F461" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.35">
@@ -10760,16 +10778,16 @@
         <v>162</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>442</v>
+        <v>333</v>
       </c>
       <c r="D462" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E462" t="s">
         <v>331</v>
       </c>
       <c r="F462" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.35">
@@ -10777,16 +10795,19 @@
         <v>162</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D463" t="s">
-        <v>128</v>
+        <v>333</v>
+      </c>
+      <c r="C463" t="s">
+        <v>340</v>
+      </c>
+      <c r="D463">
+        <v>1</v>
       </c>
       <c r="E463" t="s">
-        <v>481</v>
+        <v>331</v>
       </c>
       <c r="F463" t="s">
-        <v>64</v>
+        <v>341</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.35">
@@ -10794,16 +10815,19 @@
         <v>162</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D464" t="s">
-        <v>128</v>
+        <v>333</v>
+      </c>
+      <c r="C464" t="s">
+        <v>100</v>
+      </c>
+      <c r="D464">
+        <v>1</v>
       </c>
       <c r="E464" t="s">
-        <v>193</v>
+        <v>331</v>
       </c>
       <c r="F464" t="s">
-        <v>206</v>
+        <v>334</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
@@ -10811,16 +10835,19 @@
         <v>162</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="D465" t="s">
-        <v>144</v>
+        <v>333</v>
+      </c>
+      <c r="C465" t="s">
+        <v>342</v>
+      </c>
+      <c r="D465">
+        <v>1</v>
       </c>
       <c r="E465" t="s">
-        <v>497</v>
+        <v>331</v>
       </c>
       <c r="F465" t="s">
-        <v>503</v>
+        <v>343</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.35">
@@ -10828,19 +10855,16 @@
         <v>162</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C466" t="s">
-        <v>415</v>
-      </c>
-      <c r="D466">
-        <v>1</v>
+        <v>442</v>
+      </c>
+      <c r="D466" t="s">
+        <v>128</v>
       </c>
       <c r="E466" t="s">
-        <v>532</v>
+        <v>331</v>
       </c>
       <c r="F466" t="s">
-        <v>533</v>
+        <v>344</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.35">
@@ -10848,16 +10872,16 @@
         <v>162</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C467" t="s">
-        <v>506</v>
+        <v>482</v>
+      </c>
+      <c r="D467" t="s">
+        <v>128</v>
       </c>
       <c r="E467" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="F467" t="s">
-        <v>507</v>
+        <v>64</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.35">
@@ -10865,16 +10889,16 @@
         <v>162</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C468" t="s">
-        <v>531</v>
+        <v>232</v>
+      </c>
+      <c r="D468" t="s">
+        <v>128</v>
       </c>
       <c r="E468" t="s">
-        <v>497</v>
+        <v>193</v>
       </c>
       <c r="F468" t="s">
-        <v>527</v>
+        <v>206</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
@@ -10882,16 +10906,16 @@
         <v>162</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="D469" t="s">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="E469" t="s">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="F469" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
@@ -10899,15 +10923,86 @@
         <v>162</v>
       </c>
       <c r="B470" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C470" t="s">
+        <v>415</v>
+      </c>
+      <c r="D470">
+        <v>1</v>
+      </c>
+      <c r="E470" t="s">
+        <v>532</v>
+      </c>
+      <c r="F470" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A471" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C471" t="s">
+        <v>506</v>
+      </c>
+      <c r="E471" t="s">
+        <v>497</v>
+      </c>
+      <c r="F471" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A472" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C472" t="s">
+        <v>531</v>
+      </c>
+      <c r="E472" t="s">
+        <v>497</v>
+      </c>
+      <c r="F472" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A473" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D473" t="s">
+        <v>345</v>
+      </c>
+      <c r="E473" t="s">
+        <v>532</v>
+      </c>
+      <c r="F473" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A474" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B474" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="D470" t="s">
+      <c r="D474" t="s">
         <v>144</v>
       </c>
-      <c r="E470" t="s">
+      <c r="E474" t="s">
         <v>497</v>
       </c>
-      <c r="F470" t="s">
+      <c r="F474" t="s">
         <v>529</v>
       </c>
     </row>

--- a/snippet-extractor-metadata/word.xlsx
+++ b/snippet-extractor-metadata/word.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14863876-029E-4319-A045-C665BA386D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23473AC-1060-41C5-AA4D-116ACC111178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="623">
   <si>
     <t>Class</t>
   </si>
@@ -1859,6 +1859,36 @@
   </si>
   <si>
     <t>SelectionInsertFormulaOptions</t>
+  </si>
+  <si>
+    <t>getNextRange</t>
+  </si>
+  <si>
+    <t>getPreviousRange</t>
+  </si>
+  <si>
+    <t>word-selection-get-previous-next-range</t>
+  </si>
+  <si>
+    <t>SelectionNextOptions</t>
+  </si>
+  <si>
+    <t>SelectionPreviousOptions</t>
+  </si>
+  <si>
+    <t>getNextWord</t>
+  </si>
+  <si>
+    <t>getPreviousSentence</t>
+  </si>
+  <si>
+    <t>getPreviousWord</t>
+  </si>
+  <si>
+    <t>getNextParagraph</t>
+  </si>
+  <si>
+    <t>OperationUnit</t>
   </si>
 </sst>
 </file>
@@ -1907,7 +1937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1918,6 +1948,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1973,8 +2004,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F474" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="A1:F474" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F479" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:F479" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{1DA12987-AB2C-4056-A643-B1229DC856C5}" name="Package" dataDxfId="4"/>
     <tableColumn id="1" xr3:uid="{0CD83AD1-F92A-407D-8460-4E881461FD01}" name="Class" dataDxfId="3"/>
@@ -2284,7 +2315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F474"/>
+  <dimension ref="A1:F479"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25.08984375" bestFit="1" customWidth="1"/>
@@ -6119,14 +6150,14 @@
       <c r="B210" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C210" s="5" t="s">
+      <c r="C210" s="2" t="s">
         <v>605</v>
       </c>
       <c r="D210" s="2"/>
-      <c r="E210" s="5" t="s">
+      <c r="E210" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="F210" s="5" t="s">
+      <c r="F210" s="2" t="s">
         <v>608</v>
       </c>
     </row>
@@ -7413,20 +7444,21 @@
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A281" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>411</v>
-      </c>
+      <c r="A281" t="s">
+        <v>162</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="C281" s="6"/>
       <c r="D281" t="s">
         <v>128</v>
       </c>
-      <c r="E281" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>375</v>
+      <c r="E281" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
@@ -7434,16 +7466,16 @@
         <v>162</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>499</v>
+        <v>411</v>
       </c>
       <c r="D282" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>497</v>
+        <v>374</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>498</v>
+        <v>375</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.35">
@@ -7453,11 +7485,8 @@
       <c r="B283" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C283" t="s">
-        <v>115</v>
-      </c>
-      <c r="D283">
-        <v>1</v>
+      <c r="D283" t="s">
+        <v>144</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>497</v>
@@ -7474,13 +7503,16 @@
         <v>499</v>
       </c>
       <c r="C284" t="s">
-        <v>500</v>
+        <v>115</v>
+      </c>
+      <c r="D284">
+        <v>1</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.35">
@@ -7488,16 +7520,16 @@
         <v>162</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="D285" t="s">
-        <v>144</v>
+        <v>499</v>
+      </c>
+      <c r="C285" t="s">
+        <v>500</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
@@ -7505,7 +7537,7 @@
         <v>162</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="D286" t="s">
         <v>144</v>
@@ -7514,7 +7546,7 @@
         <v>497</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.35">
@@ -7524,8 +7556,8 @@
       <c r="B287" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C287" t="s">
-        <v>508</v>
+      <c r="D287" t="s">
+        <v>144</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>497</v>
@@ -7542,13 +7574,13 @@
         <v>504</v>
       </c>
       <c r="C288" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.35">
@@ -7556,34 +7588,33 @@
         <v>162</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="D289" t="s">
-        <v>144</v>
+        <v>504</v>
+      </c>
+      <c r="C289" t="s">
+        <v>509</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F289" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A290" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D290" t="s">
+        <v>144</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>527</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A290" t="s">
-        <v>162</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C290" s="2"/>
-      <c r="D290" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E290" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.35">
@@ -7593,77 +7624,75 @@
       <c r="B291" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C291" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D291" s="2">
-        <v>1</v>
+      <c r="C291" s="2"/>
+      <c r="D291" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A292" s="1" t="s">
+      <c r="A292" t="s">
         <v>162</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>360</v>
+        <v>115</v>
       </c>
       <c r="D292" s="2">
         <v>1</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>360</v>
+        <v>12</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A293" t="s">
+      <c r="A293" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>29</v>
+        <v>360</v>
       </c>
       <c r="D293" s="2">
         <v>1</v>
       </c>
-      <c r="E293" s="2" t="s">
-        <v>75</v>
+      <c r="E293" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>28</v>
+        <v>360</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A294" s="1" t="s">
+      <c r="A294" t="s">
         <v>162</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D294" s="2">
         <v>1</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.35">
@@ -7674,36 +7703,36 @@
         <v>10</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>556</v>
+        <v>36</v>
       </c>
       <c r="D295" s="2">
         <v>1</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>570</v>
+        <v>43</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A296" t="s">
+      <c r="A296" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>13</v>
+        <v>556</v>
       </c>
       <c r="D296" s="2">
         <v>1</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.35">
@@ -7714,16 +7743,16 @@
         <v>10</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>512</v>
+        <v>13</v>
       </c>
       <c r="D297" s="2">
         <v>1</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>537</v>
+        <v>81</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>523</v>
+        <v>22</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
@@ -7734,16 +7763,16 @@
         <v>10</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>48</v>
+        <v>512</v>
       </c>
       <c r="D298" s="2">
         <v>1</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>71</v>
+        <v>537</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>47</v>
+        <v>523</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.35">
@@ -7763,7 +7792,7 @@
         <v>71</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.35">
@@ -7773,17 +7802,17 @@
       <c r="B300" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C300" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D300" s="1">
+      <c r="C300" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D300" s="2">
         <v>1</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.35">
@@ -7793,17 +7822,17 @@
       <c r="B301" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C301" s="2" t="s">
+      <c r="C301" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D301" s="2">
+      <c r="D301" s="1">
         <v>1</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
@@ -7814,16 +7843,16 @@
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="D302" s="2">
         <v>1</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.35">
@@ -7834,16 +7863,16 @@
         <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D303" s="2">
         <v>1</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.35">
@@ -7854,14 +7883,16 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D304" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D304" s="2">
+        <v>1</v>
+      </c>
       <c r="E304" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.35">
@@ -7872,14 +7903,14 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
@@ -7890,86 +7921,86 @@
         <v>10</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A307" s="1" t="s">
+      <c r="A307" t="s">
         <v>162</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A308" s="3" t="s">
+      <c r="A308" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A309" t="s">
+      <c r="A309" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>17</v>
+        <v>381</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>17</v>
+        <v>382</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A310" s="1" t="s">
+      <c r="A310" t="s">
         <v>162</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>280</v>
+        <v>17</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" s="2" t="s">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>279</v>
+        <v>17</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.35">
@@ -7980,32 +8011,32 @@
         <v>10</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" s="2" t="s">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A312" t="s">
+      <c r="A312" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>8</v>
+        <v>238</v>
       </c>
       <c r="D312" s="2"/>
-      <c r="E312" s="1" t="s">
-        <v>79</v>
+      <c r="E312" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>11</v>
+        <v>240</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.35">
@@ -8016,14 +8047,14 @@
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" s="1" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.35">
@@ -8041,25 +8072,25 @@
         <v>350</v>
       </c>
       <c r="F314" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>162</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D315" s="2"/>
+      <c r="E315" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F315" s="2" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A315" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C315" s="2"/>
-      <c r="D315" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E315" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F315" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
@@ -8077,7 +8108,7 @@
         <v>318</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>319</v>
+        <v>267</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
@@ -8085,17 +8116,17 @@
         <v>162</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" s="2" t="s">
         <v>345</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>267</v>
+        <v>319</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.35">
@@ -8113,65 +8144,63 @@
         <v>322</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A319" t="s">
+      <c r="A319" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>190</v>
+        <v>329</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E319" s="2" t="s">
-        <v>70</v>
+        <v>345</v>
+      </c>
+      <c r="E319" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>175</v>
+        <v>324</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A320" s="1" t="s">
+      <c r="A320" t="s">
         <v>162</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C320" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D320" s="2">
-        <v>1</v>
-      </c>
-      <c r="E320" s="1" t="s">
-        <v>350</v>
+      <c r="C320" s="2"/>
+      <c r="D320" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>353</v>
+        <v>175</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A321" t="s">
+      <c r="A321" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="D321" s="2">
         <v>1</v>
       </c>
-      <c r="E321" s="2" t="s">
-        <v>70</v>
+      <c r="E321" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>175</v>
+        <v>353</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.35">
@@ -8182,14 +8211,16 @@
         <v>190</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D322" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="D322" s="2">
+        <v>1</v>
+      </c>
       <c r="E322" s="2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
@@ -8197,17 +8228,17 @@
         <v>162</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C323" s="2"/>
-      <c r="D323" s="2" t="s">
-        <v>345</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D323" s="2"/>
       <c r="E323" s="2" t="s">
-        <v>323</v>
+        <v>57</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>267</v>
+        <v>58</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
@@ -8225,25 +8256,25 @@
         <v>323</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>325</v>
+        <v>267</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A325" s="1" t="s">
+      <c r="A325" t="s">
         <v>162</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
@@ -8253,10 +8284,10 @@
       <c r="B326" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C326" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D326" s="2"/>
+      <c r="C326" s="2"/>
+      <c r="D326" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E326" s="2" t="s">
         <v>269</v>
       </c>
@@ -8272,7 +8303,7 @@
         <v>281</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" s="2" t="s">
@@ -8287,17 +8318,17 @@
         <v>162</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C328" s="2"/>
-      <c r="D328" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D328" s="2"/>
       <c r="E328" s="2" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>445</v>
+        <v>294</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -8307,17 +8338,15 @@
       <c r="B329" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C329" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D329" s="2">
-        <v>1</v>
+      <c r="C329" s="2"/>
+      <c r="D329" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>228</v>
+        <v>445</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
@@ -8328,36 +8357,36 @@
         <v>5</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>492</v>
+        <v>229</v>
       </c>
       <c r="D330" s="2">
         <v>1</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>12</v>
+        <v>228</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A331" t="s">
+      <c r="A331" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C331" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D331" s="1">
+      <c r="C331" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D331" s="2">
         <v>1</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
@@ -8368,16 +8397,16 @@
         <v>5</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>395</v>
+        <v>107</v>
       </c>
       <c r="D332" s="1">
         <v>1</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>393</v>
+        <v>145</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>427</v>
+        <v>108</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.35">
@@ -8388,16 +8417,16 @@
         <v>5</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>115</v>
+        <v>395</v>
       </c>
       <c r="D333" s="1">
         <v>1</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>494</v>
+        <v>393</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.35">
@@ -8408,16 +8437,16 @@
         <v>5</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D334" s="1">
         <v>1</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>147</v>
+        <v>494</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>121</v>
+        <v>462</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
@@ -8428,16 +8457,16 @@
         <v>5</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="D335" s="1">
         <v>1</v>
       </c>
-      <c r="E335" s="1" t="s">
-        <v>79</v>
+      <c r="E335" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
@@ -8448,16 +8477,16 @@
         <v>5</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="D336" s="1">
         <v>1</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
@@ -8468,56 +8497,56 @@
         <v>5</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="D337" s="1">
         <v>1</v>
       </c>
-      <c r="E337" s="2" t="s">
-        <v>82</v>
+      <c r="E337" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A338" s="1" t="s">
+      <c r="A338" t="s">
         <v>162</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>283</v>
+        <v>36</v>
       </c>
       <c r="D338" s="1">
         <v>1</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>284</v>
+        <v>35</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A339" t="s">
+      <c r="A339" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>88</v>
+        <v>283</v>
       </c>
       <c r="D339" s="1">
         <v>1</v>
       </c>
-      <c r="E339" s="1" t="s">
-        <v>146</v>
+      <c r="E339" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>88</v>
+        <v>284</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
@@ -8528,16 +8557,16 @@
         <v>5</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>313</v>
+        <v>88</v>
       </c>
       <c r="D340" s="1">
         <v>1</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>537</v>
+        <v>146</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>521</v>
+        <v>88</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.35">
@@ -8557,7 +8586,7 @@
         <v>537</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.35">
@@ -8568,16 +8597,16 @@
         <v>5</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>556</v>
+        <v>313</v>
       </c>
       <c r="D342" s="1">
         <v>1</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.35">
@@ -8588,16 +8617,16 @@
         <v>5</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>512</v>
+        <v>556</v>
       </c>
       <c r="D343" s="1">
         <v>1</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>511</v>
+        <v>561</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.35">
@@ -8608,31 +8637,34 @@
         <v>5</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D344" s="1"/>
+        <v>512</v>
+      </c>
+      <c r="D344" s="1">
+        <v>1</v>
+      </c>
       <c r="E344" s="1" t="s">
-        <v>146</v>
+        <v>537</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>96</v>
+        <v>511</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A345" s="1" t="s">
+      <c r="A345" t="s">
         <v>162</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C345" t="s">
-        <v>428</v>
-      </c>
-      <c r="E345" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F345" t="s">
-        <v>422</v>
+      <c r="C345" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D345" s="1"/>
+      <c r="E345" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F345" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.35">
@@ -8642,15 +8674,14 @@
       <c r="B346" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C346" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D346" s="2"/>
+      <c r="C346" t="s">
+        <v>428</v>
+      </c>
       <c r="E346" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F346" s="2" t="s">
-        <v>239</v>
+        <v>393</v>
+      </c>
+      <c r="F346" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
@@ -8658,53 +8689,53 @@
         <v>162</v>
       </c>
       <c r="B347" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D347" s="2"/>
+      <c r="E347" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F347" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A348" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C347" s="2"/>
-      <c r="D347" s="2" t="s">
+      <c r="C348" s="2"/>
+      <c r="D348" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E347" s="2" t="s">
+      <c r="E348" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F347" s="2" t="s">
+      <c r="F348" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A348" t="s">
-        <v>162</v>
-      </c>
-      <c r="B348" s="1" t="s">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>162</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C348" s="1"/>
-      <c r="D348" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E348" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F348" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A349" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B349" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="C349" s="1"/>
       <c r="D349" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>570</v>
+        <v>79</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>576</v>
+        <v>12</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
@@ -8712,7 +8743,7 @@
         <v>162</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C350" s="1"/>
       <c r="D350" s="1" t="s">
@@ -8722,7 +8753,7 @@
         <v>570</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
@@ -8730,7 +8761,7 @@
         <v>162</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C351" s="1"/>
       <c r="D351" s="1" t="s">
@@ -8740,7 +8771,7 @@
         <v>570</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
@@ -8748,17 +8779,17 @@
         <v>162</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>418</v>
+        <v>579</v>
       </c>
       <c r="C352" s="1"/>
       <c r="D352" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>413</v>
+        <v>570</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>414</v>
+        <v>576</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.35">
@@ -8766,37 +8797,35 @@
         <v>162</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>534</v>
+        <v>418</v>
       </c>
       <c r="C353" s="1"/>
       <c r="D353" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E353" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F353" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A354" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E354" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F353" s="2" t="s">
+      <c r="F354" s="2" t="s">
         <v>533</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A354" t="s">
-        <v>162</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D354" s="2">
-        <v>2</v>
-      </c>
-      <c r="E354" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F354" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.35">
@@ -8806,17 +8835,17 @@
       <c r="B355" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C355" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D355" s="1">
-        <v>1</v>
+      <c r="C355" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D355" s="2">
+        <v>2</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
@@ -8826,15 +8855,17 @@
       <c r="B356" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C356" s="1"/>
-      <c r="D356" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E356" s="1" t="s">
-        <v>140</v>
+      <c r="C356" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D356" s="1">
+        <v>1</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.35">
@@ -8842,73 +8873,73 @@
         <v>162</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C357" s="2"/>
-      <c r="D357" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C357" s="1"/>
+      <c r="D357" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E357" s="2" t="s">
+      <c r="E357" s="1" t="s">
         <v>140</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>162</v>
       </c>
-      <c r="B358" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="C358" s="5"/>
+      <c r="B358" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C358" s="2"/>
       <c r="D358" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E358" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="F358" s="5" t="s">
-        <v>608</v>
+      <c r="E358" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F358" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>162</v>
       </c>
-      <c r="B359" s="4" t="s">
+      <c r="B359" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C359" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="D359" s="2">
-        <v>1</v>
-      </c>
-      <c r="E359" s="5" t="s">
+      <c r="C359" s="2"/>
+      <c r="D359" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E359" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="F359" s="5" t="s">
-        <v>607</v>
+      <c r="F359" s="2" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>162</v>
       </c>
-      <c r="B360" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="C360" s="5"/>
-      <c r="D360" s="2" t="s">
-        <v>345</v>
+      <c r="B360" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="D360" s="2">
+        <v>1</v>
       </c>
       <c r="E360" s="5" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.35">
@@ -8916,109 +8947,111 @@
         <v>162</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C361" s="2"/>
-      <c r="D361" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E361" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F361" s="2" t="s">
-        <v>49</v>
+        <v>609</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="D361" s="2">
+        <v>1</v>
+      </c>
+      <c r="E361" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F361" s="5" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A362" s="1" t="s">
+      <c r="A362" t="s">
         <v>162</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C362" s="2"/>
-      <c r="D362" s="2" t="s">
-        <v>144</v>
+        <v>609</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D362" s="2">
+        <v>1</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>164</v>
+        <v>606</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>168</v>
+        <v>607</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A363" s="1" t="s">
+      <c r="A363" t="s">
         <v>162</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C363" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D363" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="C363" s="2"/>
+      <c r="D363" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="E363" s="2" t="s">
-        <v>164</v>
+        <v>606</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>168</v>
+        <v>611</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B364" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D364" s="2"/>
-      <c r="E364" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F364" s="2" t="s">
-        <v>168</v>
+      <c r="B364" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="C364" s="5"/>
+      <c r="D364" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E364" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F364" s="5" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B365" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C365" s="2"/>
+      <c r="B365" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="C365" s="5"/>
       <c r="D365" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E365" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F365" s="2" t="s">
-        <v>166</v>
+        <v>345</v>
+      </c>
+      <c r="E365" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F365" s="5" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A366" s="1" t="s">
+      <c r="A366" t="s">
         <v>162</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C366" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D366" s="2">
-        <v>1</v>
+        <v>159</v>
+      </c>
+      <c r="C366" s="2"/>
+      <c r="D366" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>164</v>
+        <v>71</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>168</v>
+        <v>49</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.35">
@@ -9026,17 +9059,17 @@
         <v>162</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D367" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="C367" s="2"/>
+      <c r="D367" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E367" s="2" t="s">
         <v>164</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
@@ -9044,17 +9077,17 @@
         <v>162</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C368" s="2"/>
-      <c r="D368" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D368" s="2"/>
       <c r="E368" s="2" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>489</v>
+        <v>168</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
@@ -9062,17 +9095,17 @@
         <v>162</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C369" s="2"/>
-      <c r="D369" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D369" s="2"/>
       <c r="E369" s="2" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>489</v>
+        <v>168</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.35">
@@ -9080,17 +9113,17 @@
         <v>162</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>516</v>
+        <v>167</v>
       </c>
       <c r="C370" s="2"/>
       <c r="D370" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>537</v>
+        <v>164</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>519</v>
+        <v>166</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
@@ -9098,19 +9131,19 @@
         <v>162</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>516</v>
+        <v>167</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="D371" s="2">
         <v>1</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>537</v>
+        <v>164</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>522</v>
+        <v>168</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.35">
@@ -9118,19 +9151,17 @@
         <v>162</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>516</v>
+        <v>167</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="D372" s="2">
-        <v>1</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D372" s="2"/>
       <c r="E372" s="2" t="s">
-        <v>570</v>
+        <v>164</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>584</v>
+        <v>169</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
@@ -9138,19 +9169,17 @@
         <v>162</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C373" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D373" s="2">
-        <v>1</v>
+        <v>491</v>
+      </c>
+      <c r="C373" s="2"/>
+      <c r="D373" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>570</v>
+        <v>269</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>584</v>
+        <v>489</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.35">
@@ -9158,19 +9187,17 @@
         <v>162</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C374" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="D374" s="2">
-        <v>1</v>
+        <v>490</v>
+      </c>
+      <c r="C374" s="2"/>
+      <c r="D374" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>570</v>
+        <v>269</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>581</v>
+        <v>489</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
@@ -9180,17 +9207,15 @@
       <c r="B375" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C375" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="D375" s="2">
-        <v>1</v>
+      <c r="C375" s="2"/>
+      <c r="D375" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>581</v>
+        <v>519</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.35">
@@ -9201,16 +9226,16 @@
         <v>516</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D376" s="2">
         <v>1</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>571</v>
+        <v>522</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.35">
@@ -9221,14 +9246,16 @@
         <v>516</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D377" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="D377" s="2">
+        <v>1</v>
+      </c>
       <c r="E377" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>520</v>
+        <v>584</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -9239,14 +9266,16 @@
         <v>516</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D378" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="D378" s="2">
+        <v>1</v>
+      </c>
       <c r="E378" s="2" t="s">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.35">
@@ -9257,14 +9286,16 @@
         <v>516</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D379" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="D379" s="2">
+        <v>1</v>
+      </c>
       <c r="E379" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.35">
@@ -9275,14 +9306,16 @@
         <v>516</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="D380" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="D380" s="2">
+        <v>1</v>
+      </c>
       <c r="E380" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>559</v>
+        <v>581</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.35">
@@ -9293,14 +9326,16 @@
         <v>516</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="D381" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D381" s="2">
+        <v>1</v>
+      </c>
       <c r="E381" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.35">
@@ -9311,14 +9346,14 @@
         <v>516</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>589</v>
+        <v>104</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>576</v>
+        <v>520</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.35">
@@ -9329,14 +9364,14 @@
         <v>516</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" s="2" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.35">
@@ -9347,14 +9382,14 @@
         <v>516</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
@@ -9365,14 +9400,14 @@
         <v>516</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>592</v>
+        <v>558</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.35">
@@ -9383,14 +9418,14 @@
         <v>516</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.35">
@@ -9401,14 +9436,14 @@
         <v>516</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>538</v>
+        <v>589</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.35">
@@ -9419,14 +9454,14 @@
         <v>516</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>541</v>
+        <v>591</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>542</v>
+        <v>578</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
@@ -9437,14 +9472,14 @@
         <v>516</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>94</v>
+        <v>590</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>514</v>
+        <v>576</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.35">
@@ -9452,17 +9487,17 @@
         <v>162</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C390" s="2"/>
-      <c r="D390" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D390" s="2"/>
       <c r="E390" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>549</v>
+        <v>578</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.35">
@@ -9470,17 +9505,17 @@
         <v>162</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C391" s="2"/>
-      <c r="D391" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D391" s="2"/>
       <c r="E391" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>514</v>
+        <v>571</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.35">
@@ -9488,19 +9523,17 @@
         <v>162</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="D392" s="2">
-        <v>1</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="D392" s="2"/>
       <c r="E392" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>562</v>
+        <v>539</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.35">
@@ -9508,19 +9541,17 @@
         <v>162</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D393" s="2">
-        <v>1</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="D393" s="2"/>
       <c r="E393" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>519</v>
+        <v>542</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.35">
@@ -9528,19 +9559,17 @@
         <v>162</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D394" s="2">
-        <v>1</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D394" s="2"/>
       <c r="E394" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.35">
@@ -9548,19 +9577,17 @@
         <v>162</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C395" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D395" s="2">
-        <v>1</v>
+        <v>548</v>
+      </c>
+      <c r="C395" s="2"/>
+      <c r="D395" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.35">
@@ -9570,17 +9597,15 @@
       <c r="B396" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C396" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="D396" s="2">
-        <v>1</v>
+      <c r="C396" s="2"/>
+      <c r="D396" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>571</v>
+        <v>514</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.35">
@@ -9588,17 +9613,19 @@
         <v>162</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C397" s="2"/>
-      <c r="D397" s="2" t="s">
-        <v>144</v>
+        <v>513</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D397" s="2">
+        <v>1</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>555</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.35">
@@ -9606,19 +9633,19 @@
         <v>162</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>565</v>
+        <v>513</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>301</v>
+        <v>518</v>
       </c>
       <c r="D398" s="2">
         <v>1</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>567</v>
+        <v>519</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.35">
@@ -9626,19 +9653,19 @@
         <v>162</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>565</v>
+        <v>513</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>568</v>
+        <v>100</v>
       </c>
       <c r="D399" s="2">
         <v>1</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>567</v>
+        <v>520</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.35">
@@ -9646,17 +9673,19 @@
         <v>162</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="C400" s="2"/>
-      <c r="D400" s="2" t="s">
-        <v>128</v>
+        <v>513</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D400" s="2">
+        <v>1</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.35">
@@ -9664,11 +9693,13 @@
         <v>162</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C401" s="2"/>
-      <c r="D401" s="2" t="s">
-        <v>144</v>
+        <v>513</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D401" s="2">
+        <v>1</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>570</v>
@@ -9682,19 +9713,17 @@
         <v>162</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C402" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="D402" s="2">
-        <v>1</v>
+        <v>565</v>
+      </c>
+      <c r="C402" s="2"/>
+      <c r="D402" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.35">
@@ -9702,17 +9731,19 @@
         <v>162</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D403" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="D403" s="2">
+        <v>1</v>
+      </c>
       <c r="E403" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
@@ -9720,17 +9751,19 @@
         <v>162</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="C404" s="2"/>
-      <c r="D404" s="2" t="s">
-        <v>128</v>
+        <v>565</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D404" s="2">
+        <v>1</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
@@ -9738,17 +9771,17 @@
         <v>162</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F405" s="2" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.35">
@@ -9756,17 +9789,17 @@
         <v>162</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="C406" s="2"/>
       <c r="D406" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>549</v>
+        <v>571</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.35">
@@ -9774,17 +9807,19 @@
         <v>162</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="C407" s="2"/>
-      <c r="D407" s="2" t="s">
-        <v>128</v>
+        <v>572</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D407" s="2">
+        <v>1</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.35">
@@ -9792,17 +9827,17 @@
         <v>162</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C408" s="2"/>
-      <c r="D408" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D408" s="2"/>
       <c r="E408" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>542</v>
+        <v>584</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
@@ -9810,17 +9845,17 @@
         <v>162</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C409" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="D409" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="C409" s="2"/>
+      <c r="D409" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E409" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.35">
@@ -9828,17 +9863,17 @@
         <v>162</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C410" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D410" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="C410" s="2"/>
+      <c r="D410" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E410" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.35">
@@ -9846,7 +9881,7 @@
         <v>162</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C411" s="2"/>
       <c r="D411" s="2" t="s">
@@ -9856,7 +9891,7 @@
         <v>537</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.35">
@@ -9864,7 +9899,7 @@
         <v>162</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C412" s="2"/>
       <c r="D412" s="2" t="s">
@@ -9874,7 +9909,7 @@
         <v>537</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.35">
@@ -9882,17 +9917,17 @@
         <v>162</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="C413" s="2"/>
       <c r="D413" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
@@ -9900,17 +9935,17 @@
         <v>162</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C414" s="2"/>
-      <c r="D414" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C414" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D414" s="2"/>
       <c r="E414" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>279</v>
+        <v>547</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
@@ -9918,19 +9953,17 @@
         <v>162</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>275</v>
+        <v>543</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D415" s="2">
-        <v>1</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D415" s="2"/>
       <c r="E415" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>282</v>
+        <v>547</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.35">
@@ -9938,17 +9971,17 @@
         <v>162</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C416" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D416" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="C416" s="2"/>
+      <c r="D416" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E416" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>378</v>
+        <v>547</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.35">
@@ -9956,17 +9989,17 @@
         <v>162</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C417" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D417" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="C417" s="2"/>
+      <c r="D417" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E417" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>295</v>
+        <v>547</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.35">
@@ -9974,17 +10007,17 @@
         <v>162</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C418" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D418" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="C418" s="2"/>
+      <c r="D418" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E418" s="2" t="s">
-        <v>481</v>
+        <v>537</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>64</v>
+        <v>514</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.35">
@@ -9994,10 +10027,10 @@
       <c r="B419" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C419" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D419" s="2"/>
+      <c r="C419" s="2"/>
+      <c r="D419" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E419" s="2" t="s">
         <v>269</v>
       </c>
@@ -10013,14 +10046,16 @@
         <v>275</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D420" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="D420" s="2">
+        <v>1</v>
+      </c>
       <c r="E420" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
@@ -10031,14 +10066,14 @@
         <v>275</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F421" s="2" t="s">
-        <v>489</v>
+        <v>378</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.35">
@@ -10046,17 +10081,17 @@
         <v>162</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C422" s="2"/>
-      <c r="D422" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D422" s="2"/>
       <c r="E422" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.35">
@@ -10064,19 +10099,17 @@
         <v>162</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D423" s="2">
-        <v>1</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="D423" s="2"/>
       <c r="E423" s="2" t="s">
-        <v>269</v>
+        <v>481</v>
       </c>
       <c r="F423" s="2" t="s">
-        <v>273</v>
+        <v>64</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.35">
@@ -10084,19 +10117,17 @@
         <v>162</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D424" s="2">
-        <v>1</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="D424" s="2"/>
       <c r="E424" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.35">
@@ -10104,17 +10135,17 @@
         <v>162</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C425" s="2"/>
-      <c r="D425" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D425" s="2"/>
       <c r="E425" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F425" s="2" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.35">
@@ -10122,39 +10153,35 @@
         <v>162</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>56</v>
+        <v>275</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D426" s="2">
-        <v>1</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="D426" s="2"/>
       <c r="E426" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>198</v>
+        <v>489</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A427" t="s">
+      <c r="A427" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C427" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D427" s="1">
-        <v>1</v>
+        <v>271</v>
+      </c>
+      <c r="C427" s="2"/>
+      <c r="D427" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>52</v>
+        <v>269</v>
       </c>
       <c r="F427" s="2" t="s">
-        <v>54</v>
+        <v>270</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.35">
@@ -10162,19 +10189,19 @@
         <v>162</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D428" s="1">
+        <v>271</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D428" s="2">
         <v>1</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F428" s="2" t="s">
-        <v>203</v>
+        <v>273</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.35">
@@ -10182,17 +10209,19 @@
         <v>162</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C429" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D429" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D429" s="2">
+        <v>1</v>
+      </c>
       <c r="E429" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F429" s="2" t="s">
-        <v>194</v>
+        <v>270</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
@@ -10200,17 +10229,17 @@
         <v>162</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D430" s="1"/>
+        <v>274</v>
+      </c>
+      <c r="C430" s="2"/>
+      <c r="D430" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E430" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>194</v>
+        <v>279</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.35">
@@ -10220,33 +10249,37 @@
       <c r="B431" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C431" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D431" s="1"/>
+      <c r="C431" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D431" s="2">
+        <v>1</v>
+      </c>
       <c r="E431" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A432" s="1" t="s">
+      <c r="A432" t="s">
         <v>162</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D432" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="D432" s="1">
+        <v>1</v>
+      </c>
       <c r="E432" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
@@ -10256,15 +10289,17 @@
       <c r="B433" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C433" s="2"/>
-      <c r="D433" s="2" t="s">
-        <v>144</v>
+      <c r="C433" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D433" s="1">
+        <v>1</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F433" s="2" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.35">
@@ -10272,16 +10307,17 @@
         <v>162</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D434" t="s">
-        <v>144</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D434" s="1"/>
       <c r="E434" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.35">
@@ -10289,16 +10325,17 @@
         <v>162</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C435" t="s">
-        <v>200</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D435" s="1"/>
       <c r="E435" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.35">
@@ -10306,16 +10343,17 @@
         <v>162</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C436" t="s">
-        <v>94</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D436" s="1"/>
       <c r="E436" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.35">
@@ -10323,33 +10361,35 @@
         <v>162</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C437" t="s">
-        <v>201</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C437" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D437" s="1"/>
       <c r="E437" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F437" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A438" t="s">
-        <v>162</v>
-      </c>
-      <c r="B438" t="s">
-        <v>148</v>
-      </c>
-      <c r="D438" t="s">
+      <c r="A438" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C438" s="2"/>
+      <c r="D438" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>212</v>
+        <v>53</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.35">
@@ -10357,19 +10397,16 @@
         <v>162</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C439" t="s">
-        <v>199</v>
-      </c>
-      <c r="D439">
-        <v>2</v>
+        <v>210</v>
+      </c>
+      <c r="D439" t="s">
+        <v>144</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
@@ -10377,61 +10414,58 @@
         <v>162</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="C440" t="s">
-        <v>204</v>
-      </c>
-      <c r="D440">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A441" t="s">
-        <v>162</v>
-      </c>
-      <c r="B441" t="s">
-        <v>148</v>
+      <c r="A441" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="C441" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F441" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A442" t="s">
-        <v>162</v>
-      </c>
-      <c r="B442" t="s">
-        <v>148</v>
+      <c r="A442" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="C442" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A443" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B443" s="1" t="s">
-        <v>450</v>
+      <c r="A443" t="s">
+        <v>162</v>
+      </c>
+      <c r="B443" t="s">
+        <v>148</v>
       </c>
       <c r="D443" t="s">
         <v>144</v>
@@ -10448,16 +10482,19 @@
         <v>162</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D444" t="s">
-        <v>144</v>
+        <v>148</v>
+      </c>
+      <c r="C444" t="s">
+        <v>199</v>
+      </c>
+      <c r="D444">
+        <v>2</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.35">
@@ -10465,30 +10502,30 @@
         <v>162</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>192</v>
+        <v>148</v>
       </c>
       <c r="C445" t="s">
-        <v>100</v>
+        <v>204</v>
       </c>
       <c r="D445">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>54</v>
+        <v>214</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A446" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B446" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D446" t="s">
-        <v>144</v>
+      <c r="A446" t="s">
+        <v>162</v>
+      </c>
+      <c r="B446" t="s">
+        <v>148</v>
+      </c>
+      <c r="C446" t="s">
+        <v>195</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>193</v>
@@ -10498,23 +10535,20 @@
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A447" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B447" s="1" t="s">
-        <v>209</v>
+      <c r="A447" t="s">
+        <v>162</v>
+      </c>
+      <c r="B447" t="s">
+        <v>148</v>
       </c>
       <c r="C447" t="s">
-        <v>199</v>
-      </c>
-      <c r="D447">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.35">
@@ -10522,19 +10556,16 @@
         <v>162</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C448" t="s">
-        <v>204</v>
-      </c>
-      <c r="D448">
-        <v>1</v>
+        <v>450</v>
+      </c>
+      <c r="D448" t="s">
+        <v>144</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F448" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
@@ -10542,16 +10573,16 @@
         <v>162</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C449" t="s">
-        <v>449</v>
+        <v>192</v>
+      </c>
+      <c r="D449" t="s">
+        <v>144</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F449" s="2" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.35">
@@ -10559,16 +10590,19 @@
         <v>162</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D450" t="s">
-        <v>144</v>
-      </c>
-      <c r="E450" t="s">
-        <v>193</v>
-      </c>
-      <c r="F450" t="s">
-        <v>206</v>
+        <v>192</v>
+      </c>
+      <c r="C450" t="s">
+        <v>100</v>
+      </c>
+      <c r="D450">
+        <v>1</v>
+      </c>
+      <c r="E450" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F450" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
@@ -10576,19 +10610,16 @@
         <v>162</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C451" t="s">
-        <v>100</v>
-      </c>
-      <c r="D451">
-        <v>1</v>
-      </c>
-      <c r="E451" t="s">
+        <v>209</v>
+      </c>
+      <c r="D451" t="s">
+        <v>144</v>
+      </c>
+      <c r="E451" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F451" t="s">
-        <v>208</v>
+      <c r="F451" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.35">
@@ -10596,16 +10627,19 @@
         <v>162</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D452" t="s">
-        <v>144</v>
-      </c>
-      <c r="E452" t="s">
-        <v>374</v>
-      </c>
-      <c r="F452" t="s">
-        <v>376</v>
+        <v>209</v>
+      </c>
+      <c r="C452" t="s">
+        <v>199</v>
+      </c>
+      <c r="D452">
+        <v>1</v>
+      </c>
+      <c r="E452" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F452" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
@@ -10613,16 +10647,19 @@
         <v>162</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="D453" t="s">
-        <v>144</v>
-      </c>
-      <c r="E453" t="s">
-        <v>537</v>
-      </c>
-      <c r="F453" t="s">
-        <v>539</v>
+        <v>209</v>
+      </c>
+      <c r="C453" t="s">
+        <v>204</v>
+      </c>
+      <c r="D453">
+        <v>1</v>
+      </c>
+      <c r="E453" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F453" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.35">
@@ -10630,16 +10667,16 @@
         <v>162</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>540</v>
+        <v>209</v>
       </c>
       <c r="C454" t="s">
-        <v>552</v>
-      </c>
-      <c r="E454" t="s">
-        <v>537</v>
-      </c>
-      <c r="F454" t="s">
-        <v>549</v>
+        <v>449</v>
+      </c>
+      <c r="E454" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F454" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.35">
@@ -10647,16 +10684,16 @@
         <v>162</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="C455" t="s">
-        <v>553</v>
+        <v>207</v>
+      </c>
+      <c r="D455" t="s">
+        <v>144</v>
       </c>
       <c r="E455" t="s">
-        <v>537</v>
+        <v>193</v>
       </c>
       <c r="F455" t="s">
-        <v>549</v>
+        <v>206</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.35">
@@ -10664,16 +10701,19 @@
         <v>162</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>540</v>
+        <v>207</v>
       </c>
       <c r="C456" t="s">
-        <v>196</v>
+        <v>100</v>
+      </c>
+      <c r="D456">
+        <v>1</v>
       </c>
       <c r="E456" t="s">
-        <v>537</v>
+        <v>193</v>
       </c>
       <c r="F456" t="s">
-        <v>549</v>
+        <v>208</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
@@ -10681,16 +10721,16 @@
         <v>162</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="D457" t="s">
         <v>144</v>
       </c>
       <c r="E457" t="s">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="F457" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.35">
@@ -10698,19 +10738,16 @@
         <v>162</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C458" t="s">
-        <v>336</v>
-      </c>
-      <c r="D458">
-        <v>1</v>
+        <v>540</v>
+      </c>
+      <c r="D458" t="s">
+        <v>144</v>
       </c>
       <c r="E458" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F458" t="s">
-        <v>337</v>
+        <v>539</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.35">
@@ -10718,19 +10755,16 @@
         <v>162</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>335</v>
+        <v>540</v>
       </c>
       <c r="C459" t="s">
-        <v>102</v>
-      </c>
-      <c r="D459">
-        <v>1</v>
+        <v>552</v>
       </c>
       <c r="E459" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F459" t="s">
-        <v>344</v>
+        <v>549</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.35">
@@ -10738,19 +10772,16 @@
         <v>162</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>335</v>
+        <v>540</v>
       </c>
       <c r="C460" t="s">
-        <v>115</v>
-      </c>
-      <c r="D460">
-        <v>1</v>
+        <v>553</v>
       </c>
       <c r="E460" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F460" t="s">
-        <v>334</v>
+        <v>549</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.35">
@@ -10758,19 +10789,16 @@
         <v>162</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>335</v>
+        <v>540</v>
       </c>
       <c r="C461" t="s">
-        <v>338</v>
-      </c>
-      <c r="D461">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="E461" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F461" t="s">
-        <v>339</v>
+        <v>549</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.35">
@@ -10778,7 +10806,7 @@
         <v>162</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D462" t="s">
         <v>144</v>
@@ -10787,7 +10815,7 @@
         <v>331</v>
       </c>
       <c r="F462" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.35">
@@ -10795,10 +10823,10 @@
         <v>162</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C463" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D463">
         <v>1</v>
@@ -10807,7 +10835,7 @@
         <v>331</v>
       </c>
       <c r="F463" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.35">
@@ -10815,10 +10843,10 @@
         <v>162</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C464" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D464">
         <v>1</v>
@@ -10827,7 +10855,7 @@
         <v>331</v>
       </c>
       <c r="F464" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
@@ -10835,10 +10863,10 @@
         <v>162</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C465" t="s">
-        <v>342</v>
+        <v>115</v>
       </c>
       <c r="D465">
         <v>1</v>
@@ -10847,7 +10875,7 @@
         <v>331</v>
       </c>
       <c r="F465" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.35">
@@ -10855,16 +10883,19 @@
         <v>162</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D466" t="s">
-        <v>128</v>
+        <v>335</v>
+      </c>
+      <c r="C466" t="s">
+        <v>338</v>
+      </c>
+      <c r="D466">
+        <v>1</v>
       </c>
       <c r="E466" t="s">
         <v>331</v>
       </c>
       <c r="F466" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.35">
@@ -10872,16 +10903,16 @@
         <v>162</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>482</v>
+        <v>333</v>
       </c>
       <c r="D467" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E467" t="s">
-        <v>481</v>
+        <v>331</v>
       </c>
       <c r="F467" t="s">
-        <v>64</v>
+        <v>334</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.35">
@@ -10889,16 +10920,19 @@
         <v>162</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D468" t="s">
-        <v>128</v>
+        <v>333</v>
+      </c>
+      <c r="C468" t="s">
+        <v>340</v>
+      </c>
+      <c r="D468">
+        <v>1</v>
       </c>
       <c r="E468" t="s">
-        <v>193</v>
+        <v>331</v>
       </c>
       <c r="F468" t="s">
-        <v>206</v>
+        <v>341</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
@@ -10906,16 +10940,19 @@
         <v>162</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="D469" t="s">
-        <v>144</v>
+        <v>333</v>
+      </c>
+      <c r="C469" t="s">
+        <v>100</v>
+      </c>
+      <c r="D469">
+        <v>1</v>
       </c>
       <c r="E469" t="s">
-        <v>497</v>
+        <v>331</v>
       </c>
       <c r="F469" t="s">
-        <v>503</v>
+        <v>334</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
@@ -10923,19 +10960,19 @@
         <v>162</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>502</v>
+        <v>333</v>
       </c>
       <c r="C470" t="s">
-        <v>415</v>
+        <v>342</v>
       </c>
       <c r="D470">
         <v>1</v>
       </c>
       <c r="E470" t="s">
-        <v>532</v>
+        <v>331</v>
       </c>
       <c r="F470" t="s">
-        <v>533</v>
+        <v>343</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.35">
@@ -10943,16 +10980,16 @@
         <v>162</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C471" t="s">
-        <v>506</v>
+        <v>442</v>
+      </c>
+      <c r="D471" t="s">
+        <v>128</v>
       </c>
       <c r="E471" t="s">
-        <v>497</v>
+        <v>331</v>
       </c>
       <c r="F471" t="s">
-        <v>507</v>
+        <v>344</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.35">
@@ -10960,16 +10997,16 @@
         <v>162</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C472" t="s">
-        <v>531</v>
+        <v>482</v>
+      </c>
+      <c r="D472" t="s">
+        <v>128</v>
       </c>
       <c r="E472" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="F472" t="s">
-        <v>527</v>
+        <v>64</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.35">
@@ -10977,16 +11014,16 @@
         <v>162</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>535</v>
+        <v>232</v>
       </c>
       <c r="D473" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="E473" t="s">
-        <v>532</v>
+        <v>193</v>
       </c>
       <c r="F473" t="s">
-        <v>533</v>
+        <v>206</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.35">
@@ -10994,7 +11031,7 @@
         <v>162</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>528</v>
+        <v>502</v>
       </c>
       <c r="D474" t="s">
         <v>144</v>
@@ -11003,6 +11040,94 @@
         <v>497</v>
       </c>
       <c r="F474" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A475" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C475" t="s">
+        <v>415</v>
+      </c>
+      <c r="D475">
+        <v>1</v>
+      </c>
+      <c r="E475" t="s">
+        <v>532</v>
+      </c>
+      <c r="F475" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A476" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C476" t="s">
+        <v>506</v>
+      </c>
+      <c r="E476" t="s">
+        <v>497</v>
+      </c>
+      <c r="F476" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A477" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C477" t="s">
+        <v>531</v>
+      </c>
+      <c r="E477" t="s">
+        <v>497</v>
+      </c>
+      <c r="F477" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A478" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D478" t="s">
+        <v>345</v>
+      </c>
+      <c r="E478" t="s">
+        <v>532</v>
+      </c>
+      <c r="F478" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A479" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D479" t="s">
+        <v>144</v>
+      </c>
+      <c r="E479" t="s">
+        <v>497</v>
+      </c>
+      <c r="F479" t="s">
         <v>529</v>
       </c>
     </row>

--- a/snippet-extractor-metadata/word.xlsx
+++ b/snippet-extractor-metadata/word.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF34F44-527C-4446-A3C9-73489A74B909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23473AC-1060-41C5-AA4D-116ACC111178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2351" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="623">
   <si>
     <t>Class</t>
   </si>
@@ -1835,6 +1835,60 @@
   </si>
   <si>
     <t>ExportFormat</t>
+  </si>
+  <si>
+    <t>selection</t>
+  </si>
+  <si>
+    <t>word-selection-insert-formula</t>
+  </si>
+  <si>
+    <t>insertFormulaCustom</t>
+  </si>
+  <si>
+    <t>insertFormulaAuto</t>
+  </si>
+  <si>
+    <t>Selection</t>
+  </si>
+  <si>
+    <t>insertFormula</t>
+  </si>
+  <si>
+    <t>insertFormulaWithOptions</t>
+  </si>
+  <si>
+    <t>SelectionInsertFormulaOptions</t>
+  </si>
+  <si>
+    <t>getNextRange</t>
+  </si>
+  <si>
+    <t>getPreviousRange</t>
+  </si>
+  <si>
+    <t>word-selection-get-previous-next-range</t>
+  </si>
+  <si>
+    <t>SelectionNextOptions</t>
+  </si>
+  <si>
+    <t>SelectionPreviousOptions</t>
+  </si>
+  <si>
+    <t>getNextWord</t>
+  </si>
+  <si>
+    <t>getPreviousSentence</t>
+  </si>
+  <si>
+    <t>getPreviousWord</t>
+  </si>
+  <si>
+    <t>getNextParagraph</t>
+  </si>
+  <si>
+    <t>OperationUnit</t>
   </si>
 </sst>
 </file>
@@ -1883,7 +1937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1894,7 +1948,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1951,8 +2004,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F470" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="A1:F470" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F479" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:F479" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{1DA12987-AB2C-4056-A643-B1229DC856C5}" name="Package" dataDxfId="4"/>
     <tableColumn id="1" xr3:uid="{0CD83AD1-F92A-407D-8460-4E881461FD01}" name="Class" dataDxfId="3"/>
@@ -2262,7 +2315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F470"/>
+  <dimension ref="A1:F479"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25.08984375" bestFit="1" customWidth="1"/>
@@ -5579,16 +5632,16 @@
       <c r="B182" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C182" s="4" t="s">
+      <c r="C182" s="1" t="s">
         <v>603</v>
       </c>
       <c r="D182" s="1">
         <v>1</v>
       </c>
-      <c r="E182" s="5" t="s">
+      <c r="E182" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="F182" s="2" t="s">
         <v>601</v>
       </c>
     </row>
@@ -6091,21 +6144,21 @@
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A210" s="1" t="s">
+      <c r="A210" t="s">
         <v>162</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>165</v>
+        <v>605</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" s="2" t="s">
-        <v>164</v>
+        <v>606</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>169</v>
+        <v>608</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.35">
@@ -6116,14 +6169,14 @@
         <v>65</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>530</v>
+        <v>165</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" s="2" t="s">
-        <v>497</v>
+        <v>164</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>529</v>
+        <v>169</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.35">
@@ -6131,17 +6184,17 @@
         <v>162</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C212" s="2"/>
-      <c r="D212" s="2" t="s">
-        <v>345</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D212" s="2"/>
       <c r="E212" s="2" t="s">
-        <v>389</v>
+        <v>497</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>86</v>
+        <v>529</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.35">
@@ -6149,34 +6202,34 @@
         <v>162</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D213" t="s">
-        <v>144</v>
+        <v>390</v>
+      </c>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>235</v>
+        <v>389</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>236</v>
+        <v>86</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B214" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="C214" s="7"/>
+      <c r="B214" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="D214" t="s">
-        <v>345</v>
-      </c>
-      <c r="E214" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="F214" s="5" t="s">
-        <v>601</v>
+        <v>144</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.35">
@@ -6184,16 +6237,16 @@
         <v>162</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>436</v>
+        <v>602</v>
       </c>
       <c r="D215" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>74</v>
+        <v>600</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>64</v>
+        <v>601</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.35">
@@ -6201,17 +6254,16 @@
         <v>162</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C216" s="2"/>
-      <c r="D216" s="2" t="s">
-        <v>128</v>
+        <v>436</v>
+      </c>
+      <c r="D216" t="s">
+        <v>144</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.35">
@@ -6219,17 +6271,17 @@
         <v>162</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>461</v>
+        <v>170</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>494</v>
+        <v>73</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.35">
@@ -6239,17 +6291,15 @@
       <c r="B218" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C218" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D218" s="2">
-        <v>1</v>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>494</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.35">
@@ -6260,7 +6310,7 @@
         <v>461</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D219" s="2">
         <v>1</v>
@@ -6269,7 +6319,7 @@
         <v>494</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.35">
@@ -6280,14 +6330,16 @@
         <v>461</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D220" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="D220" s="2">
+        <v>1</v>
+      </c>
       <c r="E220" s="2" t="s">
         <v>494</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.35">
@@ -6295,17 +6347,17 @@
         <v>162</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C221" s="2"/>
-      <c r="D221" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D221" s="2"/>
       <c r="E221" s="2" t="s">
-        <v>393</v>
+        <v>494</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>430</v>
+        <v>473</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.35">
@@ -6313,17 +6365,17 @@
         <v>162</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>123</v>
+        <v>430</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.35">
@@ -6341,60 +6393,60 @@
         <v>403</v>
       </c>
       <c r="F223" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A224" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>405</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
-        <v>162</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C224" s="1"/>
-      <c r="D224" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>162</v>
       </c>
-      <c r="B225" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="C225" s="4"/>
+      <c r="B225" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C225" s="1"/>
       <c r="D225" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E225" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="F225" s="6" t="s">
-        <v>601</v>
+      <c r="E225" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A226" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B226" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="C226" s="4"/>
+      <c r="A226" t="s">
+        <v>162</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C226" s="1"/>
       <c r="D226" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E226" s="5" t="s">
+      <c r="E226" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="F226" s="6" t="s">
+      <c r="F226" s="3" t="s">
         <v>601</v>
       </c>
     </row>
@@ -6403,17 +6455,17 @@
         <v>162</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C227" s="2"/>
-      <c r="D227" s="2" t="s">
-        <v>144</v>
+        <v>599</v>
+      </c>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>136</v>
+        <v>600</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.35">
@@ -6423,17 +6475,15 @@
       <c r="B228" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C228" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D228" s="1">
-        <v>1</v>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F228" s="3" t="s">
-        <v>290</v>
+      <c r="F228" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.35">
@@ -6444,7 +6494,7 @@
         <v>132</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D229" s="1">
         <v>1</v>
@@ -6453,7 +6503,7 @@
         <v>163</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
@@ -6464,7 +6514,7 @@
         <v>132</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>287</v>
+        <v>48</v>
       </c>
       <c r="D230" s="1">
         <v>1</v>
@@ -6477,38 +6527,40 @@
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
+      <c r="A231" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C231" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D231" s="2"/>
+      <c r="C231" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D231" s="1">
+        <v>1</v>
+      </c>
       <c r="E231" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F231" s="2" t="s">
-        <v>136</v>
+      <c r="F231" s="3" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A232" s="1" t="s">
+      <c r="A232" t="s">
         <v>162</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D232" s="1"/>
+      <c r="C232" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D232" s="2"/>
       <c r="E232" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F232" s="3" t="s">
+      <c r="F232" s="2" t="s">
         <v>136</v>
       </c>
     </row>
@@ -6519,33 +6571,33 @@
       <c r="B233" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C233" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D233" s="2"/>
+      <c r="C233" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D233" s="1"/>
       <c r="E233" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F233" s="2" t="s">
-        <v>289</v>
+      <c r="F233" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
+      <c r="A234" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.35">
@@ -6556,25 +6608,25 @@
         <v>132</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A236" s="1" t="s">
+      <c r="A236" t="s">
         <v>162</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" s="2" t="s">
@@ -6585,21 +6637,21 @@
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A237" t="s">
+      <c r="A237" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C237" s="2"/>
-      <c r="D237" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D237" s="2"/>
       <c r="E237" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.35">
@@ -6609,17 +6661,15 @@
       <c r="B238" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C238" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D238" s="2">
-        <v>1</v>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.35">
@@ -6630,32 +6680,34 @@
         <v>139</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D239" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="D239" s="2">
+        <v>1</v>
+      </c>
       <c r="E239" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A240" s="1" t="s">
+      <c r="A240" t="s">
         <v>162</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C240" s="2"/>
-      <c r="D240" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D240" s="2"/>
       <c r="E240" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
@@ -6663,7 +6715,7 @@
         <v>162</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>285</v>
+        <v>410</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2" t="s">
@@ -6673,7 +6725,7 @@
         <v>163</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>284</v>
+        <v>136</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
@@ -6681,17 +6733,17 @@
         <v>162</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>557</v>
+        <v>285</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>555</v>
+        <v>163</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>560</v>
+        <v>284</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
@@ -6699,53 +6751,53 @@
         <v>162</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>423</v>
+        <v>557</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>424</v>
+        <v>555</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>86</v>
+        <v>560</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A244" t="s">
+      <c r="A244" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>149</v>
+        <v>423</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="2" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A245" s="1" t="s">
+      <c r="A245" t="s">
         <v>162</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
@@ -6753,55 +6805,55 @@
         <v>162</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>525</v>
+        <v>173</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E246" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A247" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E247" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F246" s="2" t="s">
+      <c r="F247" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A247" t="s">
-        <v>162</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D247" s="2">
-        <v>1</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A248" s="1" t="s">
+      <c r="A248" t="s">
         <v>162</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C248" s="2"/>
-      <c r="D248" s="2" t="s">
-        <v>144</v>
+      <c r="C248" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D248" s="2">
+        <v>1</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
@@ -6811,15 +6863,15 @@
       <c r="B249" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C249" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E249" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.35">
@@ -6827,12 +6879,12 @@
         <v>162</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C250" s="2"/>
-      <c r="D250" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D250" s="2"/>
       <c r="E250" s="2" t="s">
         <v>70</v>
       </c>
@@ -6845,53 +6897,53 @@
         <v>162</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>347</v>
+        <v>177</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" s="2" t="s">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>348</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A252" t="s">
+      <c r="A252" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>154</v>
+        <v>347</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" s="2" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>140</v>
+        <v>235</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>155</v>
+        <v>348</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A253" s="1" t="s">
+      <c r="A253" t="s">
         <v>162</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>510</v>
+        <v>154</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="2" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>537</v>
+        <v>140</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>511</v>
+        <v>155</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
@@ -6899,17 +6951,17 @@
         <v>162</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>215</v>
+        <v>510</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>57</v>
+        <v>537</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>58</v>
+        <v>511</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
@@ -6919,11 +6971,9 @@
       <c r="B255" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C255" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D255" s="2">
-        <v>1</v>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>57</v>
@@ -6940,16 +6990,16 @@
         <v>215</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="D256" s="2">
         <v>1</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>220</v>
+        <v>58</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.35">
@@ -6960,7 +7010,7 @@
         <v>215</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D257" s="2">
         <v>1</v>
@@ -6980,14 +7030,16 @@
         <v>215</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D258" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="D258" s="2">
+        <v>1</v>
+      </c>
       <c r="E258" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.35">
@@ -6998,7 +7050,7 @@
         <v>215</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" s="2" t="s">
@@ -7013,17 +7065,17 @@
         <v>162</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C260" s="2"/>
-      <c r="D260" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D260" s="2"/>
       <c r="E260" s="2" t="s">
-        <v>481</v>
+        <v>219</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>64</v>
+        <v>300</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.35">
@@ -7031,17 +7083,17 @@
         <v>162</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>222</v>
+        <v>480</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>219</v>
+        <v>481</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>220</v>
+        <v>64</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.35">
@@ -7049,17 +7101,17 @@
         <v>162</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>425</v>
+        <v>222</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.35">
@@ -7067,17 +7119,17 @@
         <v>162</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>216</v>
+        <v>425</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>58</v>
+        <v>300</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.35">
@@ -7087,10 +7139,10 @@
       <c r="B264" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C264" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D264" s="2"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E264" s="2" t="s">
         <v>57</v>
       </c>
@@ -7103,17 +7155,17 @@
         <v>162</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C265" s="2"/>
-      <c r="D265" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D265" s="2"/>
       <c r="E265" s="2" t="s">
-        <v>481</v>
+        <v>57</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.35">
@@ -7121,7 +7173,7 @@
         <v>162</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2" t="s">
@@ -7139,17 +7191,17 @@
         <v>162</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>225</v>
+        <v>484</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>219</v>
+        <v>481</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>300</v>
+        <v>64</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.35">
@@ -7157,7 +7209,7 @@
         <v>162</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2" t="s">
@@ -7167,7 +7219,7 @@
         <v>219</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.35">
@@ -7175,17 +7227,17 @@
         <v>162</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>485</v>
+        <v>224</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>481</v>
+        <v>219</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>64</v>
+        <v>220</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.35">
@@ -7193,35 +7245,35 @@
         <v>162</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>226</v>
+        <v>485</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>227</v>
+        <v>481</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>228</v>
+        <v>64</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A271" t="s">
+      <c r="A271" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>91</v>
+        <v>226</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.35">
@@ -7231,17 +7283,15 @@
       <c r="B272" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C272" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D272" s="2">
-        <v>1</v>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.35">
@@ -7252,7 +7302,7 @@
         <v>91</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D273" s="2">
         <v>1</v>
@@ -7261,7 +7311,7 @@
         <v>146</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.35">
@@ -7272,14 +7322,16 @@
         <v>91</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D274" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="D274" s="2">
+        <v>1</v>
+      </c>
       <c r="E274" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.35">
@@ -7290,14 +7342,14 @@
         <v>91</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
@@ -7308,14 +7360,14 @@
         <v>91</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.35">
@@ -7323,17 +7375,17 @@
         <v>162</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C277" s="2"/>
-      <c r="D277" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D277" s="2"/>
       <c r="E277" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
@@ -7343,11 +7395,9 @@
       <c r="B278" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C278" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D278" s="2">
-        <v>1</v>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>146</v>
@@ -7360,51 +7410,55 @@
       <c r="A279" t="s">
         <v>162</v>
       </c>
-      <c r="B279" t="s">
-        <v>156</v>
-      </c>
-      <c r="D279" t="s">
-        <v>128</v>
+      <c r="B279" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D279" s="2">
+        <v>1</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A280" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>411</v>
+      <c r="A280" t="s">
+        <v>162</v>
+      </c>
+      <c r="B280" t="s">
+        <v>156</v>
       </c>
       <c r="D280" t="s">
         <v>128</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>374</v>
+        <v>146</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>375</v>
+        <v>95</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A281" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>499</v>
-      </c>
+      <c r="A281" t="s">
+        <v>162</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="C281" s="6"/>
       <c r="D281" t="s">
-        <v>144</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>498</v>
+        <v>128</v>
+      </c>
+      <c r="E281" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
@@ -7412,19 +7466,16 @@
         <v>162</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="C282" t="s">
-        <v>115</v>
-      </c>
-      <c r="D282">
-        <v>1</v>
+        <v>411</v>
+      </c>
+      <c r="D282" t="s">
+        <v>128</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>497</v>
+        <v>374</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>498</v>
+        <v>375</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.35">
@@ -7434,14 +7485,14 @@
       <c r="B283" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C283" t="s">
-        <v>500</v>
+      <c r="D283" t="s">
+        <v>144</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.35">
@@ -7449,10 +7500,13 @@
         <v>162</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="D284" t="s">
-        <v>144</v>
+        <v>499</v>
+      </c>
+      <c r="C284" t="s">
+        <v>115</v>
+      </c>
+      <c r="D284">
+        <v>1</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>497</v>
@@ -7466,16 +7520,16 @@
         <v>162</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="D285" t="s">
-        <v>144</v>
+        <v>499</v>
+      </c>
+      <c r="C285" t="s">
+        <v>500</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
@@ -7483,16 +7537,16 @@
         <v>162</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C286" t="s">
-        <v>508</v>
+        <v>496</v>
+      </c>
+      <c r="D286" t="s">
+        <v>144</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.35">
@@ -7502,14 +7556,14 @@
       <c r="B287" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C287" t="s">
-        <v>509</v>
+      <c r="D287" t="s">
+        <v>144</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.35">
@@ -7517,74 +7571,68 @@
         <v>162</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="D288" t="s">
-        <v>144</v>
+        <v>504</v>
+      </c>
+      <c r="C288" t="s">
+        <v>508</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F288" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A289" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C289" t="s">
+        <v>509</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F289" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A290" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D290" t="s">
+        <v>144</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A289" t="s">
-        <v>162</v>
-      </c>
-      <c r="B289" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C289" s="2"/>
-      <c r="D289" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E289" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A290" t="s">
-        <v>162</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D290" s="2">
-        <v>1</v>
-      </c>
-      <c r="E290" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A291" s="1" t="s">
+      <c r="A291" t="s">
         <v>162</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C291" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D291" s="2">
-        <v>1</v>
+      <c r="C291" s="2"/>
+      <c r="D291" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>360</v>
+        <v>11</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
@@ -7595,16 +7643,16 @@
         <v>10</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="D292" s="2">
         <v>1</v>
       </c>
-      <c r="E292" s="2" t="s">
-        <v>75</v>
+      <c r="E292" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
@@ -7615,76 +7663,76 @@
         <v>10</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>36</v>
+        <v>360</v>
       </c>
       <c r="D293" s="2">
         <v>1</v>
       </c>
-      <c r="E293" s="2" t="s">
-        <v>43</v>
+      <c r="E293" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>42</v>
+        <v>360</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A294" s="1" t="s">
+      <c r="A294" t="s">
         <v>162</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>556</v>
+        <v>29</v>
       </c>
       <c r="D294" s="2">
         <v>1</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>570</v>
+        <v>75</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>151</v>
+        <v>28</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A295" t="s">
+      <c r="A295" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D295" s="2">
         <v>1</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A296" t="s">
+      <c r="A296" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>512</v>
+        <v>556</v>
       </c>
       <c r="D296" s="2">
         <v>1</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>523</v>
+        <v>151</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.35">
@@ -7695,16 +7743,16 @@
         <v>10</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D297" s="2">
         <v>1</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
@@ -7715,16 +7763,16 @@
         <v>10</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>48</v>
+        <v>512</v>
       </c>
       <c r="D298" s="2">
         <v>1</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>71</v>
+        <v>537</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>49</v>
+        <v>523</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.35">
@@ -7734,17 +7782,17 @@
       <c r="B299" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C299" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D299" s="1">
+      <c r="C299" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D299" s="2">
         <v>1</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.35">
@@ -7755,16 +7803,16 @@
         <v>10</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="D300" s="2">
         <v>1</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.35">
@@ -7774,17 +7822,17 @@
       <c r="B301" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C301" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D301" s="2">
+      <c r="C301" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D301" s="1">
         <v>1</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
@@ -7795,16 +7843,16 @@
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="D302" s="2">
         <v>1</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.35">
@@ -7815,14 +7863,16 @@
         <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D303" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="D303" s="2">
+        <v>1</v>
+      </c>
       <c r="E303" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.35">
@@ -7833,14 +7883,16 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D304" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D304" s="2">
+        <v>1</v>
+      </c>
       <c r="E304" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.35">
@@ -7851,140 +7903,140 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A306" s="1" t="s">
+      <c r="A306" t="s">
         <v>162</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>379</v>
+        <v>19</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>380</v>
+        <v>15</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A307" s="3" t="s">
+      <c r="A307" t="s">
         <v>162</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>382</v>
+        <v>16</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A308" t="s">
+      <c r="A308" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>17</v>
+        <v>379</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>17</v>
+        <v>380</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A309" s="1" t="s">
+      <c r="A309" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>280</v>
+        <v>381</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" s="2" t="s">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>279</v>
+        <v>382</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A310" s="1" t="s">
+      <c r="A310" t="s">
         <v>162</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>238</v>
+        <v>17</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>240</v>
+        <v>17</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A311" t="s">
+      <c r="A311" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>8</v>
+        <v>280</v>
       </c>
       <c r="D311" s="2"/>
-      <c r="E311" s="1" t="s">
-        <v>79</v>
+      <c r="E311" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>11</v>
+        <v>279</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A312" t="s">
+      <c r="A312" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>369</v>
+        <v>238</v>
       </c>
       <c r="D312" s="2"/>
-      <c r="E312" s="1" t="s">
-        <v>350</v>
+      <c r="E312" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>123</v>
+        <v>240</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.35">
@@ -7995,50 +8047,50 @@
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F313" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>162</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D314" s="2"/>
+      <c r="E314" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="F313" s="2" t="s">
+      <c r="F314" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>162</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D315" s="2"/>
+      <c r="E315" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F315" s="2" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A314" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C314" s="2"/>
-      <c r="D314" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E314" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A315" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C315" s="2"/>
-      <c r="D315" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E315" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F315" s="2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
@@ -8046,14 +8098,14 @@
         <v>162</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" s="2" t="s">
         <v>345</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>267</v>
@@ -8064,35 +8116,35 @@
         <v>162</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" s="2" t="s">
         <v>345</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A318" t="s">
+      <c r="A318" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>190</v>
+        <v>329</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>70</v>
+        <v>345</v>
+      </c>
+      <c r="E318" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>175</v>
+        <v>267</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
@@ -8100,19 +8152,17 @@
         <v>162</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D319" s="2">
-        <v>1</v>
+        <v>329</v>
+      </c>
+      <c r="C319" s="2"/>
+      <c r="D319" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
@@ -8122,11 +8172,9 @@
       <c r="B320" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C320" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D320" s="2">
-        <v>1</v>
+      <c r="C320" s="2"/>
+      <c r="D320" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>70</v>
@@ -8136,21 +8184,23 @@
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A321" t="s">
+      <c r="A321" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D321" s="2"/>
-      <c r="E321" s="2" t="s">
-        <v>57</v>
+        <v>100</v>
+      </c>
+      <c r="D321" s="2">
+        <v>1</v>
+      </c>
+      <c r="E321" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>58</v>
+        <v>353</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.35">
@@ -8158,17 +8208,19 @@
         <v>162</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C322" s="2"/>
-      <c r="D322" s="2" t="s">
-        <v>345</v>
+        <v>190</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D322" s="2">
+        <v>1</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>323</v>
+        <v>70</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>267</v>
+        <v>175</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
@@ -8176,53 +8228,53 @@
         <v>162</v>
       </c>
       <c r="B323" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D323" s="2"/>
+      <c r="E323" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F323" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>162</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="C323" s="2"/>
-      <c r="D323" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E323" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A324" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>294</v>
+        <v>267</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A325" s="1" t="s">
+      <c r="A325" t="s">
         <v>162</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D325" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="C325" s="2"/>
+      <c r="D325" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="E325" s="2" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
@@ -8232,10 +8284,10 @@
       <c r="B326" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C326" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D326" s="2"/>
+      <c r="C326" s="2"/>
+      <c r="D326" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E326" s="2" t="s">
         <v>269</v>
       </c>
@@ -8248,17 +8300,17 @@
         <v>162</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C327" s="2"/>
-      <c r="D327" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D327" s="2"/>
       <c r="E327" s="2" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>445</v>
+        <v>294</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.35">
@@ -8266,19 +8318,17 @@
         <v>162</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D328" s="2">
-        <v>1</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D328" s="2"/>
       <c r="E328" s="2" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>228</v>
+        <v>294</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -8288,57 +8338,55 @@
       <c r="B329" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C329" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D329" s="2">
-        <v>1</v>
+      <c r="C329" s="2"/>
+      <c r="D329" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>12</v>
+        <v>445</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A330" t="s">
+      <c r="A330" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C330" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D330" s="1">
+      <c r="C330" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D330" s="2">
         <v>1</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>108</v>
+        <v>228</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A331" t="s">
+      <c r="A331" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C331" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D331" s="1">
+      <c r="C331" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D331" s="2">
         <v>1</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>393</v>
+        <v>79</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>427</v>
+        <v>12</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
@@ -8349,16 +8397,16 @@
         <v>5</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D332" s="1">
         <v>1</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>494</v>
+        <v>145</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>462</v>
+        <v>108</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.35">
@@ -8369,16 +8417,16 @@
         <v>5</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>121</v>
+        <v>395</v>
       </c>
       <c r="D333" s="1">
         <v>1</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>147</v>
+        <v>393</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>121</v>
+        <v>427</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.35">
@@ -8389,16 +8437,16 @@
         <v>5</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="D334" s="1">
         <v>1</v>
       </c>
-      <c r="E334" s="1" t="s">
-        <v>79</v>
+      <c r="E334" s="2" t="s">
+        <v>494</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>12</v>
+        <v>462</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
@@ -8409,16 +8457,16 @@
         <v>5</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D335" s="1">
         <v>1</v>
       </c>
-      <c r="E335" s="1" t="s">
-        <v>145</v>
+      <c r="E335" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
@@ -8429,36 +8477,36 @@
         <v>5</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D336" s="1">
         <v>1</v>
       </c>
-      <c r="E336" s="2" t="s">
-        <v>82</v>
+      <c r="E336" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A337" s="1" t="s">
+      <c r="A337" t="s">
         <v>162</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>283</v>
+        <v>106</v>
       </c>
       <c r="D337" s="1">
         <v>1</v>
       </c>
-      <c r="E337" s="2" t="s">
-        <v>163</v>
+      <c r="E337" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>284</v>
+        <v>106</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.35">
@@ -8469,36 +8517,36 @@
         <v>5</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="D338" s="1">
         <v>1</v>
       </c>
-      <c r="E338" s="1" t="s">
-        <v>146</v>
+      <c r="E338" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A339" t="s">
+      <c r="A339" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="D339" s="1">
         <v>1</v>
       </c>
-      <c r="E339" s="1" t="s">
-        <v>537</v>
+      <c r="E339" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>521</v>
+        <v>284</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
@@ -8509,16 +8557,16 @@
         <v>5</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>313</v>
+        <v>88</v>
       </c>
       <c r="D340" s="1">
         <v>1</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>537</v>
+        <v>146</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>524</v>
+        <v>88</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.35">
@@ -8529,16 +8577,16 @@
         <v>5</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>556</v>
+        <v>313</v>
       </c>
       <c r="D341" s="1">
         <v>1</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>561</v>
+        <v>521</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.35">
@@ -8549,7 +8597,7 @@
         <v>5</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>512</v>
+        <v>313</v>
       </c>
       <c r="D342" s="1">
         <v>1</v>
@@ -8558,7 +8606,7 @@
         <v>537</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.35">
@@ -8569,49 +8617,54 @@
         <v>5</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D343" s="1"/>
+        <v>556</v>
+      </c>
+      <c r="D343" s="1">
+        <v>1</v>
+      </c>
       <c r="E343" s="1" t="s">
-        <v>146</v>
+        <v>555</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>96</v>
+        <v>561</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A344" s="1" t="s">
+      <c r="A344" t="s">
         <v>162</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C344" t="s">
-        <v>428</v>
-      </c>
-      <c r="E344" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F344" t="s">
-        <v>422</v>
+      <c r="C344" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D344" s="1">
+        <v>1</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="F344" s="2" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A345" s="1" t="s">
+      <c r="A345" t="s">
         <v>162</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C345" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D345" s="2"/>
-      <c r="E345" s="2" t="s">
-        <v>82</v>
+      <c r="C345" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D345" s="1"/>
+      <c r="E345" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>239</v>
+        <v>96</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.35">
@@ -8619,35 +8672,34 @@
         <v>162</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C346" s="2"/>
-      <c r="D346" s="2" t="s">
-        <v>144</v>
+        <v>5</v>
+      </c>
+      <c r="C346" t="s">
+        <v>428</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F346" s="2" t="s">
-        <v>31</v>
+        <v>393</v>
+      </c>
+      <c r="F346" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A347" t="s">
+      <c r="A347" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C347" s="1"/>
-      <c r="D347" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E347" s="1" t="s">
-        <v>79</v>
+        <v>5</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D347" s="2"/>
+      <c r="E347" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>12</v>
+        <v>239</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.35">
@@ -8655,35 +8707,35 @@
         <v>162</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C348" s="1"/>
-      <c r="D348" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E348" s="1" t="s">
-        <v>570</v>
+        <v>437</v>
+      </c>
+      <c r="C348" s="2"/>
+      <c r="D348" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>576</v>
+        <v>31</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A349" s="1" t="s">
+      <c r="A349" t="s">
         <v>162</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>577</v>
+        <v>158</v>
       </c>
       <c r="C349" s="1"/>
       <c r="D349" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>570</v>
+        <v>79</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>578</v>
+        <v>12</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
@@ -8691,7 +8743,7 @@
         <v>162</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C350" s="1"/>
       <c r="D350" s="1" t="s">
@@ -8709,17 +8761,17 @@
         <v>162</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>418</v>
+        <v>577</v>
       </c>
       <c r="C351" s="1"/>
       <c r="D351" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>413</v>
+        <v>570</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>414</v>
+        <v>578</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
@@ -8727,57 +8779,53 @@
         <v>162</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>534</v>
+        <v>579</v>
       </c>
       <c r="C352" s="1"/>
       <c r="D352" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E352" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="F352" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A353" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F353" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A354" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E354" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F352" s="2" t="s">
+      <c r="F354" s="2" t="s">
         <v>533</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A353" t="s">
-        <v>162</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C353" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D353" s="2">
-        <v>2</v>
-      </c>
-      <c r="E353" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F353" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A354" t="s">
-        <v>162</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D354" s="1">
-        <v>1</v>
-      </c>
-      <c r="E354" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F354" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.35">
@@ -8787,15 +8835,17 @@
       <c r="B355" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C355" s="1"/>
-      <c r="D355" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>140</v>
+      <c r="C355" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D355" s="2">
+        <v>2</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
@@ -8803,17 +8853,19 @@
         <v>162</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C356" s="2"/>
-      <c r="D356" s="2" t="s">
-        <v>144</v>
+        <v>27</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D356" s="1">
+        <v>1</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.35">
@@ -8821,181 +8873,185 @@
         <v>162</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C357" s="2"/>
-      <c r="D357" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E357" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
+      </c>
+      <c r="C357" s="1"/>
+      <c r="D357" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A358" s="1" t="s">
+      <c r="A358" t="s">
         <v>162</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>296</v>
+        <v>142</v>
       </c>
       <c r="C358" s="2"/>
       <c r="D358" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A359" s="1" t="s">
+      <c r="A359" t="s">
         <v>162</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D359" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="C359" s="2"/>
+      <c r="D359" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E359" s="2" t="s">
-        <v>164</v>
+        <v>606</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>168</v>
+        <v>608</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A360" s="1" t="s">
+      <c r="A360" t="s">
         <v>162</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C360" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D360" s="2"/>
-      <c r="E360" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F360" s="2" t="s">
-        <v>168</v>
+        <v>609</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="D360" s="2">
+        <v>1</v>
+      </c>
+      <c r="E360" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F360" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A361" s="1" t="s">
+      <c r="A361" t="s">
         <v>162</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C361" s="2"/>
-      <c r="D361" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E361" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F361" s="2" t="s">
-        <v>166</v>
+        <v>609</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="D361" s="2">
+        <v>1</v>
+      </c>
+      <c r="E361" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F361" s="5" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A362" s="1" t="s">
+      <c r="A362" t="s">
         <v>162</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>167</v>
+        <v>609</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>4</v>
+        <v>610</v>
       </c>
       <c r="D362" s="2">
         <v>1</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>164</v>
+        <v>606</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>168</v>
+        <v>607</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A363" s="1" t="s">
+      <c r="A363" t="s">
         <v>162</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C363" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D363" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="C363" s="2"/>
+      <c r="D363" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="E363" s="2" t="s">
-        <v>164</v>
+        <v>606</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>169</v>
+        <v>611</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B364" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C364" s="2"/>
+      <c r="B364" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="C364" s="5"/>
       <c r="D364" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E364" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F364" s="2" t="s">
-        <v>489</v>
+        <v>345</v>
+      </c>
+      <c r="E364" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F364" s="5" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B365" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C365" s="2"/>
+      <c r="B365" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="C365" s="5"/>
       <c r="D365" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E365" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F365" s="2" t="s">
-        <v>489</v>
+        <v>345</v>
+      </c>
+      <c r="E365" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F365" s="5" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A366" s="1" t="s">
+      <c r="A366" t="s">
         <v>162</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>516</v>
+        <v>159</v>
       </c>
       <c r="C366" s="2"/>
       <c r="D366" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>537</v>
+        <v>71</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>519</v>
+        <v>49</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.35">
@@ -9003,19 +9059,17 @@
         <v>162</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D367" s="2">
-        <v>1</v>
+        <v>296</v>
+      </c>
+      <c r="C367" s="2"/>
+      <c r="D367" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>537</v>
+        <v>164</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>522</v>
+        <v>168</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
@@ -9023,19 +9077,17 @@
         <v>162</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>516</v>
+        <v>296</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="D368" s="2">
-        <v>1</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="D368" s="2"/>
       <c r="E368" s="2" t="s">
-        <v>570</v>
+        <v>164</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>584</v>
+        <v>168</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
@@ -9043,19 +9095,17 @@
         <v>162</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>516</v>
+        <v>296</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D369" s="2">
-        <v>1</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="D369" s="2"/>
       <c r="E369" s="2" t="s">
-        <v>570</v>
+        <v>164</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>584</v>
+        <v>168</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.35">
@@ -9063,19 +9113,17 @@
         <v>162</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C370" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="D370" s="2">
-        <v>1</v>
+        <v>167</v>
+      </c>
+      <c r="C370" s="2"/>
+      <c r="D370" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>570</v>
+        <v>164</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>581</v>
+        <v>166</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
@@ -9083,19 +9131,19 @@
         <v>162</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>516</v>
+        <v>167</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>588</v>
+        <v>4</v>
       </c>
       <c r="D371" s="2">
         <v>1</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>570</v>
+        <v>164</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>581</v>
+        <v>168</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.35">
@@ -9103,19 +9151,17 @@
         <v>162</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>516</v>
+        <v>167</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D372" s="2">
-        <v>1</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D372" s="2"/>
       <c r="E372" s="2" t="s">
-        <v>570</v>
+        <v>164</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>571</v>
+        <v>169</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
@@ -9123,17 +9169,17 @@
         <v>162</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C373" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D373" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="C373" s="2"/>
+      <c r="D373" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E373" s="2" t="s">
-        <v>537</v>
+        <v>269</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>520</v>
+        <v>489</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.35">
@@ -9141,17 +9187,17 @@
         <v>162</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C374" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D374" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="C374" s="2"/>
+      <c r="D374" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E374" s="2" t="s">
-        <v>595</v>
+        <v>269</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>596</v>
+        <v>489</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
@@ -9161,15 +9207,15 @@
       <c r="B375" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C375" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D375" s="2"/>
+      <c r="C375" s="2"/>
+      <c r="D375" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E375" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>564</v>
+        <v>519</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.35">
@@ -9180,14 +9226,16 @@
         <v>516</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="D376" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="D376" s="2">
+        <v>1</v>
+      </c>
       <c r="E376" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>559</v>
+        <v>522</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.35">
@@ -9198,14 +9246,16 @@
         <v>516</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="D377" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="D377" s="2">
+        <v>1</v>
+      </c>
       <c r="E377" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -9216,14 +9266,16 @@
         <v>516</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="D378" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="D378" s="2">
+        <v>1</v>
+      </c>
       <c r="E378" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.35">
@@ -9234,14 +9286,16 @@
         <v>516</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="D379" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="D379" s="2">
+        <v>1</v>
+      </c>
       <c r="E379" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.35">
@@ -9252,14 +9306,16 @@
         <v>516</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="D380" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="D380" s="2">
+        <v>1</v>
+      </c>
       <c r="E380" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.35">
@@ -9270,14 +9326,16 @@
         <v>516</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="D381" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D381" s="2">
+        <v>1</v>
+      </c>
       <c r="E381" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.35">
@@ -9288,14 +9346,14 @@
         <v>516</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>586</v>
+        <v>104</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>571</v>
+        <v>520</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.35">
@@ -9306,14 +9364,14 @@
         <v>516</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>538</v>
+        <v>597</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" s="2" t="s">
-        <v>537</v>
+        <v>595</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>539</v>
+        <v>596</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.35">
@@ -9324,14 +9382,14 @@
         <v>516</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" s="2" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>542</v>
+        <v>564</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
@@ -9342,14 +9400,14 @@
         <v>516</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>94</v>
+        <v>558</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" s="2" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>514</v>
+        <v>559</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.35">
@@ -9357,17 +9415,17 @@
         <v>162</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C386" s="2"/>
-      <c r="D386" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D386" s="2"/>
       <c r="E386" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>549</v>
+        <v>578</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.35">
@@ -9375,17 +9433,17 @@
         <v>162</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C387" s="2"/>
-      <c r="D387" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="D387" s="2"/>
       <c r="E387" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>514</v>
+        <v>576</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.35">
@@ -9393,19 +9451,17 @@
         <v>162</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="D388" s="2">
-        <v>1</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="D388" s="2"/>
       <c r="E388" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
@@ -9413,19 +9469,17 @@
         <v>162</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D389" s="2">
-        <v>1</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="D389" s="2"/>
       <c r="E389" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>519</v>
+        <v>576</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.35">
@@ -9433,19 +9487,17 @@
         <v>162</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D390" s="2">
-        <v>1</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="D390" s="2"/>
       <c r="E390" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>520</v>
+        <v>578</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.35">
@@ -9453,19 +9505,17 @@
         <v>162</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D391" s="2">
-        <v>1</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="D391" s="2"/>
       <c r="E391" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>536</v>
+        <v>571</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.35">
@@ -9473,19 +9523,17 @@
         <v>162</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="D392" s="2">
-        <v>1</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="D392" s="2"/>
       <c r="E392" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.35">
@@ -9493,17 +9541,17 @@
         <v>162</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C393" s="2"/>
-      <c r="D393" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D393" s="2"/>
       <c r="E393" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.35">
@@ -9511,19 +9559,17 @@
         <v>162</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>565</v>
+        <v>516</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D394" s="2">
-        <v>1</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D394" s="2"/>
       <c r="E394" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>567</v>
+        <v>514</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.35">
@@ -9531,19 +9577,17 @@
         <v>162</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C395" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="D395" s="2">
-        <v>1</v>
+        <v>548</v>
+      </c>
+      <c r="C395" s="2"/>
+      <c r="D395" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.35">
@@ -9551,17 +9595,17 @@
         <v>162</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>566</v>
+        <v>513</v>
       </c>
       <c r="C396" s="2"/>
       <c r="D396" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>564</v>
+        <v>514</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.35">
@@ -9569,17 +9613,19 @@
         <v>162</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C397" s="2"/>
-      <c r="D397" s="2" t="s">
-        <v>144</v>
+        <v>513</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D397" s="2">
+        <v>1</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.35">
@@ -9587,19 +9633,19 @@
         <v>162</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>572</v>
+        <v>513</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>573</v>
+        <v>518</v>
       </c>
       <c r="D398" s="2">
         <v>1</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>574</v>
+        <v>519</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.35">
@@ -9607,17 +9653,19 @@
         <v>162</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>572</v>
+        <v>513</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D399" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="D399" s="2">
+        <v>1</v>
+      </c>
       <c r="E399" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>584</v>
+        <v>520</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.35">
@@ -9625,17 +9673,19 @@
         <v>162</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="C400" s="2"/>
-      <c r="D400" s="2" t="s">
-        <v>128</v>
+        <v>513</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D400" s="2">
+        <v>1</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>581</v>
+        <v>536</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.35">
@@ -9643,17 +9693,19 @@
         <v>162</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="C401" s="2"/>
-      <c r="D401" s="2" t="s">
-        <v>128</v>
+        <v>513</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D401" s="2">
+        <v>1</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.35">
@@ -9661,17 +9713,17 @@
         <v>162</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="C402" s="2"/>
       <c r="D402" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.35">
@@ -9679,17 +9731,19 @@
         <v>162</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="C403" s="2"/>
-      <c r="D403" s="2" t="s">
-        <v>128</v>
+        <v>565</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D403" s="2">
+        <v>1</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
@@ -9697,17 +9751,19 @@
         <v>162</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C404" s="2"/>
-      <c r="D404" s="2" t="s">
-        <v>144</v>
+        <v>565</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D404" s="2">
+        <v>1</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
@@ -9715,17 +9771,17 @@
         <v>162</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="D405" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="C405" s="2"/>
+      <c r="D405" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E405" s="2" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F405" s="2" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.35">
@@ -9733,17 +9789,17 @@
         <v>162</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C406" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D406" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="C406" s="2"/>
+      <c r="D406" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E406" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>547</v>
+        <v>571</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.35">
@@ -9751,17 +9807,19 @@
         <v>162</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C407" s="2"/>
-      <c r="D407" s="2" t="s">
-        <v>128</v>
+        <v>572</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D407" s="2">
+        <v>1</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>547</v>
+        <v>574</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.35">
@@ -9769,17 +9827,17 @@
         <v>162</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="C408" s="2"/>
-      <c r="D408" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D408" s="2"/>
       <c r="E408" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
@@ -9787,17 +9845,17 @@
         <v>162</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>517</v>
+        <v>580</v>
       </c>
       <c r="C409" s="2"/>
       <c r="D409" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>514</v>
+        <v>581</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.35">
@@ -9805,17 +9863,17 @@
         <v>162</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>275</v>
+        <v>582</v>
       </c>
       <c r="C410" s="2"/>
       <c r="D410" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>269</v>
+        <v>570</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>279</v>
+        <v>581</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.35">
@@ -9823,19 +9881,17 @@
         <v>162</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C411" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D411" s="2">
-        <v>1</v>
+        <v>550</v>
+      </c>
+      <c r="C411" s="2"/>
+      <c r="D411" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>282</v>
+        <v>549</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.35">
@@ -9843,17 +9899,17 @@
         <v>162</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C412" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D412" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="C412" s="2"/>
+      <c r="D412" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E412" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>378</v>
+        <v>549</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.35">
@@ -9861,17 +9917,17 @@
         <v>162</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C413" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D413" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C413" s="2"/>
+      <c r="D413" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E413" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>295</v>
+        <v>542</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
@@ -9879,17 +9935,17 @@
         <v>162</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>275</v>
+        <v>543</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" s="2" t="s">
-        <v>481</v>
+        <v>537</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>64</v>
+        <v>547</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
@@ -9897,17 +9953,17 @@
         <v>162</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>275</v>
+        <v>543</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>276</v>
+        <v>94</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>279</v>
+        <v>547</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.35">
@@ -9915,17 +9971,17 @@
         <v>162</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C416" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D416" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="C416" s="2"/>
+      <c r="D416" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E416" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>294</v>
+        <v>547</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.35">
@@ -9933,17 +9989,17 @@
         <v>162</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C417" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="D417" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="C417" s="2"/>
+      <c r="D417" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E417" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>489</v>
+        <v>547</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.35">
@@ -9951,17 +10007,17 @@
         <v>162</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>271</v>
+        <v>517</v>
       </c>
       <c r="C418" s="2"/>
       <c r="D418" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>270</v>
+        <v>514</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.35">
@@ -9969,19 +10025,17 @@
         <v>162</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C419" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D419" s="2">
-        <v>1</v>
+        <v>275</v>
+      </c>
+      <c r="C419" s="2"/>
+      <c r="D419" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.35">
@@ -9989,10 +10043,10 @@
         <v>162</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>270</v>
+        <v>97</v>
       </c>
       <c r="D420" s="2">
         <v>1</v>
@@ -10001,7 +10055,7 @@
         <v>269</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
@@ -10009,17 +10063,17 @@
         <v>162</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C421" s="2"/>
-      <c r="D421" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D421" s="2"/>
       <c r="E421" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F421" s="2" t="s">
-        <v>279</v>
+        <v>378</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.35">
@@ -10027,39 +10081,35 @@
         <v>162</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>56</v>
+        <v>275</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D422" s="2">
-        <v>1</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="D422" s="2"/>
       <c r="E422" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A423" t="s">
+      <c r="A423" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C423" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D423" s="1">
-        <v>1</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D423" s="2"/>
       <c r="E423" s="2" t="s">
-        <v>52</v>
+        <v>481</v>
       </c>
       <c r="F423" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.35">
@@ -10067,19 +10117,17 @@
         <v>162</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C424" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D424" s="1">
-        <v>1</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D424" s="2"/>
       <c r="E424" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>203</v>
+        <v>279</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.35">
@@ -10087,17 +10135,17 @@
         <v>162</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D425" s="1"/>
+        <v>275</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D425" s="2"/>
       <c r="E425" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F425" s="2" t="s">
-        <v>194</v>
+        <v>294</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.35">
@@ -10105,17 +10153,17 @@
         <v>162</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C426" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D426" s="1"/>
+        <v>275</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D426" s="2"/>
       <c r="E426" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>194</v>
+        <v>489</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
@@ -10123,17 +10171,17 @@
         <v>162</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C427" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D427" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="C427" s="2"/>
+      <c r="D427" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E427" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F427" s="2" t="s">
-        <v>206</v>
+        <v>270</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.35">
@@ -10141,17 +10189,19 @@
         <v>162</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D428" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D428" s="2">
+        <v>1</v>
+      </c>
       <c r="E428" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F428" s="2" t="s">
-        <v>194</v>
+        <v>273</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.35">
@@ -10159,17 +10209,19 @@
         <v>162</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C429" s="2"/>
-      <c r="D429" s="2" t="s">
-        <v>144</v>
+        <v>271</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D429" s="2">
+        <v>1</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>52</v>
+        <v>269</v>
       </c>
       <c r="F429" s="2" t="s">
-        <v>53</v>
+        <v>270</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
@@ -10177,16 +10229,17 @@
         <v>162</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D430" t="s">
-        <v>144</v>
+        <v>274</v>
+      </c>
+      <c r="C430" s="2"/>
+      <c r="D430" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.35">
@@ -10194,10 +10247,13 @@
         <v>162</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C431" t="s">
-        <v>200</v>
+        <v>56</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D431" s="2">
+        <v>1</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>193</v>
@@ -10207,20 +10263,23 @@
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A432" s="1" t="s">
+      <c r="A432" t="s">
         <v>162</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C432" t="s">
-        <v>94</v>
+        <v>56</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D432" s="1">
+        <v>1</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>198</v>
+        <v>54</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
@@ -10228,33 +10287,37 @@
         <v>162</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C433" t="s">
-        <v>201</v>
+        <v>56</v>
+      </c>
+      <c r="C433" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D433" s="1">
+        <v>1</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F433" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A434" t="s">
-        <v>162</v>
-      </c>
-      <c r="B434" t="s">
-        <v>148</v>
-      </c>
-      <c r="D434" t="s">
-        <v>144</v>
-      </c>
+      <c r="A434" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D434" s="1"/>
       <c r="E434" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.35">
@@ -10262,19 +10325,17 @@
         <v>162</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C435" t="s">
-        <v>199</v>
-      </c>
-      <c r="D435">
-        <v>2</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D435" s="1"/>
       <c r="E435" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.35">
@@ -10282,53 +10343,53 @@
         <v>162</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C436" t="s">
-        <v>204</v>
-      </c>
-      <c r="D436">
-        <v>2</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D436" s="1"/>
       <c r="E436" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A437" t="s">
-        <v>162</v>
-      </c>
-      <c r="B437" t="s">
-        <v>148</v>
-      </c>
-      <c r="C437" t="s">
-        <v>195</v>
-      </c>
+      <c r="A437" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C437" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D437" s="1"/>
       <c r="E437" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F437" s="2" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A438" t="s">
-        <v>162</v>
-      </c>
-      <c r="B438" t="s">
-        <v>148</v>
-      </c>
-      <c r="C438" t="s">
-        <v>196</v>
+      <c r="A438" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C438" s="2"/>
+      <c r="D438" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>212</v>
+        <v>53</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.35">
@@ -10336,7 +10397,7 @@
         <v>162</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>450</v>
+        <v>210</v>
       </c>
       <c r="D439" t="s">
         <v>144</v>
@@ -10345,7 +10406,7 @@
         <v>193</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
@@ -10353,16 +10414,16 @@
         <v>162</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D440" t="s">
-        <v>144</v>
+        <v>210</v>
+      </c>
+      <c r="C440" t="s">
+        <v>200</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.35">
@@ -10370,19 +10431,16 @@
         <v>162</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C441" t="s">
-        <v>100</v>
-      </c>
-      <c r="D441">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F441" s="2" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.35">
@@ -10390,36 +10448,33 @@
         <v>162</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D442" t="s">
-        <v>144</v>
+        <v>210</v>
+      </c>
+      <c r="C442" t="s">
+        <v>201</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A443" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B443" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C443" t="s">
-        <v>199</v>
-      </c>
-      <c r="D443">
-        <v>1</v>
+      <c r="A443" t="s">
+        <v>162</v>
+      </c>
+      <c r="B443" t="s">
+        <v>148</v>
+      </c>
+      <c r="D443" t="s">
+        <v>144</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.35">
@@ -10427,19 +10482,19 @@
         <v>162</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>209</v>
+        <v>148</v>
       </c>
       <c r="C444" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D444">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.35">
@@ -10447,53 +10502,53 @@
         <v>162</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>209</v>
+        <v>148</v>
       </c>
       <c r="C445" t="s">
-        <v>449</v>
+        <v>204</v>
+      </c>
+      <c r="D445">
+        <v>2</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F445" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>162</v>
+      </c>
+      <c r="B446" t="s">
+        <v>148</v>
+      </c>
+      <c r="C446" t="s">
+        <v>195</v>
+      </c>
+      <c r="E446" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F446" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A446" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B446" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D446" t="s">
-        <v>144</v>
-      </c>
-      <c r="E446" t="s">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>162</v>
+      </c>
+      <c r="B447" t="s">
+        <v>148</v>
+      </c>
+      <c r="C447" t="s">
+        <v>196</v>
+      </c>
+      <c r="E447" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F446" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A447" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B447" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C447" t="s">
-        <v>100</v>
-      </c>
-      <c r="D447">
-        <v>1</v>
-      </c>
-      <c r="E447" t="s">
-        <v>193</v>
-      </c>
-      <c r="F447" t="s">
-        <v>208</v>
+      <c r="F447" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.35">
@@ -10501,16 +10556,16 @@
         <v>162</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>373</v>
+        <v>450</v>
       </c>
       <c r="D448" t="s">
         <v>144</v>
       </c>
-      <c r="E448" t="s">
-        <v>374</v>
-      </c>
-      <c r="F448" t="s">
-        <v>376</v>
+      <c r="E448" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F448" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
@@ -10518,16 +10573,16 @@
         <v>162</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>540</v>
+        <v>192</v>
       </c>
       <c r="D449" t="s">
         <v>144</v>
       </c>
-      <c r="E449" t="s">
-        <v>537</v>
-      </c>
-      <c r="F449" t="s">
-        <v>539</v>
+      <c r="E449" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F449" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.35">
@@ -10535,16 +10590,19 @@
         <v>162</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>540</v>
+        <v>192</v>
       </c>
       <c r="C450" t="s">
-        <v>552</v>
-      </c>
-      <c r="E450" t="s">
-        <v>537</v>
-      </c>
-      <c r="F450" t="s">
-        <v>549</v>
+        <v>100</v>
+      </c>
+      <c r="D450">
+        <v>1</v>
+      </c>
+      <c r="E450" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F450" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
@@ -10552,16 +10610,16 @@
         <v>162</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="C451" t="s">
-        <v>553</v>
-      </c>
-      <c r="E451" t="s">
-        <v>537</v>
-      </c>
-      <c r="F451" t="s">
-        <v>549</v>
+        <v>209</v>
+      </c>
+      <c r="D451" t="s">
+        <v>144</v>
+      </c>
+      <c r="E451" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F451" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.35">
@@ -10569,16 +10627,19 @@
         <v>162</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>540</v>
+        <v>209</v>
       </c>
       <c r="C452" t="s">
-        <v>196</v>
-      </c>
-      <c r="E452" t="s">
-        <v>537</v>
-      </c>
-      <c r="F452" t="s">
-        <v>549</v>
+        <v>199</v>
+      </c>
+      <c r="D452">
+        <v>1</v>
+      </c>
+      <c r="E452" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F452" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
@@ -10586,16 +10647,19 @@
         <v>162</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D453" t="s">
-        <v>144</v>
-      </c>
-      <c r="E453" t="s">
-        <v>331</v>
-      </c>
-      <c r="F453" t="s">
-        <v>344</v>
+        <v>209</v>
+      </c>
+      <c r="C453" t="s">
+        <v>204</v>
+      </c>
+      <c r="D453">
+        <v>1</v>
+      </c>
+      <c r="E453" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F453" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.35">
@@ -10603,19 +10667,16 @@
         <v>162</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>335</v>
+        <v>209</v>
       </c>
       <c r="C454" t="s">
-        <v>336</v>
-      </c>
-      <c r="D454">
-        <v>1</v>
-      </c>
-      <c r="E454" t="s">
-        <v>331</v>
-      </c>
-      <c r="F454" t="s">
-        <v>337</v>
+        <v>449</v>
+      </c>
+      <c r="E454" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F454" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.35">
@@ -10623,19 +10684,16 @@
         <v>162</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C455" t="s">
-        <v>102</v>
-      </c>
-      <c r="D455">
-        <v>1</v>
+        <v>207</v>
+      </c>
+      <c r="D455" t="s">
+        <v>144</v>
       </c>
       <c r="E455" t="s">
-        <v>331</v>
+        <v>193</v>
       </c>
       <c r="F455" t="s">
-        <v>344</v>
+        <v>206</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.35">
@@ -10643,19 +10701,19 @@
         <v>162</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>335</v>
+        <v>207</v>
       </c>
       <c r="C456" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D456">
         <v>1</v>
       </c>
       <c r="E456" t="s">
-        <v>331</v>
+        <v>193</v>
       </c>
       <c r="F456" t="s">
-        <v>334</v>
+        <v>208</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
@@ -10663,19 +10721,16 @@
         <v>162</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C457" t="s">
-        <v>338</v>
-      </c>
-      <c r="D457">
-        <v>1</v>
+        <v>373</v>
+      </c>
+      <c r="D457" t="s">
+        <v>144</v>
       </c>
       <c r="E457" t="s">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="F457" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.35">
@@ -10683,16 +10738,16 @@
         <v>162</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>333</v>
+        <v>540</v>
       </c>
       <c r="D458" t="s">
         <v>144</v>
       </c>
       <c r="E458" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F458" t="s">
-        <v>334</v>
+        <v>539</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.35">
@@ -10700,19 +10755,16 @@
         <v>162</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>333</v>
+        <v>540</v>
       </c>
       <c r="C459" t="s">
-        <v>340</v>
-      </c>
-      <c r="D459">
-        <v>1</v>
+        <v>552</v>
       </c>
       <c r="E459" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F459" t="s">
-        <v>341</v>
+        <v>549</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.35">
@@ -10720,19 +10772,16 @@
         <v>162</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>333</v>
+        <v>540</v>
       </c>
       <c r="C460" t="s">
-        <v>100</v>
-      </c>
-      <c r="D460">
-        <v>1</v>
+        <v>553</v>
       </c>
       <c r="E460" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F460" t="s">
-        <v>334</v>
+        <v>549</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.35">
@@ -10740,19 +10789,16 @@
         <v>162</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>333</v>
+        <v>540</v>
       </c>
       <c r="C461" t="s">
-        <v>342</v>
-      </c>
-      <c r="D461">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="E461" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F461" t="s">
-        <v>343</v>
+        <v>549</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.35">
@@ -10760,10 +10806,10 @@
         <v>162</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>442</v>
+        <v>335</v>
       </c>
       <c r="D462" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E462" t="s">
         <v>331</v>
@@ -10777,16 +10823,19 @@
         <v>162</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D463" t="s">
-        <v>128</v>
+        <v>335</v>
+      </c>
+      <c r="C463" t="s">
+        <v>336</v>
+      </c>
+      <c r="D463">
+        <v>1</v>
       </c>
       <c r="E463" t="s">
-        <v>481</v>
+        <v>331</v>
       </c>
       <c r="F463" t="s">
-        <v>64</v>
+        <v>337</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.35">
@@ -10794,16 +10843,19 @@
         <v>162</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D464" t="s">
-        <v>128</v>
+        <v>335</v>
+      </c>
+      <c r="C464" t="s">
+        <v>102</v>
+      </c>
+      <c r="D464">
+        <v>1</v>
       </c>
       <c r="E464" t="s">
-        <v>193</v>
+        <v>331</v>
       </c>
       <c r="F464" t="s">
-        <v>206</v>
+        <v>344</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
@@ -10811,16 +10863,19 @@
         <v>162</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="D465" t="s">
-        <v>144</v>
+        <v>335</v>
+      </c>
+      <c r="C465" t="s">
+        <v>115</v>
+      </c>
+      <c r="D465">
+        <v>1</v>
       </c>
       <c r="E465" t="s">
-        <v>497</v>
+        <v>331</v>
       </c>
       <c r="F465" t="s">
-        <v>503</v>
+        <v>334</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.35">
@@ -10828,19 +10883,19 @@
         <v>162</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>502</v>
+        <v>335</v>
       </c>
       <c r="C466" t="s">
-        <v>415</v>
+        <v>338</v>
       </c>
       <c r="D466">
         <v>1</v>
       </c>
       <c r="E466" t="s">
-        <v>532</v>
+        <v>331</v>
       </c>
       <c r="F466" t="s">
-        <v>533</v>
+        <v>339</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.35">
@@ -10848,16 +10903,16 @@
         <v>162</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C467" t="s">
-        <v>506</v>
+        <v>333</v>
+      </c>
+      <c r="D467" t="s">
+        <v>144</v>
       </c>
       <c r="E467" t="s">
-        <v>497</v>
+        <v>331</v>
       </c>
       <c r="F467" t="s">
-        <v>507</v>
+        <v>334</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.35">
@@ -10865,16 +10920,19 @@
         <v>162</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>502</v>
+        <v>333</v>
       </c>
       <c r="C468" t="s">
-        <v>531</v>
+        <v>340</v>
+      </c>
+      <c r="D468">
+        <v>1</v>
       </c>
       <c r="E468" t="s">
-        <v>497</v>
+        <v>331</v>
       </c>
       <c r="F468" t="s">
-        <v>527</v>
+        <v>341</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
@@ -10882,16 +10940,19 @@
         <v>162</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="D469" t="s">
-        <v>345</v>
+        <v>333</v>
+      </c>
+      <c r="C469" t="s">
+        <v>100</v>
+      </c>
+      <c r="D469">
+        <v>1</v>
       </c>
       <c r="E469" t="s">
-        <v>532</v>
+        <v>331</v>
       </c>
       <c r="F469" t="s">
-        <v>533</v>
+        <v>334</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
@@ -10899,15 +10960,174 @@
         <v>162</v>
       </c>
       <c r="B470" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C470" t="s">
+        <v>342</v>
+      </c>
+      <c r="D470">
+        <v>1</v>
+      </c>
+      <c r="E470" t="s">
+        <v>331</v>
+      </c>
+      <c r="F470" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A471" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D471" t="s">
+        <v>128</v>
+      </c>
+      <c r="E471" t="s">
+        <v>331</v>
+      </c>
+      <c r="F471" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A472" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D472" t="s">
+        <v>128</v>
+      </c>
+      <c r="E472" t="s">
+        <v>481</v>
+      </c>
+      <c r="F472" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A473" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D473" t="s">
+        <v>128</v>
+      </c>
+      <c r="E473" t="s">
+        <v>193</v>
+      </c>
+      <c r="F473" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A474" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D474" t="s">
+        <v>144</v>
+      </c>
+      <c r="E474" t="s">
+        <v>497</v>
+      </c>
+      <c r="F474" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A475" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C475" t="s">
+        <v>415</v>
+      </c>
+      <c r="D475">
+        <v>1</v>
+      </c>
+      <c r="E475" t="s">
+        <v>532</v>
+      </c>
+      <c r="F475" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A476" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C476" t="s">
+        <v>506</v>
+      </c>
+      <c r="E476" t="s">
+        <v>497</v>
+      </c>
+      <c r="F476" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A477" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C477" t="s">
+        <v>531</v>
+      </c>
+      <c r="E477" t="s">
+        <v>497</v>
+      </c>
+      <c r="F477" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A478" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D478" t="s">
+        <v>345</v>
+      </c>
+      <c r="E478" t="s">
+        <v>532</v>
+      </c>
+      <c r="F478" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A479" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B479" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="D470" t="s">
+      <c r="D479" t="s">
         <v>144</v>
       </c>
-      <c r="E470" t="s">
+      <c r="E479" t="s">
         <v>497</v>
       </c>
-      <c r="F470" t="s">
+      <c r="F479" t="s">
         <v>529</v>
       </c>
     </row>

--- a/snippet-extractor-metadata/word.xlsx
+++ b/snippet-extractor-metadata/word.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5E045A-282C-4500-A6F0-4F2B11073174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6F834F-7E2F-41F4-AFC1-C8258BC9E2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2426" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2431" uniqueCount="634">
   <si>
     <t>Class</t>
   </si>
@@ -1919,6 +1919,9 @@
   </si>
   <si>
     <t>countLevel1Items</t>
+  </si>
+  <si>
+    <t>ExportOptimizeFor</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1975,10 +1978,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2034,8 +2033,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F485" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="A1:F485" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F486" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:F486" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{1DA12987-AB2C-4056-A643-B1229DC856C5}" name="Package" dataDxfId="4"/>
     <tableColumn id="1" xr3:uid="{0CD83AD1-F92A-407D-8460-4E881461FD01}" name="Class" dataDxfId="3"/>
@@ -2345,7 +2344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F485"/>
+  <dimension ref="A1:F486"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25.08984375" bestFit="1" customWidth="1"/>
@@ -2846,16 +2845,16 @@
       <c r="B28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" t="s">
         <v>623</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" t="s">
         <v>624</v>
       </c>
     </row>
@@ -6522,18 +6521,18 @@
       <c r="A229" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C229" s="2"/>
-      <c r="D229" s="2" t="s">
-        <v>144</v>
+      <c r="B229" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="C229" s="4"/>
+      <c r="D229" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>136</v>
+        <v>600</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
@@ -6543,17 +6542,15 @@
       <c r="B230" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D230" s="1">
-        <v>1</v>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F230" s="3" t="s">
-        <v>290</v>
+      <c r="F230" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
@@ -6564,7 +6561,7 @@
         <v>132</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D231" s="1">
         <v>1</v>
@@ -6573,7 +6570,7 @@
         <v>163</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.35">
@@ -6584,7 +6581,7 @@
         <v>132</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>287</v>
+        <v>48</v>
       </c>
       <c r="D232" s="1">
         <v>1</v>
@@ -6597,38 +6594,40 @@
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
+      <c r="A233" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C233" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D233" s="2"/>
+      <c r="C233" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D233" s="1">
+        <v>1</v>
+      </c>
       <c r="E233" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F233" s="2" t="s">
-        <v>136</v>
+      <c r="F233" s="3" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A234" s="1" t="s">
+      <c r="A234" t="s">
         <v>162</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D234" s="1"/>
+      <c r="C234" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D234" s="2"/>
       <c r="E234" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F234" s="3" t="s">
+      <c r="F234" s="2" t="s">
         <v>136</v>
       </c>
     </row>
@@ -6639,33 +6638,33 @@
       <c r="B235" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C235" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D235" s="2"/>
+      <c r="C235" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D235" s="1"/>
       <c r="E235" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F235" s="2" t="s">
-        <v>289</v>
+      <c r="F235" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A236" t="s">
+      <c r="A236" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.35">
@@ -6676,25 +6675,25 @@
         <v>132</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A238" s="1" t="s">
+      <c r="A238" t="s">
         <v>162</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" s="2" t="s">
@@ -6705,21 +6704,21 @@
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
+      <c r="A239" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C239" s="2"/>
-      <c r="D239" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D239" s="2"/>
       <c r="E239" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.35">
@@ -6729,17 +6728,15 @@
       <c r="B240" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C240" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D240" s="2">
-        <v>1</v>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
@@ -6750,32 +6747,34 @@
         <v>139</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D241" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="D241" s="2">
+        <v>1</v>
+      </c>
       <c r="E241" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A242" s="1" t="s">
+      <c r="A242" t="s">
         <v>162</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C242" s="2"/>
-      <c r="D242" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D242" s="2"/>
       <c r="E242" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
@@ -6783,7 +6782,7 @@
         <v>162</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>285</v>
+        <v>410</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2" t="s">
@@ -6793,7 +6792,7 @@
         <v>163</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>284</v>
+        <v>136</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
@@ -6801,17 +6800,17 @@
         <v>162</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>557</v>
+        <v>285</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>555</v>
+        <v>163</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>560</v>
+        <v>284</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
@@ -6819,53 +6818,53 @@
         <v>162</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>423</v>
+        <v>557</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>424</v>
+        <v>555</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>86</v>
+        <v>560</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A246" t="s">
+      <c r="A246" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>149</v>
+        <v>423</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A247" s="1" t="s">
+      <c r="A247" t="s">
         <v>162</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
@@ -6873,55 +6872,55 @@
         <v>162</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>525</v>
+        <v>173</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E248" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A249" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E249" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F248" s="2" t="s">
+      <c r="F249" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A249" t="s">
-        <v>162</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D249" s="2">
-        <v>1</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A250" s="1" t="s">
+      <c r="A250" t="s">
         <v>162</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C250" s="2"/>
-      <c r="D250" s="2" t="s">
-        <v>144</v>
+      <c r="C250" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D250" s="2">
+        <v>1</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
@@ -6931,15 +6930,15 @@
       <c r="B251" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C251" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D251" s="2"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E251" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
@@ -6947,12 +6946,12 @@
         <v>162</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C252" s="2"/>
-      <c r="D252" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D252" s="2"/>
       <c r="E252" s="2" t="s">
         <v>70</v>
       </c>
@@ -6965,53 +6964,53 @@
         <v>162</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>347</v>
+        <v>177</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="2" t="s">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>348</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A254" t="s">
+      <c r="A254" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>154</v>
+        <v>347</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>140</v>
+        <v>235</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>155</v>
+        <v>348</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A255" s="1" t="s">
+      <c r="A255" t="s">
         <v>162</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>510</v>
+        <v>154</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="2" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>537</v>
+        <v>140</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>511</v>
+        <v>155</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.35">
@@ -7019,17 +7018,17 @@
         <v>162</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>215</v>
+        <v>510</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>57</v>
+        <v>537</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>58</v>
+        <v>511</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.35">
@@ -7039,11 +7038,9 @@
       <c r="B257" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C257" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D257" s="2">
-        <v>1</v>
+      <c r="C257" s="2"/>
+      <c r="D257" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>57</v>
@@ -7060,16 +7057,16 @@
         <v>215</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="D258" s="2">
         <v>1</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>220</v>
+        <v>58</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.35">
@@ -7080,7 +7077,7 @@
         <v>215</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D259" s="2">
         <v>1</v>
@@ -7100,14 +7097,16 @@
         <v>215</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D260" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="D260" s="2">
+        <v>1</v>
+      </c>
       <c r="E260" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.35">
@@ -7118,7 +7117,7 @@
         <v>215</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" s="2" t="s">
@@ -7133,17 +7132,17 @@
         <v>162</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C262" s="2"/>
-      <c r="D262" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D262" s="2"/>
       <c r="E262" s="2" t="s">
-        <v>481</v>
+        <v>219</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>64</v>
+        <v>300</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.35">
@@ -7151,17 +7150,17 @@
         <v>162</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>222</v>
+        <v>480</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>219</v>
+        <v>481</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>220</v>
+        <v>64</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.35">
@@ -7169,73 +7168,73 @@
         <v>162</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>425</v>
+        <v>222</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B265" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="C265" s="6"/>
+      <c r="B265" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C265" s="2"/>
       <c r="D265" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E265" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="F265" s="6" t="s">
-        <v>624</v>
+      <c r="E265" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B266" s="4" t="s">
+      <c r="B266" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C266" s="6" t="s">
-        <v>628</v>
-      </c>
-      <c r="D266" s="2">
-        <v>1</v>
-      </c>
-      <c r="E266" s="6" t="s">
+      <c r="C266" s="2"/>
+      <c r="D266" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="F266" s="6" t="s">
-        <v>630</v>
+      <c r="F266" s="2" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B267" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="C267" s="6"/>
-      <c r="D267" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E267" s="6" t="s">
+      <c r="B267" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D267" s="2">
+        <v>1</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="F267" s="6" t="s">
-        <v>629</v>
+      <c r="F267" s="2" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.35">
@@ -7243,17 +7242,17 @@
         <v>162</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>216</v>
+        <v>627</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>57</v>
+        <v>623</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>58</v>
+        <v>629</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.35">
@@ -7263,10 +7262,10 @@
       <c r="B269" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C269" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D269" s="2"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E269" s="2" t="s">
         <v>57</v>
       </c>
@@ -7279,17 +7278,17 @@
         <v>162</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C270" s="2"/>
-      <c r="D270" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D270" s="2"/>
       <c r="E270" s="2" t="s">
-        <v>481</v>
+        <v>57</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.35">
@@ -7297,7 +7296,7 @@
         <v>162</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2" t="s">
@@ -7315,17 +7314,17 @@
         <v>162</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>225</v>
+        <v>484</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>219</v>
+        <v>481</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>300</v>
+        <v>64</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.35">
@@ -7333,7 +7332,7 @@
         <v>162</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2" t="s">
@@ -7343,7 +7342,7 @@
         <v>219</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.35">
@@ -7351,17 +7350,17 @@
         <v>162</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>485</v>
+        <v>224</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>481</v>
+        <v>219</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>64</v>
+        <v>220</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.35">
@@ -7369,35 +7368,35 @@
         <v>162</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>226</v>
+        <v>485</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>227</v>
+        <v>481</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>228</v>
+        <v>64</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A276" t="s">
+      <c r="A276" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>91</v>
+        <v>226</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.35">
@@ -7407,17 +7406,15 @@
       <c r="B277" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C277" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D277" s="2">
-        <v>1</v>
+      <c r="C277" s="2"/>
+      <c r="D277" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
@@ -7428,7 +7425,7 @@
         <v>91</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D278" s="2">
         <v>1</v>
@@ -7437,7 +7434,7 @@
         <v>146</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.35">
@@ -7448,14 +7445,16 @@
         <v>91</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D279" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="D279" s="2">
+        <v>1</v>
+      </c>
       <c r="E279" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
@@ -7466,14 +7465,14 @@
         <v>91</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.35">
@@ -7484,14 +7483,14 @@
         <v>91</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
@@ -7499,17 +7498,17 @@
         <v>162</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C282" s="2"/>
-      <c r="D282" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D282" s="2"/>
       <c r="E282" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.35">
@@ -7519,11 +7518,9 @@
       <c r="B283" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C283" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D283" s="2">
-        <v>1</v>
+      <c r="C283" s="2"/>
+      <c r="D283" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>146</v>
@@ -7536,69 +7533,71 @@
       <c r="A284" t="s">
         <v>162</v>
       </c>
-      <c r="B284" t="s">
-        <v>156</v>
-      </c>
-      <c r="D284" t="s">
-        <v>128</v>
+      <c r="B284" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D284" s="2">
+        <v>1</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A285" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B285" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="C285" s="5"/>
+      <c r="A285" t="s">
+        <v>162</v>
+      </c>
+      <c r="B285" t="s">
+        <v>156</v>
+      </c>
       <c r="D285" t="s">
         <v>128</v>
       </c>
-      <c r="E285" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="F285" s="6" t="s">
-        <v>632</v>
+      <c r="E285" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F285" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A286" t="s">
+      <c r="A286" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D286" t="s">
         <v>128</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A287" s="1" t="s">
+      <c r="A287" t="s">
         <v>162</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>411</v>
+        <v>622</v>
       </c>
       <c r="D287" t="s">
         <v>128</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>374</v>
+        <v>615</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>375</v>
+        <v>618</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.35">
@@ -7606,16 +7605,16 @@
         <v>162</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>499</v>
+        <v>411</v>
       </c>
       <c r="D288" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>497</v>
+        <v>374</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>498</v>
+        <v>375</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.35">
@@ -7625,11 +7624,8 @@
       <c r="B289" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C289" t="s">
-        <v>115</v>
-      </c>
-      <c r="D289">
-        <v>1</v>
+      <c r="D289" t="s">
+        <v>144</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>497</v>
@@ -7646,13 +7642,16 @@
         <v>499</v>
       </c>
       <c r="C290" t="s">
-        <v>500</v>
+        <v>115</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.35">
@@ -7660,16 +7659,16 @@
         <v>162</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="D291" t="s">
-        <v>144</v>
+        <v>499</v>
+      </c>
+      <c r="C291" t="s">
+        <v>500</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
@@ -7677,7 +7676,7 @@
         <v>162</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="D292" t="s">
         <v>144</v>
@@ -7686,7 +7685,7 @@
         <v>497</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
@@ -7696,8 +7695,8 @@
       <c r="B293" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C293" t="s">
-        <v>508</v>
+      <c r="D293" t="s">
+        <v>144</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>497</v>
@@ -7714,13 +7713,13 @@
         <v>504</v>
       </c>
       <c r="C294" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.35">
@@ -7728,34 +7727,33 @@
         <v>162</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="D295" t="s">
-        <v>144</v>
+        <v>504</v>
+      </c>
+      <c r="C295" t="s">
+        <v>509</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F295" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A296" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D296" t="s">
+        <v>144</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F296" s="2" t="s">
         <v>527</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A296" t="s">
-        <v>162</v>
-      </c>
-      <c r="B296" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C296" s="2"/>
-      <c r="D296" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E296" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.35">
@@ -7765,77 +7763,75 @@
       <c r="B297" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C297" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D297" s="2">
-        <v>1</v>
+      <c r="C297" s="2"/>
+      <c r="D297" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A298" s="1" t="s">
+      <c r="A298" t="s">
         <v>162</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>360</v>
+        <v>115</v>
       </c>
       <c r="D298" s="2">
         <v>1</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>360</v>
+        <v>12</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A299" t="s">
+      <c r="A299" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>29</v>
+        <v>360</v>
       </c>
       <c r="D299" s="2">
         <v>1</v>
       </c>
-      <c r="E299" s="2" t="s">
-        <v>75</v>
+      <c r="E299" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>28</v>
+        <v>360</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A300" s="1" t="s">
+      <c r="A300" t="s">
         <v>162</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D300" s="2">
         <v>1</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.35">
@@ -7846,36 +7842,36 @@
         <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>556</v>
+        <v>36</v>
       </c>
       <c r="D301" s="2">
         <v>1</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>570</v>
+        <v>43</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A302" t="s">
+      <c r="A302" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>13</v>
+        <v>556</v>
       </c>
       <c r="D302" s="2">
         <v>1</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.35">
@@ -7886,16 +7882,16 @@
         <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>512</v>
+        <v>13</v>
       </c>
       <c r="D303" s="2">
         <v>1</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>537</v>
+        <v>81</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>523</v>
+        <v>22</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.35">
@@ -7906,16 +7902,16 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>48</v>
+        <v>512</v>
       </c>
       <c r="D304" s="2">
         <v>1</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>71</v>
+        <v>537</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>47</v>
+        <v>523</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.35">
@@ -7935,7 +7931,7 @@
         <v>71</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
@@ -7945,17 +7941,17 @@
       <c r="B306" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C306" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D306" s="1">
+      <c r="C306" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D306" s="2">
         <v>1</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
@@ -7965,17 +7961,17 @@
       <c r="B307" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C307" s="2" t="s">
+      <c r="C307" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D307" s="2">
+      <c r="D307" s="1">
         <v>1</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
@@ -7986,16 +7982,16 @@
         <v>10</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="D308" s="2">
         <v>1</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.35">
@@ -8006,16 +8002,16 @@
         <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D309" s="2">
         <v>1</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
@@ -8026,14 +8022,16 @@
         <v>10</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D310" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D310" s="2">
+        <v>1</v>
+      </c>
       <c r="E310" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.35">
@@ -8044,14 +8042,14 @@
         <v>10</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.35">
@@ -8062,86 +8060,86 @@
         <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A313" s="1" t="s">
+      <c r="A313" t="s">
         <v>162</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A314" s="3" t="s">
+      <c r="A314" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A315" t="s">
+      <c r="A315" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>17</v>
+        <v>381</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>17</v>
+        <v>382</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A316" s="1" t="s">
+      <c r="A316" t="s">
         <v>162</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>280</v>
+        <v>17</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" s="2" t="s">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>279</v>
+        <v>17</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
@@ -8152,32 +8150,32 @@
         <v>10</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" s="2" t="s">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A318" t="s">
+      <c r="A318" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B318" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>8</v>
+        <v>238</v>
       </c>
       <c r="D318" s="2"/>
-      <c r="E318" s="1" t="s">
-        <v>79</v>
+      <c r="E318" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>11</v>
+        <v>240</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
@@ -8188,14 +8186,14 @@
         <v>10</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" s="1" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
@@ -8213,25 +8211,25 @@
         <v>350</v>
       </c>
       <c r="F320" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>162</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D321" s="2"/>
+      <c r="E321" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F321" s="2" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A321" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B321" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C321" s="2"/>
-      <c r="D321" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E321" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.35">
@@ -8249,7 +8247,7 @@
         <v>318</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>319</v>
+        <v>267</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
@@ -8257,17 +8255,17 @@
         <v>162</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" s="2" t="s">
         <v>345</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>267</v>
+        <v>319</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
@@ -8285,65 +8283,63 @@
         <v>322</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A325" t="s">
+      <c r="A325" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>190</v>
+        <v>329</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E325" s="2" t="s">
-        <v>70</v>
+        <v>345</v>
+      </c>
+      <c r="E325" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>175</v>
+        <v>324</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A326" s="1" t="s">
+      <c r="A326" t="s">
         <v>162</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C326" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D326" s="2">
-        <v>1</v>
-      </c>
-      <c r="E326" s="1" t="s">
-        <v>350</v>
+      <c r="C326" s="2"/>
+      <c r="D326" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>353</v>
+        <v>175</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A327" t="s">
+      <c r="A327" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="D327" s="2">
         <v>1</v>
       </c>
-      <c r="E327" s="2" t="s">
-        <v>70</v>
+      <c r="E327" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>175</v>
+        <v>353</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.35">
@@ -8354,14 +8350,16 @@
         <v>190</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D328" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="D328" s="2">
+        <v>1</v>
+      </c>
       <c r="E328" s="2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -8369,17 +8367,17 @@
         <v>162</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C329" s="2"/>
-      <c r="D329" s="2" t="s">
-        <v>345</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D329" s="2"/>
       <c r="E329" s="2" t="s">
-        <v>323</v>
+        <v>57</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>267</v>
+        <v>58</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
@@ -8397,25 +8395,25 @@
         <v>323</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>325</v>
+        <v>267</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A331" s="1" t="s">
+      <c r="A331" t="s">
         <v>162</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
@@ -8425,10 +8423,10 @@
       <c r="B332" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C332" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D332" s="2"/>
+      <c r="C332" s="2"/>
+      <c r="D332" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E332" s="2" t="s">
         <v>269</v>
       </c>
@@ -8444,7 +8442,7 @@
         <v>281</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" s="2" t="s">
@@ -8459,17 +8457,17 @@
         <v>162</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C334" s="2"/>
-      <c r="D334" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D334" s="2"/>
       <c r="E334" s="2" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>445</v>
+        <v>294</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
@@ -8479,17 +8477,15 @@
       <c r="B335" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C335" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D335" s="2">
-        <v>1</v>
+      <c r="C335" s="2"/>
+      <c r="D335" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>228</v>
+        <v>445</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
@@ -8500,36 +8496,36 @@
         <v>5</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>492</v>
+        <v>229</v>
       </c>
       <c r="D336" s="2">
         <v>1</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>12</v>
+        <v>228</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A337" t="s">
+      <c r="A337" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C337" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D337" s="1">
+      <c r="C337" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D337" s="2">
         <v>1</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.35">
@@ -8540,16 +8536,16 @@
         <v>5</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>395</v>
+        <v>107</v>
       </c>
       <c r="D338" s="1">
         <v>1</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>393</v>
+        <v>145</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>427</v>
+        <v>108</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
@@ -8560,16 +8556,16 @@
         <v>5</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>115</v>
+        <v>395</v>
       </c>
       <c r="D339" s="1">
         <v>1</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>494</v>
+        <v>393</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
@@ -8580,16 +8576,16 @@
         <v>5</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D340" s="1">
         <v>1</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>147</v>
+        <v>494</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>121</v>
+        <v>462</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.35">
@@ -8600,16 +8596,16 @@
         <v>5</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="D341" s="1">
         <v>1</v>
       </c>
-      <c r="E341" s="1" t="s">
-        <v>79</v>
+      <c r="E341" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.35">
@@ -8620,16 +8616,16 @@
         <v>5</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="D342" s="1">
         <v>1</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.35">
@@ -8640,56 +8636,56 @@
         <v>5</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="D343" s="1">
         <v>1</v>
       </c>
-      <c r="E343" s="2" t="s">
-        <v>82</v>
+      <c r="E343" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A344" s="1" t="s">
+      <c r="A344" t="s">
         <v>162</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>283</v>
+        <v>36</v>
       </c>
       <c r="D344" s="1">
         <v>1</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>284</v>
+        <v>35</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A345" t="s">
+      <c r="A345" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>88</v>
+        <v>283</v>
       </c>
       <c r="D345" s="1">
         <v>1</v>
       </c>
-      <c r="E345" s="1" t="s">
-        <v>146</v>
+      <c r="E345" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>88</v>
+        <v>284</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.35">
@@ -8700,16 +8696,16 @@
         <v>5</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>313</v>
+        <v>88</v>
       </c>
       <c r="D346" s="1">
         <v>1</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>537</v>
+        <v>146</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>521</v>
+        <v>88</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
@@ -8729,7 +8725,7 @@
         <v>537</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.35">
@@ -8740,16 +8736,16 @@
         <v>5</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>556</v>
+        <v>313</v>
       </c>
       <c r="D348" s="1">
         <v>1</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.35">
@@ -8760,16 +8756,16 @@
         <v>5</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>512</v>
+        <v>556</v>
       </c>
       <c r="D349" s="1">
         <v>1</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>511</v>
+        <v>561</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
@@ -8780,14 +8776,16 @@
         <v>5</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D350" s="1"/>
+        <v>512</v>
+      </c>
+      <c r="D350" s="1">
+        <v>1</v>
+      </c>
       <c r="E350" s="1" t="s">
-        <v>146</v>
+        <v>537</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>96</v>
+        <v>511</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
@@ -8797,32 +8795,33 @@
       <c r="B351" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C351" s="4" t="s">
-        <v>625</v>
+      <c r="C351" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="D351" s="1"/>
-      <c r="E351" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="F351" s="6" t="s">
-        <v>624</v>
+      <c r="E351" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F351" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A352" s="1" t="s">
+      <c r="A352" t="s">
         <v>162</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C352" t="s">
-        <v>428</v>
-      </c>
-      <c r="E352" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F352" t="s">
-        <v>422</v>
+      <c r="C352" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D352" s="1"/>
+      <c r="E352" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="F352" s="2" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.35">
@@ -8832,15 +8831,14 @@
       <c r="B353" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C353" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D353" s="2"/>
+      <c r="C353" t="s">
+        <v>428</v>
+      </c>
       <c r="E353" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F353" s="2" t="s">
-        <v>239</v>
+        <v>393</v>
+      </c>
+      <c r="F353" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.35">
@@ -8848,53 +8846,53 @@
         <v>162</v>
       </c>
       <c r="B354" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D354" s="2"/>
+      <c r="E354" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F354" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A355" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C354" s="2"/>
-      <c r="D354" s="2" t="s">
+      <c r="C355" s="2"/>
+      <c r="D355" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E354" s="2" t="s">
+      <c r="E355" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F354" s="2" t="s">
+      <c r="F355" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A355" t="s">
-        <v>162</v>
-      </c>
-      <c r="B355" s="1" t="s">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>162</v>
+      </c>
+      <c r="B356" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C355" s="1"/>
-      <c r="D355" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F355" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A356" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="C356" s="1"/>
       <c r="D356" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>570</v>
+        <v>79</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>576</v>
+        <v>12</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.35">
@@ -8902,7 +8900,7 @@
         <v>162</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C357" s="1"/>
       <c r="D357" s="1" t="s">
@@ -8912,7 +8910,7 @@
         <v>570</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.35">
@@ -8920,7 +8918,7 @@
         <v>162</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C358" s="1"/>
       <c r="D358" s="1" t="s">
@@ -8930,7 +8928,7 @@
         <v>570</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
@@ -8938,17 +8936,17 @@
         <v>162</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>418</v>
+        <v>579</v>
       </c>
       <c r="C359" s="1"/>
       <c r="D359" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>413</v>
+        <v>570</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>414</v>
+        <v>576</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.35">
@@ -8956,37 +8954,35 @@
         <v>162</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>534</v>
+        <v>418</v>
       </c>
       <c r="C360" s="1"/>
       <c r="D360" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E360" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F360" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A361" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C361" s="1"/>
+      <c r="D361" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E361" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F360" s="2" t="s">
+      <c r="F361" s="2" t="s">
         <v>533</v>
-      </c>
-    </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A361" t="s">
-        <v>162</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C361" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D361" s="2">
-        <v>2</v>
-      </c>
-      <c r="E361" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F361" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.35">
@@ -8996,17 +8992,17 @@
       <c r="B362" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C362" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D362" s="1">
-        <v>1</v>
+      <c r="C362" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D362" s="2">
+        <v>2</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.35">
@@ -9016,15 +9012,17 @@
       <c r="B363" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C363" s="1"/>
-      <c r="D363" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E363" s="1" t="s">
-        <v>140</v>
+      <c r="C363" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D363" s="1">
+        <v>1</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
@@ -9032,17 +9030,17 @@
         <v>162</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C364" s="2"/>
-      <c r="D364" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C364" s="1"/>
+      <c r="D364" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E364" s="2" t="s">
+      <c r="E364" s="1" t="s">
         <v>140</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
@@ -9050,17 +9048,17 @@
         <v>162</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>609</v>
+        <v>142</v>
       </c>
       <c r="C365" s="2"/>
       <c r="D365" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>606</v>
+        <v>140</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>608</v>
+        <v>143</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.35">
@@ -9070,17 +9068,15 @@
       <c r="B366" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C366" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="D366" s="2">
-        <v>1</v>
+      <c r="C366" s="2"/>
+      <c r="D366" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.35">
@@ -9091,7 +9087,7 @@
         <v>609</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D367" s="2">
         <v>1</v>
@@ -9100,7 +9096,7 @@
         <v>615</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
@@ -9111,16 +9107,16 @@
         <v>609</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D368" s="2">
         <v>1</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
@@ -9128,35 +9124,37 @@
         <v>162</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="C369" s="2"/>
-      <c r="D369" s="2" t="s">
-        <v>345</v>
+        <v>609</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D369" s="2">
+        <v>1</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>606</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A370" s="1" t="s">
+      <c r="A370" t="s">
         <v>162</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C370" s="2"/>
       <c r="D370" s="2" t="s">
         <v>345</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
@@ -9164,7 +9162,7 @@
         <v>162</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C371" s="2"/>
       <c r="D371" s="2" t="s">
@@ -9174,43 +9172,43 @@
         <v>615</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A372" t="s">
+      <c r="A372" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>159</v>
+        <v>617</v>
       </c>
       <c r="C372" s="2"/>
       <c r="D372" s="2" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>71</v>
+        <v>615</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>49</v>
+        <v>620</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A373" s="1" t="s">
+      <c r="A373" t="s">
         <v>162</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>296</v>
+        <v>159</v>
       </c>
       <c r="C373" s="2"/>
       <c r="D373" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>164</v>
+        <v>71</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>168</v>
+        <v>49</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.35">
@@ -9220,10 +9218,10 @@
       <c r="B374" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C374" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D374" s="2"/>
+      <c r="C374" s="2"/>
+      <c r="D374" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E374" s="2" t="s">
         <v>164</v>
       </c>
@@ -9239,7 +9237,7 @@
         <v>296</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" s="2" t="s">
@@ -9254,17 +9252,17 @@
         <v>162</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C376" s="2"/>
-      <c r="D376" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D376" s="2"/>
       <c r="E376" s="2" t="s">
         <v>164</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.35">
@@ -9274,17 +9272,15 @@
       <c r="B377" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C377" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D377" s="2">
-        <v>1</v>
+      <c r="C377" s="2"/>
+      <c r="D377" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>164</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -9295,14 +9291,16 @@
         <v>167</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D378" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="D378" s="2">
+        <v>1</v>
+      </c>
       <c r="E378" s="2" t="s">
         <v>164</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.35">
@@ -9310,17 +9308,17 @@
         <v>162</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C379" s="2"/>
-      <c r="D379" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D379" s="2"/>
       <c r="E379" s="2" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>489</v>
+        <v>169</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.35">
@@ -9328,11 +9326,11 @@
         <v>162</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C380" s="2"/>
       <c r="D380" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>269</v>
@@ -9346,17 +9344,17 @@
         <v>162</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="C381" s="2"/>
       <c r="D381" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>537</v>
+        <v>269</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>519</v>
+        <v>489</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.35">
@@ -9366,17 +9364,15 @@
       <c r="B382" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C382" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D382" s="2">
-        <v>1</v>
+      <c r="C382" s="2"/>
+      <c r="D382" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.35">
@@ -9387,16 +9383,16 @@
         <v>516</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>583</v>
+        <v>97</v>
       </c>
       <c r="D383" s="2">
         <v>1</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.35">
@@ -9407,7 +9403,7 @@
         <v>516</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D384" s="2">
         <v>1</v>
@@ -9427,7 +9423,7 @@
         <v>516</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D385" s="2">
         <v>1</v>
@@ -9436,7 +9432,7 @@
         <v>570</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.35">
@@ -9447,7 +9443,7 @@
         <v>516</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D386" s="2">
         <v>1</v>
@@ -9467,7 +9463,7 @@
         <v>516</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>48</v>
+        <v>588</v>
       </c>
       <c r="D387" s="2">
         <v>1</v>
@@ -9476,7 +9472,7 @@
         <v>570</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.35">
@@ -9487,14 +9483,16 @@
         <v>516</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D388" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D388" s="2">
+        <v>1</v>
+      </c>
       <c r="E388" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>520</v>
+        <v>571</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
@@ -9505,14 +9503,14 @@
         <v>516</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>597</v>
+        <v>104</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" s="2" t="s">
-        <v>595</v>
+        <v>537</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>596</v>
+        <v>520</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.35">
@@ -9523,14 +9521,14 @@
         <v>516</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>563</v>
+        <v>597</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" s="2" t="s">
-        <v>555</v>
+        <v>595</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>564</v>
+        <v>596</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.35">
@@ -9541,14 +9539,14 @@
         <v>516</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" s="2" t="s">
         <v>555</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.35">
@@ -9559,14 +9557,14 @@
         <v>516</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>593</v>
+        <v>558</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.35">
@@ -9577,14 +9575,14 @@
         <v>516</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.35">
@@ -9595,14 +9593,14 @@
         <v>516</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.35">
@@ -9613,14 +9611,14 @@
         <v>516</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.35">
@@ -9631,14 +9629,14 @@
         <v>516</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.35">
@@ -9649,14 +9647,14 @@
         <v>516</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.35">
@@ -9667,14 +9665,14 @@
         <v>516</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>538</v>
+        <v>586</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.35">
@@ -9685,14 +9683,14 @@
         <v>516</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D399" s="2"/>
       <c r="E399" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.35">
@@ -9703,14 +9701,14 @@
         <v>516</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>94</v>
+        <v>541</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.35">
@@ -9718,17 +9716,17 @@
         <v>162</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C401" s="2"/>
-      <c r="D401" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D401" s="2"/>
       <c r="E401" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>549</v>
+        <v>514</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.35">
@@ -9736,17 +9734,17 @@
         <v>162</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>513</v>
+        <v>548</v>
       </c>
       <c r="C402" s="2"/>
       <c r="D402" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>514</v>
+        <v>549</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.35">
@@ -9756,17 +9754,15 @@
       <c r="B403" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C403" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="D403" s="2">
-        <v>1</v>
+      <c r="C403" s="2"/>
+      <c r="D403" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>562</v>
+        <v>514</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
@@ -9777,16 +9773,16 @@
         <v>513</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="D404" s="2">
         <v>1</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>519</v>
+        <v>562</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
@@ -9797,7 +9793,7 @@
         <v>513</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>100</v>
+        <v>518</v>
       </c>
       <c r="D405" s="2">
         <v>1</v>
@@ -9806,7 +9802,7 @@
         <v>537</v>
       </c>
       <c r="F405" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.35">
@@ -9817,7 +9813,7 @@
         <v>513</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="D406" s="2">
         <v>1</v>
@@ -9826,7 +9822,7 @@
         <v>537</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.35">
@@ -9837,16 +9833,16 @@
         <v>513</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>569</v>
+        <v>135</v>
       </c>
       <c r="D407" s="2">
         <v>1</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>571</v>
+        <v>536</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.35">
@@ -9854,17 +9850,19 @@
         <v>162</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C408" s="2"/>
-      <c r="D408" s="2" t="s">
-        <v>144</v>
+        <v>513</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D408" s="2">
+        <v>1</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
@@ -9874,17 +9872,15 @@
       <c r="B409" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C409" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D409" s="2">
-        <v>1</v>
+      <c r="C409" s="2"/>
+      <c r="D409" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>555</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.35">
@@ -9895,7 +9891,7 @@
         <v>565</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>568</v>
+        <v>301</v>
       </c>
       <c r="D410" s="2">
         <v>1</v>
@@ -9912,17 +9908,19 @@
         <v>162</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="C411" s="2"/>
-      <c r="D411" s="2" t="s">
-        <v>128</v>
+        <v>565</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D411" s="2">
+        <v>1</v>
       </c>
       <c r="E411" s="2" t="s">
         <v>555</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.35">
@@ -9930,17 +9928,17 @@
         <v>162</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="C412" s="2"/>
       <c r="D412" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.35">
@@ -9950,17 +9948,15 @@
       <c r="B413" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="C413" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="D413" s="2">
-        <v>1</v>
+      <c r="C413" s="2"/>
+      <c r="D413" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
@@ -9971,14 +9967,16 @@
         <v>572</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D414" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="D414" s="2">
+        <v>1</v>
+      </c>
       <c r="E414" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
@@ -9986,17 +9984,17 @@
         <v>162</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="C415" s="2"/>
-      <c r="D415" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="C415" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D415" s="2"/>
       <c r="E415" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.35">
@@ -10004,7 +10002,7 @@
         <v>162</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C416" s="2"/>
       <c r="D416" s="2" t="s">
@@ -10022,17 +10020,17 @@
         <v>162</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="C417" s="2"/>
       <c r="D417" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.35">
@@ -10040,7 +10038,7 @@
         <v>162</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C418" s="2"/>
       <c r="D418" s="2" t="s">
@@ -10058,17 +10056,17 @@
         <v>162</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="C419" s="2"/>
       <c r="D419" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.35">
@@ -10078,15 +10076,15 @@
       <c r="B420" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C420" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="D420" s="2"/>
+      <c r="C420" s="2"/>
+      <c r="D420" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E420" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
@@ -10097,7 +10095,7 @@
         <v>543</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>94</v>
+        <v>544</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" s="2" t="s">
@@ -10112,12 +10110,12 @@
         <v>162</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C422" s="2"/>
-      <c r="D422" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D422" s="2"/>
       <c r="E422" s="2" t="s">
         <v>537</v>
       </c>
@@ -10130,7 +10128,7 @@
         <v>162</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C423" s="2"/>
       <c r="D423" s="2" t="s">
@@ -10148,7 +10146,7 @@
         <v>162</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="C424" s="2"/>
       <c r="D424" s="2" t="s">
@@ -10158,7 +10156,7 @@
         <v>537</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.35">
@@ -10166,17 +10164,17 @@
         <v>162</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>275</v>
+        <v>517</v>
       </c>
       <c r="C425" s="2"/>
       <c r="D425" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F425" s="2" t="s">
-        <v>279</v>
+        <v>514</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.35">
@@ -10186,17 +10184,15 @@
       <c r="B426" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C426" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D426" s="2">
-        <v>1</v>
+      <c r="C426" s="2"/>
+      <c r="D426" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
@@ -10207,14 +10203,16 @@
         <v>275</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D427" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="D427" s="2">
+        <v>1</v>
+      </c>
       <c r="E427" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F427" s="2" t="s">
-        <v>378</v>
+        <v>282</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.35">
@@ -10225,14 +10223,14 @@
         <v>275</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>277</v>
+        <v>487</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F428" s="2" t="s">
-        <v>295</v>
+        <v>378</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.35">
@@ -10243,14 +10241,14 @@
         <v>275</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>486</v>
+        <v>277</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" s="2" t="s">
-        <v>481</v>
+        <v>269</v>
       </c>
       <c r="F429" s="2" t="s">
-        <v>64</v>
+        <v>295</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
@@ -10261,14 +10259,14 @@
         <v>275</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>276</v>
+        <v>486</v>
       </c>
       <c r="D430" s="2"/>
       <c r="E430" s="2" t="s">
-        <v>269</v>
+        <v>481</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>279</v>
+        <v>64</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.35">
@@ -10279,14 +10277,14 @@
         <v>275</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.35">
@@ -10297,14 +10295,14 @@
         <v>275</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>488</v>
+        <v>278</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>489</v>
+        <v>294</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
@@ -10312,17 +10310,17 @@
         <v>162</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C433" s="2"/>
-      <c r="D433" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C433" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D433" s="2"/>
       <c r="E433" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F433" s="2" t="s">
-        <v>270</v>
+        <v>489</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.35">
@@ -10332,17 +10330,15 @@
       <c r="B434" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C434" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D434" s="2">
-        <v>1</v>
+      <c r="C434" s="2"/>
+      <c r="D434" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.35">
@@ -10353,7 +10349,7 @@
         <v>271</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D435" s="2">
         <v>1</v>
@@ -10362,7 +10358,7 @@
         <v>269</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.35">
@@ -10370,17 +10366,19 @@
         <v>162</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C436" s="2"/>
-      <c r="D436" s="2" t="s">
-        <v>128</v>
+        <v>271</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D436" s="2">
+        <v>1</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.35">
@@ -10388,59 +10386,57 @@
         <v>162</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C437" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D437" s="2">
-        <v>1</v>
+        <v>274</v>
+      </c>
+      <c r="C437" s="2"/>
+      <c r="D437" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F437" s="2" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A438" t="s">
+      <c r="A438" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C438" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D438" s="1">
+      <c r="C438" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D438" s="2">
         <v>1</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A439" s="1" t="s">
+      <c r="A439" t="s">
         <v>162</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="D439" s="1">
         <v>1</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>203</v>
+        <v>54</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
@@ -10451,14 +10447,16 @@
         <v>56</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D440" s="1"/>
+        <v>204</v>
+      </c>
+      <c r="D440" s="1">
+        <v>1</v>
+      </c>
       <c r="E440" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.35">
@@ -10469,7 +10467,7 @@
         <v>56</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="D441" s="1"/>
       <c r="E441" s="2" t="s">
@@ -10487,14 +10485,14 @@
         <v>56</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D442" s="1"/>
       <c r="E442" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.35">
@@ -10505,14 +10503,14 @@
         <v>56</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D443" s="1"/>
       <c r="E443" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.35">
@@ -10522,15 +10520,15 @@
       <c r="B444" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C444" s="2"/>
-      <c r="D444" s="2" t="s">
-        <v>144</v>
-      </c>
+      <c r="C444" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D444" s="1"/>
       <c r="E444" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>53</v>
+        <v>194</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.35">
@@ -10538,16 +10536,17 @@
         <v>162</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D445" t="s">
+        <v>56</v>
+      </c>
+      <c r="C445" s="2"/>
+      <c r="D445" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>198</v>
+        <v>53</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.35">
@@ -10557,8 +10556,8 @@
       <c r="B446" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C446" t="s">
-        <v>200</v>
+      <c r="D446" t="s">
+        <v>144</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>193</v>
@@ -10575,7 +10574,7 @@
         <v>210</v>
       </c>
       <c r="C447" t="s">
-        <v>94</v>
+        <v>200</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>193</v>
@@ -10592,7 +10591,7 @@
         <v>210</v>
       </c>
       <c r="C448" t="s">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>193</v>
@@ -10602,40 +10601,37 @@
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A449" t="s">
-        <v>162</v>
-      </c>
-      <c r="B449" t="s">
-        <v>148</v>
-      </c>
-      <c r="D449" t="s">
-        <v>144</v>
+      <c r="A449" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C449" t="s">
+        <v>201</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F449" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A450" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B450" s="1" t="s">
+      <c r="A450" t="s">
+        <v>162</v>
+      </c>
+      <c r="B450" t="s">
         <v>148</v>
       </c>
-      <c r="C450" t="s">
-        <v>199</v>
-      </c>
-      <c r="D450">
-        <v>2</v>
+      <c r="D450" t="s">
+        <v>144</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F450" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
@@ -10646,7 +10642,7 @@
         <v>148</v>
       </c>
       <c r="C451" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D451">
         <v>2</v>
@@ -10655,24 +10651,27 @@
         <v>193</v>
       </c>
       <c r="F451" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A452" t="s">
-        <v>162</v>
-      </c>
-      <c r="B452" t="s">
+      <c r="A452" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B452" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C452" t="s">
-        <v>195</v>
+        <v>204</v>
+      </c>
+      <c r="D452">
+        <v>2</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F452" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
@@ -10683,7 +10682,7 @@
         <v>148</v>
       </c>
       <c r="C453" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>193</v>
@@ -10693,14 +10692,14 @@
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A454" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B454" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="D454" t="s">
-        <v>144</v>
+      <c r="A454" t="s">
+        <v>162</v>
+      </c>
+      <c r="B454" t="s">
+        <v>148</v>
+      </c>
+      <c r="C454" t="s">
+        <v>196</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>193</v>
@@ -10714,7 +10713,7 @@
         <v>162</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>192</v>
+        <v>450</v>
       </c>
       <c r="D455" t="s">
         <v>144</v>
@@ -10723,7 +10722,7 @@
         <v>193</v>
       </c>
       <c r="F455" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.35">
@@ -10733,17 +10732,14 @@
       <c r="B456" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C456" t="s">
-        <v>100</v>
-      </c>
-      <c r="D456">
-        <v>1</v>
+      <c r="D456" t="s">
+        <v>144</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F456" s="2" t="s">
-        <v>54</v>
+        <v>194</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
@@ -10751,16 +10747,19 @@
         <v>162</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D457" t="s">
-        <v>144</v>
+        <v>192</v>
+      </c>
+      <c r="C457" t="s">
+        <v>100</v>
+      </c>
+      <c r="D457">
+        <v>1</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F457" s="2" t="s">
-        <v>212</v>
+        <v>54</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.35">
@@ -10770,17 +10769,14 @@
       <c r="B458" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C458" t="s">
-        <v>199</v>
-      </c>
-      <c r="D458">
-        <v>1</v>
+      <c r="D458" t="s">
+        <v>144</v>
       </c>
       <c r="E458" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F458" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.35">
@@ -10791,7 +10787,7 @@
         <v>209</v>
       </c>
       <c r="C459" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D459">
         <v>1</v>
@@ -10800,7 +10796,7 @@
         <v>193</v>
       </c>
       <c r="F459" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.35">
@@ -10811,13 +10807,16 @@
         <v>209</v>
       </c>
       <c r="C460" t="s">
-        <v>449</v>
+        <v>204</v>
+      </c>
+      <c r="D460">
+        <v>1</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F460" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.35">
@@ -10825,16 +10824,16 @@
         <v>162</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D461" t="s">
-        <v>144</v>
-      </c>
-      <c r="E461" t="s">
+        <v>209</v>
+      </c>
+      <c r="C461" t="s">
+        <v>449</v>
+      </c>
+      <c r="E461" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F461" t="s">
-        <v>206</v>
+      <c r="F461" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.35">
@@ -10844,17 +10843,14 @@
       <c r="B462" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C462" t="s">
-        <v>100</v>
-      </c>
-      <c r="D462">
-        <v>1</v>
+      <c r="D462" t="s">
+        <v>144</v>
       </c>
       <c r="E462" t="s">
         <v>193</v>
       </c>
       <c r="F462" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.35">
@@ -10862,16 +10858,19 @@
         <v>162</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D463" t="s">
-        <v>144</v>
+        <v>207</v>
+      </c>
+      <c r="C463" t="s">
+        <v>100</v>
+      </c>
+      <c r="D463">
+        <v>1</v>
       </c>
       <c r="E463" t="s">
-        <v>374</v>
+        <v>193</v>
       </c>
       <c r="F463" t="s">
-        <v>376</v>
+        <v>208</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.35">
@@ -10879,16 +10878,16 @@
         <v>162</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>540</v>
+        <v>373</v>
       </c>
       <c r="D464" t="s">
         <v>144</v>
       </c>
       <c r="E464" t="s">
-        <v>537</v>
+        <v>374</v>
       </c>
       <c r="F464" t="s">
-        <v>539</v>
+        <v>376</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
@@ -10898,14 +10897,14 @@
       <c r="B465" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C465" t="s">
-        <v>552</v>
+      <c r="D465" t="s">
+        <v>144</v>
       </c>
       <c r="E465" t="s">
         <v>537</v>
       </c>
       <c r="F465" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.35">
@@ -10916,7 +10915,7 @@
         <v>540</v>
       </c>
       <c r="C466" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E466" t="s">
         <v>537</v>
@@ -10933,7 +10932,7 @@
         <v>540</v>
       </c>
       <c r="C467" t="s">
-        <v>196</v>
+        <v>553</v>
       </c>
       <c r="E467" t="s">
         <v>537</v>
@@ -10947,16 +10946,16 @@
         <v>162</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D468" t="s">
-        <v>144</v>
+        <v>540</v>
+      </c>
+      <c r="C468" t="s">
+        <v>196</v>
       </c>
       <c r="E468" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F468" t="s">
-        <v>344</v>
+        <v>549</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
@@ -10966,17 +10965,14 @@
       <c r="B469" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C469" t="s">
-        <v>336</v>
-      </c>
-      <c r="D469">
-        <v>1</v>
+      <c r="D469" t="s">
+        <v>144</v>
       </c>
       <c r="E469" t="s">
         <v>331</v>
       </c>
       <c r="F469" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
@@ -10987,7 +10983,7 @@
         <v>335</v>
       </c>
       <c r="C470" t="s">
-        <v>102</v>
+        <v>336</v>
       </c>
       <c r="D470">
         <v>1</v>
@@ -10996,7 +10992,7 @@
         <v>331</v>
       </c>
       <c r="F470" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.35">
@@ -11007,7 +11003,7 @@
         <v>335</v>
       </c>
       <c r="C471" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D471">
         <v>1</v>
@@ -11016,7 +11012,7 @@
         <v>331</v>
       </c>
       <c r="F471" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.35">
@@ -11027,7 +11023,7 @@
         <v>335</v>
       </c>
       <c r="C472" t="s">
-        <v>338</v>
+        <v>115</v>
       </c>
       <c r="D472">
         <v>1</v>
@@ -11036,7 +11032,7 @@
         <v>331</v>
       </c>
       <c r="F472" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.35">
@@ -11044,16 +11040,19 @@
         <v>162</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D473" t="s">
-        <v>144</v>
+        <v>335</v>
+      </c>
+      <c r="C473" t="s">
+        <v>338</v>
+      </c>
+      <c r="D473">
+        <v>1</v>
       </c>
       <c r="E473" t="s">
         <v>331</v>
       </c>
       <c r="F473" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.35">
@@ -11063,17 +11062,14 @@
       <c r="B474" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C474" t="s">
-        <v>340</v>
-      </c>
-      <c r="D474">
-        <v>1</v>
+      <c r="D474" t="s">
+        <v>144</v>
       </c>
       <c r="E474" t="s">
         <v>331</v>
       </c>
       <c r="F474" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.35">
@@ -11084,7 +11080,7 @@
         <v>333</v>
       </c>
       <c r="C475" t="s">
-        <v>100</v>
+        <v>340</v>
       </c>
       <c r="D475">
         <v>1</v>
@@ -11093,7 +11089,7 @@
         <v>331</v>
       </c>
       <c r="F475" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.35">
@@ -11104,7 +11100,7 @@
         <v>333</v>
       </c>
       <c r="C476" t="s">
-        <v>342</v>
+        <v>100</v>
       </c>
       <c r="D476">
         <v>1</v>
@@ -11113,7 +11109,7 @@
         <v>331</v>
       </c>
       <c r="F476" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.35">
@@ -11121,16 +11117,19 @@
         <v>162</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D477" t="s">
-        <v>128</v>
+        <v>333</v>
+      </c>
+      <c r="C477" t="s">
+        <v>342</v>
+      </c>
+      <c r="D477">
+        <v>1</v>
       </c>
       <c r="E477" t="s">
         <v>331</v>
       </c>
       <c r="F477" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.35">
@@ -11138,16 +11137,16 @@
         <v>162</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>482</v>
+        <v>442</v>
       </c>
       <c r="D478" t="s">
         <v>128</v>
       </c>
       <c r="E478" t="s">
-        <v>481</v>
+        <v>331</v>
       </c>
       <c r="F478" t="s">
-        <v>64</v>
+        <v>344</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.35">
@@ -11155,16 +11154,16 @@
         <v>162</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>232</v>
+        <v>482</v>
       </c>
       <c r="D479" t="s">
         <v>128</v>
       </c>
       <c r="E479" t="s">
-        <v>193</v>
+        <v>481</v>
       </c>
       <c r="F479" t="s">
-        <v>206</v>
+        <v>64</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.35">
@@ -11172,16 +11171,16 @@
         <v>162</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>502</v>
+        <v>232</v>
       </c>
       <c r="D480" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E480" t="s">
-        <v>497</v>
+        <v>193</v>
       </c>
       <c r="F480" t="s">
-        <v>503</v>
+        <v>206</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.35">
@@ -11191,17 +11190,14 @@
       <c r="B481" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C481" t="s">
-        <v>415</v>
-      </c>
-      <c r="D481">
-        <v>1</v>
+      <c r="D481" t="s">
+        <v>144</v>
       </c>
       <c r="E481" t="s">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="F481" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.35">
@@ -11212,13 +11208,16 @@
         <v>502</v>
       </c>
       <c r="C482" t="s">
-        <v>506</v>
+        <v>415</v>
+      </c>
+      <c r="D482">
+        <v>1</v>
       </c>
       <c r="E482" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="F482" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.35">
@@ -11229,13 +11228,13 @@
         <v>502</v>
       </c>
       <c r="C483" t="s">
-        <v>531</v>
+        <v>506</v>
       </c>
       <c r="E483" t="s">
         <v>497</v>
       </c>
       <c r="F483" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.35">
@@ -11243,16 +11242,16 @@
         <v>162</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="D484" t="s">
-        <v>345</v>
+        <v>502</v>
+      </c>
+      <c r="C484" t="s">
+        <v>531</v>
       </c>
       <c r="E484" t="s">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="F484" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.35">
@@ -11260,15 +11259,32 @@
         <v>162</v>
       </c>
       <c r="B485" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D485" t="s">
+        <v>345</v>
+      </c>
+      <c r="E485" t="s">
+        <v>532</v>
+      </c>
+      <c r="F485" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A486" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B486" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="D485" t="s">
+      <c r="D486" t="s">
         <v>144</v>
       </c>
-      <c r="E485" t="s">
+      <c r="E486" t="s">
         <v>497</v>
       </c>
-      <c r="F485" t="s">
+      <c r="F486" t="s">
         <v>529</v>
       </c>
     </row>

--- a/snippet-extractor-metadata/word.xlsx
+++ b/snippet-extractor-metadata/word.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6F834F-7E2F-41F4-AFC1-C8258BC9E2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28AE63E-A78F-4D65-8195-52AEEFF6A709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2431" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="640">
   <si>
     <t>Class</t>
   </si>
@@ -1922,6 +1922,24 @@
   </si>
   <si>
     <t>ExportOptimizeFor</t>
+  </si>
+  <si>
+    <t>insertSymbol</t>
+  </si>
+  <si>
+    <t>word-selection-insert-symbol</t>
+  </si>
+  <si>
+    <t>insertWingdings</t>
+  </si>
+  <si>
+    <t>insertCopyright</t>
+  </si>
+  <si>
+    <t>SelectionInsertSymbolOptions</t>
+  </si>
+  <si>
+    <t>FontBias</t>
   </si>
 </sst>
 </file>
@@ -1970,7 +1988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1978,6 +1996,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2033,8 +2054,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F486" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="A1:F486" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F489" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:F489" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{1DA12987-AB2C-4056-A643-B1229DC856C5}" name="Package" dataDxfId="4"/>
     <tableColumn id="1" xr3:uid="{0CD83AD1-F92A-407D-8460-4E881461FD01}" name="Class" dataDxfId="3"/>
@@ -2344,7 +2365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F486"/>
+  <dimension ref="A1:F489"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25.08984375" bestFit="1" customWidth="1"/>
@@ -6521,10 +6542,10 @@
       <c r="A229" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B229" s="4" t="s">
+      <c r="B229" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C229" s="4"/>
+      <c r="C229" s="1"/>
       <c r="D229" s="1" t="s">
         <v>128</v>
       </c>
@@ -6817,18 +6838,18 @@
       <c r="A245" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="C245" s="2"/>
+      <c r="B245" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="C245" s="5"/>
       <c r="D245" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E245" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>560</v>
+      <c r="E245" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
@@ -6836,53 +6857,53 @@
         <v>162</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>423</v>
+        <v>557</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>424</v>
+        <v>555</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>86</v>
+        <v>560</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A247" t="s">
+      <c r="A247" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>149</v>
+        <v>423</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="2" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A248" s="1" t="s">
+      <c r="A248" t="s">
         <v>162</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
@@ -6890,55 +6911,55 @@
         <v>162</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>525</v>
+        <v>173</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E249" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A250" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E250" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F249" s="2" t="s">
+      <c r="F250" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A250" t="s">
-        <v>162</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D250" s="2">
-        <v>1</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A251" s="1" t="s">
+      <c r="A251" t="s">
         <v>162</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C251" s="2"/>
-      <c r="D251" s="2" t="s">
-        <v>144</v>
+      <c r="C251" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D251" s="2">
+        <v>1</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
@@ -6948,15 +6969,15 @@
       <c r="B252" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C252" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E252" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
@@ -6964,12 +6985,12 @@
         <v>162</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C253" s="2"/>
-      <c r="D253" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D253" s="2"/>
       <c r="E253" s="2" t="s">
         <v>70</v>
       </c>
@@ -6982,53 +7003,53 @@
         <v>162</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>347</v>
+        <v>177</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2" t="s">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>348</v>
+        <v>23</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A255" t="s">
+      <c r="A255" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>154</v>
+        <v>347</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="2" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>140</v>
+        <v>235</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>155</v>
+        <v>348</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A256" s="1" t="s">
+      <c r="A256" t="s">
         <v>162</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>510</v>
+        <v>154</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="2" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>537</v>
+        <v>140</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>511</v>
+        <v>155</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.35">
@@ -7036,17 +7057,17 @@
         <v>162</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>215</v>
+        <v>510</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>57</v>
+        <v>537</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>58</v>
+        <v>511</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.35">
@@ -7056,11 +7077,9 @@
       <c r="B258" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C258" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D258" s="2">
-        <v>1</v>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>57</v>
@@ -7077,16 +7096,16 @@
         <v>215</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="D259" s="2">
         <v>1</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>220</v>
+        <v>58</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.35">
@@ -7097,7 +7116,7 @@
         <v>215</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D260" s="2">
         <v>1</v>
@@ -7117,14 +7136,16 @@
         <v>215</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D261" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="D261" s="2">
+        <v>1</v>
+      </c>
       <c r="E261" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.35">
@@ -7135,7 +7156,7 @@
         <v>215</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" s="2" t="s">
@@ -7150,17 +7171,17 @@
         <v>162</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C263" s="2"/>
-      <c r="D263" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D263" s="2"/>
       <c r="E263" s="2" t="s">
-        <v>481</v>
+        <v>219</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>64</v>
+        <v>300</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.35">
@@ -7168,17 +7189,17 @@
         <v>162</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>222</v>
+        <v>480</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>219</v>
+        <v>481</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>220</v>
+        <v>64</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.35">
@@ -7186,17 +7207,17 @@
         <v>162</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>425</v>
+        <v>222</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>219</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>300</v>
+        <v>220</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.35">
@@ -7204,17 +7225,17 @@
         <v>162</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>626</v>
+        <v>425</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>623</v>
+        <v>219</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>624</v>
+        <v>300</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.35">
@@ -7224,17 +7245,15 @@
       <c r="B267" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C267" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="D267" s="2">
-        <v>1</v>
+      <c r="C267" s="2"/>
+      <c r="D267" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>623</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.35">
@@ -7242,17 +7261,19 @@
         <v>162</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="C268" s="2"/>
-      <c r="D268" s="2" t="s">
-        <v>345</v>
+        <v>626</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D268" s="2">
+        <v>1</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>623</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.35">
@@ -7260,17 +7281,17 @@
         <v>162</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>216</v>
+        <v>627</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>57</v>
+        <v>623</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>58</v>
+        <v>629</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.35">
@@ -7280,10 +7301,10 @@
       <c r="B270" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C270" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D270" s="2"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E270" s="2" t="s">
         <v>57</v>
       </c>
@@ -7296,17 +7317,17 @@
         <v>162</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C271" s="2"/>
-      <c r="D271" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D271" s="2"/>
       <c r="E271" s="2" t="s">
-        <v>481</v>
+        <v>57</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.35">
@@ -7314,7 +7335,7 @@
         <v>162</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2" t="s">
@@ -7332,17 +7353,17 @@
         <v>162</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>225</v>
+        <v>484</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>219</v>
+        <v>481</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>300</v>
+        <v>64</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.35">
@@ -7350,7 +7371,7 @@
         <v>162</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2" t="s">
@@ -7360,7 +7381,7 @@
         <v>219</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.35">
@@ -7368,17 +7389,17 @@
         <v>162</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>485</v>
+        <v>224</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>481</v>
+        <v>219</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>64</v>
+        <v>220</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
@@ -7386,35 +7407,35 @@
         <v>162</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>226</v>
+        <v>485</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>227</v>
+        <v>481</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>228</v>
+        <v>64</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A277" t="s">
+      <c r="A277" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>91</v>
+        <v>226</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
@@ -7424,17 +7445,15 @@
       <c r="B278" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C278" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D278" s="2">
-        <v>1</v>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.35">
@@ -7445,7 +7464,7 @@
         <v>91</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D279" s="2">
         <v>1</v>
@@ -7454,7 +7473,7 @@
         <v>146</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
@@ -7465,14 +7484,16 @@
         <v>91</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D280" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="D280" s="2">
+        <v>1</v>
+      </c>
       <c r="E280" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.35">
@@ -7483,14 +7504,14 @@
         <v>91</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
@@ -7501,14 +7522,14 @@
         <v>91</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.35">
@@ -7516,17 +7537,17 @@
         <v>162</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C283" s="2"/>
-      <c r="D283" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D283" s="2"/>
       <c r="E283" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.35">
@@ -7536,11 +7557,9 @@
       <c r="B284" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C284" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D284" s="2">
-        <v>1</v>
+      <c r="C284" s="2"/>
+      <c r="D284" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>146</v>
@@ -7553,68 +7572,71 @@
       <c r="A285" t="s">
         <v>162</v>
       </c>
-      <c r="B285" t="s">
-        <v>156</v>
-      </c>
-      <c r="D285" t="s">
-        <v>128</v>
+      <c r="B285" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D285" s="2">
+        <v>1</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A286" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>631</v>
+      <c r="A286" t="s">
+        <v>162</v>
+      </c>
+      <c r="B286" t="s">
+        <v>156</v>
       </c>
       <c r="D286" t="s">
         <v>128</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>623</v>
+        <v>146</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>632</v>
+        <v>95</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A287" t="s">
+      <c r="A287" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D287" t="s">
         <v>128</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A288" s="1" t="s">
+      <c r="A288" t="s">
         <v>162</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>411</v>
+        <v>622</v>
       </c>
       <c r="D288" t="s">
         <v>128</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>374</v>
+        <v>615</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>375</v>
+        <v>618</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.35">
@@ -7622,16 +7644,16 @@
         <v>162</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>499</v>
+        <v>411</v>
       </c>
       <c r="D289" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>497</v>
+        <v>374</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>498</v>
+        <v>375</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.35">
@@ -7641,11 +7663,8 @@
       <c r="B290" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C290" t="s">
-        <v>115</v>
-      </c>
-      <c r="D290">
-        <v>1</v>
+      <c r="D290" t="s">
+        <v>144</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>497</v>
@@ -7662,13 +7681,16 @@
         <v>499</v>
       </c>
       <c r="C291" t="s">
-        <v>500</v>
+        <v>115</v>
+      </c>
+      <c r="D291">
+        <v>1</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
@@ -7676,16 +7698,16 @@
         <v>162</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="D292" t="s">
-        <v>144</v>
+        <v>499</v>
+      </c>
+      <c r="C292" t="s">
+        <v>500</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
@@ -7693,7 +7715,7 @@
         <v>162</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="D293" t="s">
         <v>144</v>
@@ -7702,7 +7724,7 @@
         <v>497</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
@@ -7712,8 +7734,8 @@
       <c r="B294" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C294" t="s">
-        <v>508</v>
+      <c r="D294" t="s">
+        <v>144</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>497</v>
@@ -7730,13 +7752,13 @@
         <v>504</v>
       </c>
       <c r="C295" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
@@ -7744,34 +7766,33 @@
         <v>162</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="D296" t="s">
-        <v>144</v>
+        <v>504</v>
+      </c>
+      <c r="C296" t="s">
+        <v>509</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F296" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A297" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D297" t="s">
+        <v>144</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F297" s="2" t="s">
         <v>527</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A297" t="s">
-        <v>162</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C297" s="2"/>
-      <c r="D297" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E297" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
@@ -7781,77 +7802,75 @@
       <c r="B298" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C298" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D298" s="2">
-        <v>1</v>
+      <c r="C298" s="2"/>
+      <c r="D298" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A299" s="1" t="s">
+      <c r="A299" t="s">
         <v>162</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>360</v>
+        <v>115</v>
       </c>
       <c r="D299" s="2">
         <v>1</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>360</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A300" t="s">
+      <c r="A300" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>29</v>
+        <v>360</v>
       </c>
       <c r="D300" s="2">
         <v>1</v>
       </c>
-      <c r="E300" s="2" t="s">
-        <v>75</v>
+      <c r="E300" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>28</v>
+        <v>360</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A301" s="1" t="s">
+      <c r="A301" t="s">
         <v>162</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D301" s="2">
         <v>1</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
@@ -7862,36 +7881,36 @@
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>556</v>
+        <v>36</v>
       </c>
       <c r="D302" s="2">
         <v>1</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>570</v>
+        <v>43</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A303" t="s">
+      <c r="A303" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>13</v>
+        <v>556</v>
       </c>
       <c r="D303" s="2">
         <v>1</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.35">
@@ -7902,16 +7921,16 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>512</v>
+        <v>13</v>
       </c>
       <c r="D304" s="2">
         <v>1</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>537</v>
+        <v>81</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>523</v>
+        <v>22</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.35">
@@ -7922,16 +7941,16 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>48</v>
+        <v>512</v>
       </c>
       <c r="D305" s="2">
         <v>1</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>71</v>
+        <v>537</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>47</v>
+        <v>523</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
@@ -7951,7 +7970,7 @@
         <v>71</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
@@ -7961,17 +7980,17 @@
       <c r="B307" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C307" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D307" s="1">
+      <c r="C307" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D307" s="2">
         <v>1</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
@@ -7981,17 +8000,17 @@
       <c r="B308" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C308" s="2" t="s">
+      <c r="C308" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D308" s="2">
+      <c r="D308" s="1">
         <v>1</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.35">
@@ -8002,16 +8021,16 @@
         <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="D309" s="2">
         <v>1</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
@@ -8022,16 +8041,16 @@
         <v>10</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D310" s="2">
         <v>1</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.35">
@@ -8042,14 +8061,16 @@
         <v>10</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D311" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D311" s="2">
+        <v>1</v>
+      </c>
       <c r="E311" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.35">
@@ -8060,14 +8081,14 @@
         <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.35">
@@ -8078,86 +8099,86 @@
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A314" s="1" t="s">
+      <c r="A314" t="s">
         <v>162</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A315" s="3" t="s">
+      <c r="A315" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A316" t="s">
+      <c r="A316" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>17</v>
+        <v>381</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>17</v>
+        <v>382</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A317" s="1" t="s">
+      <c r="A317" t="s">
         <v>162</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>280</v>
+        <v>17</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" s="2" t="s">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>279</v>
+        <v>17</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.35">
@@ -8168,32 +8189,32 @@
         <v>10</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" s="2" t="s">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A319" t="s">
+      <c r="A319" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>8</v>
+        <v>238</v>
       </c>
       <c r="D319" s="2"/>
-      <c r="E319" s="1" t="s">
-        <v>79</v>
+      <c r="E319" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>11</v>
+        <v>240</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
@@ -8204,14 +8225,14 @@
         <v>10</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" s="1" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
@@ -8229,25 +8250,25 @@
         <v>350</v>
       </c>
       <c r="F321" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>162</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D322" s="2"/>
+      <c r="E322" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F322" s="2" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A322" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C322" s="2"/>
-      <c r="D322" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E322" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
@@ -8265,7 +8286,7 @@
         <v>318</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>319</v>
+        <v>267</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
@@ -8273,17 +8294,17 @@
         <v>162</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" s="2" t="s">
         <v>345</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>267</v>
+        <v>319</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
@@ -8301,65 +8322,63 @@
         <v>322</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A326" t="s">
+      <c r="A326" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>190</v>
+        <v>329</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E326" s="2" t="s">
-        <v>70</v>
+        <v>345</v>
+      </c>
+      <c r="E326" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>175</v>
+        <v>324</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A327" s="1" t="s">
+      <c r="A327" t="s">
         <v>162</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C327" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D327" s="2">
-        <v>1</v>
-      </c>
-      <c r="E327" s="1" t="s">
-        <v>350</v>
+      <c r="C327" s="2"/>
+      <c r="D327" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>353</v>
+        <v>175</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A328" t="s">
+      <c r="A328" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="D328" s="2">
         <v>1</v>
       </c>
-      <c r="E328" s="2" t="s">
-        <v>70</v>
+      <c r="E328" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>175</v>
+        <v>353</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -8370,14 +8389,16 @@
         <v>190</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D329" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="D329" s="2">
+        <v>1</v>
+      </c>
       <c r="E329" s="2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
@@ -8385,17 +8406,17 @@
         <v>162</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C330" s="2"/>
-      <c r="D330" s="2" t="s">
-        <v>345</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D330" s="2"/>
       <c r="E330" s="2" t="s">
-        <v>323</v>
+        <v>57</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>267</v>
+        <v>58</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
@@ -8413,25 +8434,25 @@
         <v>323</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>325</v>
+        <v>267</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A332" s="1" t="s">
+      <c r="A332" t="s">
         <v>162</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" s="2" t="s">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.35">
@@ -8441,10 +8462,10 @@
       <c r="B333" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C333" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D333" s="2"/>
+      <c r="C333" s="2"/>
+      <c r="D333" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E333" s="2" t="s">
         <v>269</v>
       </c>
@@ -8460,7 +8481,7 @@
         <v>281</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" s="2" t="s">
@@ -8475,17 +8496,17 @@
         <v>162</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C335" s="2"/>
-      <c r="D335" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D335" s="2"/>
       <c r="E335" s="2" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>445</v>
+        <v>294</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
@@ -8495,17 +8516,15 @@
       <c r="B336" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C336" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D336" s="2">
-        <v>1</v>
+      <c r="C336" s="2"/>
+      <c r="D336" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>228</v>
+        <v>445</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
@@ -8516,36 +8535,36 @@
         <v>5</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>492</v>
+        <v>229</v>
       </c>
       <c r="D337" s="2">
         <v>1</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>12</v>
+        <v>228</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A338" t="s">
+      <c r="A338" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C338" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D338" s="1">
+      <c r="C338" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D338" s="2">
         <v>1</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
@@ -8556,16 +8575,16 @@
         <v>5</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>395</v>
+        <v>107</v>
       </c>
       <c r="D339" s="1">
         <v>1</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>393</v>
+        <v>145</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>427</v>
+        <v>108</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
@@ -8576,16 +8595,16 @@
         <v>5</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>115</v>
+        <v>395</v>
       </c>
       <c r="D340" s="1">
         <v>1</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>494</v>
+        <v>393</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.35">
@@ -8596,16 +8615,16 @@
         <v>5</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D341" s="1">
         <v>1</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>147</v>
+        <v>494</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>121</v>
+        <v>462</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.35">
@@ -8616,16 +8635,16 @@
         <v>5</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="D342" s="1">
         <v>1</v>
       </c>
-      <c r="E342" s="1" t="s">
-        <v>79</v>
+      <c r="E342" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.35">
@@ -8636,16 +8655,16 @@
         <v>5</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="D343" s="1">
         <v>1</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.35">
@@ -8656,56 +8675,56 @@
         <v>5</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="D344" s="1">
         <v>1</v>
       </c>
-      <c r="E344" s="2" t="s">
-        <v>82</v>
+      <c r="E344" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A345" s="1" t="s">
+      <c r="A345" t="s">
         <v>162</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>283</v>
+        <v>36</v>
       </c>
       <c r="D345" s="1">
         <v>1</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>284</v>
+        <v>35</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A346" t="s">
+      <c r="A346" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>88</v>
+        <v>283</v>
       </c>
       <c r="D346" s="1">
         <v>1</v>
       </c>
-      <c r="E346" s="1" t="s">
-        <v>146</v>
+      <c r="E346" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>88</v>
+        <v>284</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
@@ -8716,16 +8735,16 @@
         <v>5</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>313</v>
+        <v>88</v>
       </c>
       <c r="D347" s="1">
         <v>1</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>537</v>
+        <v>146</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>521</v>
+        <v>88</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.35">
@@ -8745,7 +8764,7 @@
         <v>537</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.35">
@@ -8756,16 +8775,16 @@
         <v>5</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>556</v>
+        <v>313</v>
       </c>
       <c r="D349" s="1">
         <v>1</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
@@ -8776,16 +8795,16 @@
         <v>5</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>512</v>
+        <v>556</v>
       </c>
       <c r="D350" s="1">
         <v>1</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>511</v>
+        <v>561</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
@@ -8796,14 +8815,16 @@
         <v>5</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D351" s="1"/>
+        <v>512</v>
+      </c>
+      <c r="D351" s="1">
+        <v>1</v>
+      </c>
       <c r="E351" s="1" t="s">
-        <v>146</v>
+        <v>537</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>96</v>
+        <v>511</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
@@ -8814,31 +8835,32 @@
         <v>5</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>625</v>
+        <v>89</v>
       </c>
       <c r="D352" s="1"/>
       <c r="E352" s="1" t="s">
-        <v>623</v>
+        <v>146</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>624</v>
+        <v>96</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A353" s="1" t="s">
+      <c r="A353" t="s">
         <v>162</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C353" t="s">
-        <v>428</v>
-      </c>
-      <c r="E353" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F353" t="s">
-        <v>422</v>
+      <c r="C353" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D353" s="1"/>
+      <c r="E353" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="F353" s="2" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.35">
@@ -8848,15 +8870,14 @@
       <c r="B354" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C354" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D354" s="2"/>
+      <c r="C354" t="s">
+        <v>428</v>
+      </c>
       <c r="E354" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F354" s="2" t="s">
-        <v>239</v>
+        <v>393</v>
+      </c>
+      <c r="F354" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.35">
@@ -8864,53 +8885,53 @@
         <v>162</v>
       </c>
       <c r="B355" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D355" s="2"/>
+      <c r="E355" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F355" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A356" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B356" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C355" s="2"/>
-      <c r="D355" s="2" t="s">
+      <c r="C356" s="2"/>
+      <c r="D356" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E355" s="2" t="s">
+      <c r="E356" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F355" s="2" t="s">
+      <c r="F356" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A356" t="s">
-        <v>162</v>
-      </c>
-      <c r="B356" s="1" t="s">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>162</v>
+      </c>
+      <c r="B357" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C356" s="1"/>
-      <c r="D356" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E356" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F356" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A357" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B357" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="C357" s="1"/>
       <c r="D357" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>570</v>
+        <v>79</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>576</v>
+        <v>12</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.35">
@@ -8918,7 +8939,7 @@
         <v>162</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C358" s="1"/>
       <c r="D358" s="1" t="s">
@@ -8928,7 +8949,7 @@
         <v>570</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
@@ -8936,7 +8957,7 @@
         <v>162</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C359" s="1"/>
       <c r="D359" s="1" t="s">
@@ -8946,7 +8967,7 @@
         <v>570</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.35">
@@ -8954,17 +8975,17 @@
         <v>162</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>418</v>
+        <v>579</v>
       </c>
       <c r="C360" s="1"/>
       <c r="D360" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>413</v>
+        <v>570</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>414</v>
+        <v>576</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.35">
@@ -8972,37 +8993,35 @@
         <v>162</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>534</v>
+        <v>418</v>
       </c>
       <c r="C361" s="1"/>
       <c r="D361" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E361" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F361" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A362" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C362" s="1"/>
+      <c r="D362" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E362" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F361" s="2" t="s">
+      <c r="F362" s="2" t="s">
         <v>533</v>
-      </c>
-    </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A362" t="s">
-        <v>162</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C362" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D362" s="2">
-        <v>2</v>
-      </c>
-      <c r="E362" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F362" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.35">
@@ -9012,17 +9031,17 @@
       <c r="B363" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C363" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D363" s="1">
-        <v>1</v>
+      <c r="C363" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D363" s="2">
+        <v>2</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
@@ -9032,15 +9051,17 @@
       <c r="B364" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C364" s="1"/>
-      <c r="D364" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E364" s="1" t="s">
-        <v>140</v>
+      <c r="C364" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D364" s="1">
+        <v>1</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
@@ -9048,17 +9069,17 @@
         <v>162</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C365" s="2"/>
-      <c r="D365" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C365" s="1"/>
+      <c r="D365" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E365" s="2" t="s">
+      <c r="E365" s="1" t="s">
         <v>140</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.35">
@@ -9066,17 +9087,17 @@
         <v>162</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>609</v>
+        <v>142</v>
       </c>
       <c r="C366" s="2"/>
       <c r="D366" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>606</v>
+        <v>140</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>608</v>
+        <v>143</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.35">
@@ -9086,17 +9107,15 @@
       <c r="B367" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C367" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="D367" s="2">
-        <v>1</v>
+      <c r="C367" s="2"/>
+      <c r="D367" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
@@ -9107,7 +9126,7 @@
         <v>609</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D368" s="2">
         <v>1</v>
@@ -9116,7 +9135,7 @@
         <v>615</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
@@ -9127,16 +9146,16 @@
         <v>609</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D369" s="2">
         <v>1</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.35">
@@ -9144,89 +9163,93 @@
         <v>162</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="C370" s="2"/>
-      <c r="D370" s="2" t="s">
-        <v>345</v>
+        <v>609</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D370" s="2">
+        <v>1</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>606</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A371" s="1" t="s">
+      <c r="A371" t="s">
         <v>162</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="C371" s="2"/>
-      <c r="D371" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E371" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F371" s="2" t="s">
-        <v>618</v>
+        <v>609</v>
+      </c>
+      <c r="C371" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="D371" s="2">
+        <v>1</v>
+      </c>
+      <c r="E371" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F371" s="5" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A372" s="1" t="s">
+      <c r="A372" t="s">
         <v>162</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C372" s="2"/>
       <c r="D372" s="2" t="s">
         <v>345</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A373" t="s">
-        <v>162</v>
-      </c>
-      <c r="B373" s="1" t="s">
+      <c r="A373" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="C373" s="5"/>
+      <c r="D373" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E373" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F373" s="5" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>162</v>
+      </c>
+      <c r="B374" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C373" s="2"/>
-      <c r="D373" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E373" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F373" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A374" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B374" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="C374" s="2"/>
       <c r="D374" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>164</v>
+        <v>71</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>168</v>
+        <v>49</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
@@ -9234,17 +9257,17 @@
         <v>162</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C375" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D375" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="C375" s="2"/>
+      <c r="D375" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="E375" s="2" t="s">
-        <v>164</v>
+        <v>615</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>168</v>
+        <v>618</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.35">
@@ -9252,17 +9275,17 @@
         <v>162</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C376" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D376" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="C376" s="2"/>
+      <c r="D376" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="E376" s="2" t="s">
-        <v>164</v>
+        <v>615</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>168</v>
+        <v>620</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.35">
@@ -9270,7 +9293,7 @@
         <v>162</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>167</v>
+        <v>296</v>
       </c>
       <c r="C377" s="2"/>
       <c r="D377" s="2" t="s">
@@ -9280,7 +9303,7 @@
         <v>164</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -9288,14 +9311,12 @@
         <v>162</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>167</v>
+        <v>296</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D378" s="2">
-        <v>1</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="D378" s="2"/>
       <c r="E378" s="2" t="s">
         <v>164</v>
       </c>
@@ -9308,17 +9329,17 @@
         <v>162</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>167</v>
+        <v>296</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>67</v>
+        <v>298</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" s="2" t="s">
         <v>164</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.35">
@@ -9326,17 +9347,17 @@
         <v>162</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>491</v>
+        <v>167</v>
       </c>
       <c r="C380" s="2"/>
       <c r="D380" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>489</v>
+        <v>166</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.35">
@@ -9344,17 +9365,19 @@
         <v>162</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C381" s="2"/>
-      <c r="D381" s="2" t="s">
-        <v>128</v>
+        <v>167</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D381" s="2">
+        <v>1</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>489</v>
+        <v>168</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.35">
@@ -9362,17 +9385,17 @@
         <v>162</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C382" s="2"/>
-      <c r="D382" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D382" s="2"/>
       <c r="E382" s="2" t="s">
-        <v>537</v>
+        <v>164</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>519</v>
+        <v>169</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.35">
@@ -9380,19 +9403,17 @@
         <v>162</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C383" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D383" s="2">
-        <v>1</v>
+        <v>491</v>
+      </c>
+      <c r="C383" s="2"/>
+      <c r="D383" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>537</v>
+        <v>269</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.35">
@@ -9400,19 +9421,17 @@
         <v>162</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C384" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="D384" s="2">
-        <v>1</v>
+        <v>490</v>
+      </c>
+      <c r="C384" s="2"/>
+      <c r="D384" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>570</v>
+        <v>269</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>584</v>
+        <v>489</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
@@ -9422,17 +9441,15 @@
       <c r="B385" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C385" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D385" s="2">
-        <v>1</v>
+      <c r="C385" s="2"/>
+      <c r="D385" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>584</v>
+        <v>519</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.35">
@@ -9443,16 +9460,16 @@
         <v>516</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>587</v>
+        <v>97</v>
       </c>
       <c r="D386" s="2">
         <v>1</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>581</v>
+        <v>522</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.35">
@@ -9463,7 +9480,7 @@
         <v>516</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D387" s="2">
         <v>1</v>
@@ -9472,7 +9489,7 @@
         <v>570</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.35">
@@ -9483,7 +9500,7 @@
         <v>516</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>48</v>
+        <v>585</v>
       </c>
       <c r="D388" s="2">
         <v>1</v>
@@ -9492,7 +9509,7 @@
         <v>570</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
@@ -9503,14 +9520,16 @@
         <v>516</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D389" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="D389" s="2">
+        <v>1</v>
+      </c>
       <c r="E389" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>520</v>
+        <v>581</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.35">
@@ -9521,14 +9540,16 @@
         <v>516</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D390" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="D390" s="2">
+        <v>1</v>
+      </c>
       <c r="E390" s="2" t="s">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.35">
@@ -9539,14 +9560,16 @@
         <v>516</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D391" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D391" s="2">
+        <v>1</v>
+      </c>
       <c r="E391" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.35">
@@ -9557,14 +9580,14 @@
         <v>516</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>558</v>
+        <v>104</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>559</v>
+        <v>520</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.35">
@@ -9575,14 +9598,14 @@
         <v>516</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" s="2" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.35">
@@ -9593,14 +9616,14 @@
         <v>516</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>589</v>
+        <v>563</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.35">
@@ -9611,14 +9634,14 @@
         <v>516</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>591</v>
+        <v>558</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.35">
@@ -9629,14 +9652,14 @@
         <v>516</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.35">
@@ -9647,14 +9670,14 @@
         <v>516</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.35">
@@ -9665,14 +9688,14 @@
         <v>516</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.35">
@@ -9683,14 +9706,14 @@
         <v>516</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>538</v>
+        <v>590</v>
       </c>
       <c r="D399" s="2"/>
       <c r="E399" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.35">
@@ -9701,14 +9724,14 @@
         <v>516</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>541</v>
+        <v>592</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>542</v>
+        <v>578</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.35">
@@ -9719,14 +9742,14 @@
         <v>516</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>94</v>
+        <v>586</v>
       </c>
       <c r="D401" s="2"/>
       <c r="E401" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>514</v>
+        <v>571</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.35">
@@ -9734,17 +9757,17 @@
         <v>162</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C402" s="2"/>
-      <c r="D402" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D402" s="2"/>
       <c r="E402" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.35">
@@ -9752,17 +9775,17 @@
         <v>162</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C403" s="2"/>
-      <c r="D403" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D403" s="2"/>
       <c r="E403" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
@@ -9770,19 +9793,17 @@
         <v>162</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="D404" s="2">
-        <v>1</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D404" s="2"/>
       <c r="E404" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>562</v>
+        <v>514</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
@@ -9790,19 +9811,17 @@
         <v>162</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D405" s="2">
-        <v>1</v>
+        <v>548</v>
+      </c>
+      <c r="C405" s="2"/>
+      <c r="D405" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F405" s="2" t="s">
-        <v>519</v>
+        <v>549</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.35">
@@ -9812,17 +9831,15 @@
       <c r="B406" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C406" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D406" s="2">
-        <v>1</v>
+      <c r="C406" s="2"/>
+      <c r="D406" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.35">
@@ -9833,16 +9850,16 @@
         <v>513</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>135</v>
+        <v>554</v>
       </c>
       <c r="D407" s="2">
         <v>1</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.35">
@@ -9853,16 +9870,16 @@
         <v>513</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>569</v>
+        <v>518</v>
       </c>
       <c r="D408" s="2">
         <v>1</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>571</v>
+        <v>519</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
@@ -9870,17 +9887,19 @@
         <v>162</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C409" s="2"/>
-      <c r="D409" s="2" t="s">
-        <v>144</v>
+        <v>513</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D409" s="2">
+        <v>1</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>564</v>
+        <v>520</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.35">
@@ -9888,19 +9907,19 @@
         <v>162</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>565</v>
+        <v>513</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>301</v>
+        <v>135</v>
       </c>
       <c r="D410" s="2">
         <v>1</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>567</v>
+        <v>536</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.35">
@@ -9908,19 +9927,19 @@
         <v>162</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>565</v>
+        <v>513</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D411" s="2">
         <v>1</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.35">
@@ -9928,11 +9947,11 @@
         <v>162</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C412" s="2"/>
       <c r="D412" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>555</v>
@@ -9946,17 +9965,19 @@
         <v>162</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C413" s="2"/>
-      <c r="D413" s="2" t="s">
-        <v>144</v>
+        <v>565</v>
+      </c>
+      <c r="C413" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D413" s="2">
+        <v>1</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
@@ -9964,19 +9985,19 @@
         <v>162</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D414" s="2">
         <v>1</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
@@ -9984,17 +10005,17 @@
         <v>162</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C415" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D415" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="C415" s="2"/>
+      <c r="D415" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E415" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>584</v>
+        <v>564</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.35">
@@ -10002,17 +10023,17 @@
         <v>162</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="C416" s="2"/>
       <c r="D416" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.35">
@@ -10020,17 +10041,19 @@
         <v>162</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="C417" s="2"/>
-      <c r="D417" s="2" t="s">
-        <v>128</v>
+        <v>572</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D417" s="2">
+        <v>1</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.35">
@@ -10038,17 +10061,17 @@
         <v>162</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C418" s="2"/>
-      <c r="D418" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D418" s="2"/>
       <c r="E418" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>549</v>
+        <v>584</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.35">
@@ -10056,17 +10079,17 @@
         <v>162</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>551</v>
+        <v>580</v>
       </c>
       <c r="C419" s="2"/>
       <c r="D419" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.35">
@@ -10074,17 +10097,17 @@
         <v>162</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="C420" s="2"/>
       <c r="D420" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
@@ -10092,17 +10115,17 @@
         <v>162</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C421" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="D421" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C421" s="2"/>
+      <c r="D421" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E421" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F421" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.35">
@@ -10110,17 +10133,17 @@
         <v>162</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C422" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D422" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="C422" s="2"/>
+      <c r="D422" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E422" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.35">
@@ -10128,17 +10151,17 @@
         <v>162</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C423" s="2"/>
       <c r="D423" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F423" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.35">
@@ -10146,12 +10169,12 @@
         <v>162</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="C424" s="2"/>
-      <c r="D424" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D424" s="2"/>
       <c r="E424" s="2" t="s">
         <v>537</v>
       </c>
@@ -10164,17 +10187,17 @@
         <v>162</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="C425" s="2"/>
-      <c r="D425" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D425" s="2"/>
       <c r="E425" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F425" s="2" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.35">
@@ -10182,17 +10205,17 @@
         <v>162</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>275</v>
+        <v>545</v>
       </c>
       <c r="C426" s="2"/>
       <c r="D426" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>279</v>
+        <v>547</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
@@ -10200,19 +10223,17 @@
         <v>162</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C427" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D427" s="2">
-        <v>1</v>
+        <v>546</v>
+      </c>
+      <c r="C427" s="2"/>
+      <c r="D427" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F427" s="2" t="s">
-        <v>282</v>
+        <v>547</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.35">
@@ -10220,17 +10241,17 @@
         <v>162</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C428" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D428" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="C428" s="2"/>
+      <c r="D428" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="E428" s="2" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F428" s="2" t="s">
-        <v>378</v>
+        <v>514</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.35">
@@ -10240,15 +10261,15 @@
       <c r="B429" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C429" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D429" s="2"/>
+      <c r="C429" s="2"/>
+      <c r="D429" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E429" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F429" s="2" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
@@ -10259,14 +10280,16 @@
         <v>275</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D430" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="D430" s="2">
+        <v>1</v>
+      </c>
       <c r="E430" s="2" t="s">
-        <v>481</v>
+        <v>269</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>64</v>
+        <v>282</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.35">
@@ -10277,14 +10300,14 @@
         <v>275</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>276</v>
+        <v>487</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>279</v>
+        <v>378</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.35">
@@ -10295,14 +10318,14 @@
         <v>275</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
@@ -10313,14 +10336,14 @@
         <v>275</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" s="2" t="s">
-        <v>269</v>
+        <v>481</v>
       </c>
       <c r="F433" s="2" t="s">
-        <v>489</v>
+        <v>64</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.35">
@@ -10328,17 +10351,17 @@
         <v>162</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C434" s="2"/>
-      <c r="D434" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D434" s="2"/>
       <c r="E434" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.35">
@@ -10346,19 +10369,17 @@
         <v>162</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D435" s="2">
-        <v>1</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="D435" s="2"/>
       <c r="E435" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.35">
@@ -10366,19 +10387,17 @@
         <v>162</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D436" s="2">
-        <v>1</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="D436" s="2"/>
       <c r="E436" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>270</v>
+        <v>489</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.35">
@@ -10386,17 +10405,17 @@
         <v>162</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C437" s="2"/>
       <c r="D437" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F437" s="2" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
@@ -10404,39 +10423,39 @@
         <v>162</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>56</v>
+        <v>271</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>199</v>
+        <v>272</v>
       </c>
       <c r="D438" s="2">
         <v>1</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>198</v>
+        <v>273</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A439" t="s">
+      <c r="A439" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D439" s="1">
+        <v>271</v>
+      </c>
+      <c r="C439" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D439" s="2">
         <v>1</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>52</v>
+        <v>269</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>54</v>
+        <v>270</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
@@ -10444,19 +10463,17 @@
         <v>162</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D440" s="1">
-        <v>1</v>
+        <v>274</v>
+      </c>
+      <c r="C440" s="2"/>
+      <c r="D440" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>203</v>
+        <v>279</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.35">
@@ -10466,33 +10483,37 @@
       <c r="B441" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C441" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D441" s="1"/>
+      <c r="C441" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D441" s="2">
+        <v>1</v>
+      </c>
       <c r="E441" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F441" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A442" s="1" t="s">
+      <c r="A442" t="s">
         <v>162</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D442" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="D442" s="1">
+        <v>1</v>
+      </c>
       <c r="E442" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.35">
@@ -10503,14 +10524,16 @@
         <v>56</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D443" s="1"/>
+        <v>204</v>
+      </c>
+      <c r="D443" s="1">
+        <v>1</v>
+      </c>
       <c r="E443" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.35">
@@ -10521,7 +10544,7 @@
         <v>56</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="D444" s="1"/>
       <c r="E444" s="2" t="s">
@@ -10538,15 +10561,15 @@
       <c r="B445" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C445" s="2"/>
-      <c r="D445" s="2" t="s">
-        <v>144</v>
-      </c>
+      <c r="C445" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D445" s="1"/>
       <c r="E445" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>53</v>
+        <v>194</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.35">
@@ -10554,16 +10577,17 @@
         <v>162</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D446" t="s">
-        <v>144</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C446" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D446" s="1"/>
       <c r="E446" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F446" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.35">
@@ -10571,16 +10595,17 @@
         <v>162</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C447" t="s">
-        <v>200</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C447" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D447" s="1"/>
       <c r="E447" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.35">
@@ -10588,16 +10613,17 @@
         <v>162</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C448" t="s">
-        <v>94</v>
+        <v>56</v>
+      </c>
+      <c r="C448" s="2"/>
+      <c r="D448" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F448" s="2" t="s">
-        <v>198</v>
+        <v>53</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
@@ -10607,8 +10633,8 @@
       <c r="B449" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C449" t="s">
-        <v>201</v>
+      <c r="D449" t="s">
+        <v>144</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>193</v>
@@ -10618,20 +10644,20 @@
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A450" t="s">
-        <v>162</v>
-      </c>
-      <c r="B450" t="s">
-        <v>148</v>
-      </c>
-      <c r="D450" t="s">
-        <v>144</v>
+      <c r="A450" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B450" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C450" t="s">
+        <v>200</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F450" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
@@ -10639,19 +10665,16 @@
         <v>162</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="C451" t="s">
-        <v>199</v>
-      </c>
-      <c r="D451">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F451" s="2" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.35">
@@ -10659,19 +10682,16 @@
         <v>162</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="C452" t="s">
-        <v>204</v>
-      </c>
-      <c r="D452">
-        <v>2</v>
+        <v>201</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F452" s="2" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
@@ -10681,8 +10701,8 @@
       <c r="B453" t="s">
         <v>148</v>
       </c>
-      <c r="C453" t="s">
-        <v>195</v>
+      <c r="D453" t="s">
+        <v>144</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>193</v>
@@ -10692,20 +10712,23 @@
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A454" t="s">
-        <v>162</v>
-      </c>
-      <c r="B454" t="s">
+      <c r="A454" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B454" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C454" t="s">
-        <v>196</v>
+        <v>199</v>
+      </c>
+      <c r="D454">
+        <v>2</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.35">
@@ -10713,53 +10736,53 @@
         <v>162</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="D455" t="s">
-        <v>144</v>
+        <v>148</v>
+      </c>
+      <c r="C455" t="s">
+        <v>204</v>
+      </c>
+      <c r="D455">
+        <v>2</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F455" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A456" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B456" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D456" t="s">
-        <v>144</v>
+      <c r="A456" t="s">
+        <v>162</v>
+      </c>
+      <c r="B456" t="s">
+        <v>148</v>
+      </c>
+      <c r="C456" t="s">
+        <v>195</v>
       </c>
       <c r="E456" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F456" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A457" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B457" s="1" t="s">
-        <v>192</v>
+      <c r="A457" t="s">
+        <v>162</v>
+      </c>
+      <c r="B457" t="s">
+        <v>148</v>
       </c>
       <c r="C457" t="s">
-        <v>100</v>
-      </c>
-      <c r="D457">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="F457" s="2" t="s">
-        <v>54</v>
+        <v>212</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.35">
@@ -10767,7 +10790,7 @@
         <v>162</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>209</v>
+        <v>450</v>
       </c>
       <c r="D458" t="s">
         <v>144</v>
@@ -10784,19 +10807,16 @@
         <v>162</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C459" t="s">
-        <v>199</v>
-      </c>
-      <c r="D459">
-        <v>1</v>
+        <v>192</v>
+      </c>
+      <c r="D459" t="s">
+        <v>144</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F459" s="2" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.35">
@@ -10804,19 +10824,19 @@
         <v>162</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C460" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="D460">
         <v>1</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="F460" s="2" t="s">
-        <v>211</v>
+        <v>54</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.35">
@@ -10826,8 +10846,8 @@
       <c r="B461" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C461" t="s">
-        <v>449</v>
+      <c r="D461" t="s">
+        <v>144</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>193</v>
@@ -10841,16 +10861,19 @@
         <v>162</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D462" t="s">
-        <v>144</v>
-      </c>
-      <c r="E462" t="s">
+        <v>209</v>
+      </c>
+      <c r="C462" t="s">
+        <v>199</v>
+      </c>
+      <c r="D462">
+        <v>1</v>
+      </c>
+      <c r="E462" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F462" t="s">
-        <v>206</v>
+      <c r="F462" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.35">
@@ -10858,19 +10881,19 @@
         <v>162</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C463" t="s">
-        <v>100</v>
+        <v>204</v>
       </c>
       <c r="D463">
         <v>1</v>
       </c>
-      <c r="E463" t="s">
+      <c r="E463" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F463" t="s">
-        <v>208</v>
+      <c r="F463" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.35">
@@ -10878,16 +10901,16 @@
         <v>162</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D464" t="s">
-        <v>144</v>
-      </c>
-      <c r="E464" t="s">
-        <v>374</v>
-      </c>
-      <c r="F464" t="s">
-        <v>376</v>
+        <v>209</v>
+      </c>
+      <c r="C464" t="s">
+        <v>449</v>
+      </c>
+      <c r="E464" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F464" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
@@ -10895,16 +10918,16 @@
         <v>162</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>540</v>
+        <v>207</v>
       </c>
       <c r="D465" t="s">
         <v>144</v>
       </c>
       <c r="E465" t="s">
-        <v>537</v>
+        <v>193</v>
       </c>
       <c r="F465" t="s">
-        <v>539</v>
+        <v>206</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.35">
@@ -10912,16 +10935,19 @@
         <v>162</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>540</v>
+        <v>207</v>
       </c>
       <c r="C466" t="s">
-        <v>552</v>
+        <v>100</v>
+      </c>
+      <c r="D466">
+        <v>1</v>
       </c>
       <c r="E466" t="s">
-        <v>537</v>
+        <v>193</v>
       </c>
       <c r="F466" t="s">
-        <v>549</v>
+        <v>208</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.35">
@@ -10929,16 +10955,16 @@
         <v>162</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="C467" t="s">
-        <v>553</v>
+        <v>373</v>
+      </c>
+      <c r="D467" t="s">
+        <v>144</v>
       </c>
       <c r="E467" t="s">
-        <v>537</v>
+        <v>374</v>
       </c>
       <c r="F467" t="s">
-        <v>549</v>
+        <v>376</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.35">
@@ -10948,14 +10974,14 @@
       <c r="B468" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C468" t="s">
-        <v>196</v>
+      <c r="D468" t="s">
+        <v>144</v>
       </c>
       <c r="E468" t="s">
         <v>537</v>
       </c>
       <c r="F468" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
@@ -10963,16 +10989,16 @@
         <v>162</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D469" t="s">
-        <v>144</v>
+        <v>540</v>
+      </c>
+      <c r="C469" t="s">
+        <v>552</v>
       </c>
       <c r="E469" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F469" t="s">
-        <v>344</v>
+        <v>549</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
@@ -10980,19 +11006,16 @@
         <v>162</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>335</v>
+        <v>540</v>
       </c>
       <c r="C470" t="s">
-        <v>336</v>
-      </c>
-      <c r="D470">
-        <v>1</v>
+        <v>553</v>
       </c>
       <c r="E470" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F470" t="s">
-        <v>337</v>
+        <v>549</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.35">
@@ -11000,19 +11023,16 @@
         <v>162</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>335</v>
+        <v>540</v>
       </c>
       <c r="C471" t="s">
-        <v>102</v>
-      </c>
-      <c r="D471">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="E471" t="s">
-        <v>331</v>
+        <v>537</v>
       </c>
       <c r="F471" t="s">
-        <v>344</v>
+        <v>549</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.35">
@@ -11022,17 +11042,14 @@
       <c r="B472" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C472" t="s">
-        <v>115</v>
-      </c>
-      <c r="D472">
-        <v>1</v>
+      <c r="D472" t="s">
+        <v>144</v>
       </c>
       <c r="E472" t="s">
         <v>331</v>
       </c>
       <c r="F472" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.35">
@@ -11043,7 +11060,7 @@
         <v>335</v>
       </c>
       <c r="C473" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D473">
         <v>1</v>
@@ -11052,7 +11069,7 @@
         <v>331</v>
       </c>
       <c r="F473" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.35">
@@ -11060,16 +11077,19 @@
         <v>162</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D474" t="s">
-        <v>144</v>
+        <v>335</v>
+      </c>
+      <c r="C474" t="s">
+        <v>102</v>
+      </c>
+      <c r="D474">
+        <v>1</v>
       </c>
       <c r="E474" t="s">
         <v>331</v>
       </c>
       <c r="F474" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.35">
@@ -11077,10 +11097,10 @@
         <v>162</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C475" t="s">
-        <v>340</v>
+        <v>115</v>
       </c>
       <c r="D475">
         <v>1</v>
@@ -11089,7 +11109,7 @@
         <v>331</v>
       </c>
       <c r="F475" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.35">
@@ -11097,10 +11117,10 @@
         <v>162</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C476" t="s">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="D476">
         <v>1</v>
@@ -11109,7 +11129,7 @@
         <v>331</v>
       </c>
       <c r="F476" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.35">
@@ -11119,17 +11139,14 @@
       <c r="B477" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C477" t="s">
-        <v>342</v>
-      </c>
-      <c r="D477">
-        <v>1</v>
+      <c r="D477" t="s">
+        <v>144</v>
       </c>
       <c r="E477" t="s">
         <v>331</v>
       </c>
       <c r="F477" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.35">
@@ -11137,16 +11154,19 @@
         <v>162</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D478" t="s">
-        <v>128</v>
+        <v>333</v>
+      </c>
+      <c r="C478" t="s">
+        <v>340</v>
+      </c>
+      <c r="D478">
+        <v>1</v>
       </c>
       <c r="E478" t="s">
         <v>331</v>
       </c>
       <c r="F478" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.35">
@@ -11154,16 +11174,19 @@
         <v>162</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D479" t="s">
-        <v>128</v>
+        <v>333</v>
+      </c>
+      <c r="C479" t="s">
+        <v>100</v>
+      </c>
+      <c r="D479">
+        <v>1</v>
       </c>
       <c r="E479" t="s">
-        <v>481</v>
+        <v>331</v>
       </c>
       <c r="F479" t="s">
-        <v>64</v>
+        <v>334</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.35">
@@ -11171,16 +11194,19 @@
         <v>162</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D480" t="s">
-        <v>128</v>
+        <v>333</v>
+      </c>
+      <c r="C480" t="s">
+        <v>342</v>
+      </c>
+      <c r="D480">
+        <v>1</v>
       </c>
       <c r="E480" t="s">
-        <v>193</v>
+        <v>331</v>
       </c>
       <c r="F480" t="s">
-        <v>206</v>
+        <v>343</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.35">
@@ -11188,16 +11214,16 @@
         <v>162</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>502</v>
+        <v>442</v>
       </c>
       <c r="D481" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E481" t="s">
-        <v>497</v>
+        <v>331</v>
       </c>
       <c r="F481" t="s">
-        <v>503</v>
+        <v>344</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.35">
@@ -11205,19 +11231,16 @@
         <v>162</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C482" t="s">
-        <v>415</v>
-      </c>
-      <c r="D482">
-        <v>1</v>
+        <v>482</v>
+      </c>
+      <c r="D482" t="s">
+        <v>128</v>
       </c>
       <c r="E482" t="s">
-        <v>532</v>
+        <v>481</v>
       </c>
       <c r="F482" t="s">
-        <v>533</v>
+        <v>64</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.35">
@@ -11225,16 +11248,16 @@
         <v>162</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C483" t="s">
-        <v>506</v>
+        <v>232</v>
+      </c>
+      <c r="D483" t="s">
+        <v>128</v>
       </c>
       <c r="E483" t="s">
-        <v>497</v>
+        <v>193</v>
       </c>
       <c r="F483" t="s">
-        <v>507</v>
+        <v>206</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.35">
@@ -11244,14 +11267,14 @@
       <c r="B484" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C484" t="s">
-        <v>531</v>
+      <c r="D484" t="s">
+        <v>144</v>
       </c>
       <c r="E484" t="s">
         <v>497</v>
       </c>
       <c r="F484" t="s">
-        <v>527</v>
+        <v>503</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.35">
@@ -11259,10 +11282,13 @@
         <v>162</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="D485" t="s">
-        <v>345</v>
+        <v>502</v>
+      </c>
+      <c r="C485" t="s">
+        <v>415</v>
+      </c>
+      <c r="D485">
+        <v>1</v>
       </c>
       <c r="E485" t="s">
         <v>532</v>
@@ -11276,15 +11302,66 @@
         <v>162</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="D486" t="s">
-        <v>144</v>
+        <v>502</v>
+      </c>
+      <c r="C486" t="s">
+        <v>506</v>
       </c>
       <c r="E486" t="s">
         <v>497</v>
       </c>
       <c r="F486" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A487" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C487" t="s">
+        <v>531</v>
+      </c>
+      <c r="E487" t="s">
+        <v>497</v>
+      </c>
+      <c r="F487" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A488" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D488" t="s">
+        <v>345</v>
+      </c>
+      <c r="E488" t="s">
+        <v>532</v>
+      </c>
+      <c r="F488" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A489" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D489" t="s">
+        <v>144</v>
+      </c>
+      <c r="E489" t="s">
+        <v>497</v>
+      </c>
+      <c r="F489" t="s">
         <v>529</v>
       </c>
     </row>
